--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\명찰\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A498F48D-C98A-4455-8174-77E52117731B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5BB23D5-BBD0-4040-9CEC-DA75388274AB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19290" windowHeight="9540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="126">
   <si>
     <t xml:space="preserve">러닝센터 명찰제작 양식 </t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -326,6 +326,100 @@
     <t>25년 서비스센터 실장 
 데이터 역량 교육</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택 특강</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. 성과관리/ 피플 리더십</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. AI Tool을 활용한 서비스 문제해결 워크샵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 데이터 핸들링 기초 역량 업그레이드</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. AI Tool을 활용한 서비스 문제해결 워크샵</t>
+  </si>
+  <si>
+    <t>3. 데이터 핸들링 기초 역량 업그레이드</t>
+  </si>
+  <si>
+    <t>4. 성과관리/ 피플 리더십</t>
+  </si>
+  <si>
+    <t>3. AI Tool을 활용한 서비스 문제해결 워크샵</t>
+  </si>
+  <si>
+    <t>4. 데이터 핸들링 기초 역량 업그레이드</t>
+  </si>
+  <si>
+    <t>5. 성과관리/ 피플 리더십</t>
+  </si>
+  <si>
+    <t>4. AI Tool을 활용한 서비스 문제해결 워크샵</t>
+  </si>
+  <si>
+    <t>5. 데이터 핸들링 기초 역량 업그레이드</t>
+  </si>
+  <si>
+    <t>6. 성과관리/ 피플 리더십</t>
+  </si>
+  <si>
+    <t>5. AI Tool을 활용한 서비스 문제해결 워크샵</t>
+  </si>
+  <si>
+    <t>6. 데이터 핸들링 기초 역량 업그레이드</t>
+  </si>
+  <si>
+    <t>7. 성과관리/ 피플 리더십</t>
+  </si>
+  <si>
+    <t>6. AI Tool을 활용한 서비스 문제해결 워크샵</t>
+  </si>
+  <si>
+    <t>7. 데이터 핸들링 기초 역량 업그레이드</t>
+  </si>
+  <si>
+    <t>8. 성과관리/ 피플 리더십</t>
+  </si>
+  <si>
+    <t>7. AI Tool을 활용한 서비스 문제해결 워크샵</t>
+  </si>
+  <si>
+    <t>8. 데이터 핸들링 기초 역량 업그레이드</t>
+  </si>
+  <si>
+    <t>9. 성과관리/ 피플 리더십</t>
+  </si>
+  <si>
+    <t>8. AI Tool을 활용한 서비스 문제해결 워크샵</t>
+  </si>
+  <si>
+    <t>9. 데이터 핸들링 기초 역량 업그레이드</t>
+  </si>
+  <si>
+    <t>10. 성과관리/ 피플 리더십</t>
+  </si>
+  <si>
+    <t>9. AI Tool을 활용한 서비스 문제해결 워크샵</t>
+  </si>
+  <si>
+    <t>10. 데이터 핸들링 기초 역량 업그레이드</t>
+  </si>
+  <si>
+    <t>11. 성과관리/ 피플 리더십</t>
+  </si>
+  <si>
+    <t>10. AI Tool을 활용한 서비스 문제해결 워크샵</t>
+  </si>
+  <si>
+    <t>11. 데이터 핸들링 기초 역량 업그레이드</t>
   </si>
 </sst>
 </file>
@@ -1640,29 +1734,29 @@
     <xf numFmtId="0" fontId="6" fillId="36" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="238">
@@ -2239,51 +2333,56 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:E53"/>
+  <dimension ref="A2:F53"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15.77734375" customWidth="1"/>
+    <col min="3" max="6" width="15.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" ht="20.25">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:6" ht="20.25">
+      <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-    </row>
-    <row r="3" spans="1:5" ht="54" customHeight="1">
-      <c r="A3" s="6" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+    </row>
+    <row r="3" spans="1:6" ht="54" customHeight="1">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-    </row>
-    <row r="4" spans="1:5" ht="16.5">
-      <c r="A4" s="6" t="s">
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+    </row>
+    <row r="4" spans="1:6" ht="16.5">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="16.5" customHeight="1">
+    <row r="5" spans="1:6" ht="16.5" customHeight="1">
       <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
@@ -2293,14 +2392,15 @@
       <c r="C5" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D5" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="D5" s="2"/>
+      <c r="E5" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="16.5" customHeight="1">
+    <row r="6" spans="1:6" ht="16.5" customHeight="1">
       <c r="A6" s="8"/>
       <c r="B6" s="1" t="s">
         <v>87</v>
@@ -2308,14 +2408,15 @@
       <c r="C6" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D6" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E6" s="10" t="s">
+      <c r="D6" s="2"/>
+      <c r="E6" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="16.5" customHeight="1">
+    <row r="7" spans="1:6" ht="16.5" customHeight="1">
       <c r="A7" s="8"/>
       <c r="B7" s="1" t="s">
         <v>86</v>
@@ -2323,29 +2424,35 @@
       <c r="C7" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D7" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E7" s="10">
+      <c r="D7" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F7" s="7">
         <v>318537</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="16.5">
+    <row r="8" spans="1:6" ht="16.5">
       <c r="A8" s="8"/>
       <c r="B8" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="D8" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E8" s="10" t="s">
+      <c r="D8" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="13.5" customHeight="1">
+    <row r="9" spans="1:6" ht="13.5" customHeight="1">
       <c r="A9" s="8" t="s">
         <v>5</v>
       </c>
@@ -2355,14 +2462,17 @@
       <c r="C9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E9" s="1">
+      <c r="D9" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F9" s="1">
         <v>293575</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="16.5">
+    <row r="10" spans="1:6" ht="16.5">
       <c r="A10" s="8"/>
       <c r="B10" s="1" t="s">
         <v>48</v>
@@ -2370,14 +2480,17 @@
       <c r="C10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E10" s="1">
+      <c r="D10" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F10" s="1">
         <v>294004</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="16.5">
+    <row r="11" spans="1:6" ht="16.5">
       <c r="A11" s="8"/>
       <c r="B11" s="1" t="s">
         <v>49</v>
@@ -2385,14 +2498,17 @@
       <c r="C11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E11" s="1">
+      <c r="D11" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E11" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F11" s="1">
         <v>292052</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="16.5">
+    <row r="12" spans="1:6" ht="16.5">
       <c r="A12" s="8"/>
       <c r="B12" s="1" t="s">
         <v>49</v>
@@ -2400,14 +2516,17 @@
       <c r="C12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E12" s="1">
+      <c r="D12" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E12" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F12" s="1">
         <v>292052</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="16.5">
+    <row r="13" spans="1:6" ht="16.5">
       <c r="A13" s="8"/>
       <c r="B13" s="1" t="s">
         <v>50</v>
@@ -2415,14 +2534,17 @@
       <c r="C13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E13" s="1">
+      <c r="D13" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F13" s="1">
         <v>293976</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="16.5">
+    <row r="14" spans="1:6" ht="16.5">
       <c r="A14" s="8"/>
       <c r="B14" s="1" t="s">
         <v>51</v>
@@ -2430,14 +2552,17 @@
       <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E14" s="1">
+      <c r="D14" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E14" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F14" s="1">
         <v>289090</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="16.5">
+    <row r="15" spans="1:6" ht="16.5">
       <c r="A15" s="8"/>
       <c r="B15" s="1" t="s">
         <v>52</v>
@@ -2445,14 +2570,17 @@
       <c r="C15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E15" s="1">
+      <c r="D15" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F15" s="1">
         <v>293378</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="16.5">
+    <row r="16" spans="1:6" ht="16.5">
       <c r="A16" s="8"/>
       <c r="B16" s="1" t="s">
         <v>53</v>
@@ -2460,14 +2588,17 @@
       <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E16" s="1">
+      <c r="D16" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F16" s="1">
         <v>292659</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="16.5">
+    <row r="17" spans="1:6" ht="16.5">
       <c r="A17" s="8"/>
       <c r="B17" s="1" t="s">
         <v>54</v>
@@ -2475,14 +2606,17 @@
       <c r="C17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E17" s="1">
+      <c r="D17" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F17" s="1">
         <v>292672</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="16.5">
+    <row r="18" spans="1:6" ht="16.5">
       <c r="A18" s="8"/>
       <c r="B18" s="1" t="s">
         <v>55</v>
@@ -2490,14 +2624,17 @@
       <c r="C18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E18" s="1">
+      <c r="D18" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E18" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F18" s="1">
         <v>294269</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="16.5">
+    <row r="19" spans="1:6" ht="16.5">
       <c r="A19" s="8"/>
       <c r="B19" s="1" t="s">
         <v>56</v>
@@ -2505,14 +2642,17 @@
       <c r="C19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E19" s="1">
+      <c r="D19" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E19" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F19" s="1">
         <v>292325</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="16.5">
+    <row r="20" spans="1:6" ht="16.5">
       <c r="A20" s="8"/>
       <c r="B20" s="1" t="s">
         <v>57</v>
@@ -2520,14 +2660,17 @@
       <c r="C20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E20" s="1">
+      <c r="D20" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E20" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F20" s="1">
         <v>293533</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="16.5">
+    <row r="21" spans="1:6" ht="16.5">
       <c r="A21" s="8"/>
       <c r="B21" s="1" t="s">
         <v>58</v>
@@ -2535,14 +2678,17 @@
       <c r="C21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E21" s="1">
+      <c r="D21" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F21" s="1">
         <v>291742</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="16.5">
+    <row r="22" spans="1:6" ht="16.5">
       <c r="A22" s="8"/>
       <c r="B22" s="1" t="s">
         <v>59</v>
@@ -2550,14 +2696,17 @@
       <c r="C22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E22" s="1">
+      <c r="D22" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F22" s="1">
         <v>293692</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="16.5">
+    <row r="23" spans="1:6" ht="16.5">
       <c r="A23" s="8"/>
       <c r="B23" s="1" t="s">
         <v>60</v>
@@ -2565,14 +2714,17 @@
       <c r="C23" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E23" s="1">
+      <c r="D23" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F23" s="1">
         <v>293127</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="16.5">
+    <row r="24" spans="1:6" ht="16.5">
       <c r="A24" s="8"/>
       <c r="B24" s="1" t="s">
         <v>61</v>
@@ -2580,14 +2732,17 @@
       <c r="C24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E24" s="1">
+      <c r="D24" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E24" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F24" s="1">
         <v>293979</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="16.5">
+    <row r="25" spans="1:6" ht="16.5">
       <c r="A25" s="8"/>
       <c r="B25" s="1" t="s">
         <v>62</v>
@@ -2595,14 +2750,17 @@
       <c r="C25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E25" s="1">
+      <c r="D25" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F25" s="1">
         <v>292961</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="16.5">
+    <row r="26" spans="1:6" ht="16.5">
       <c r="A26" s="8"/>
       <c r="B26" s="1" t="s">
         <v>63</v>
@@ -2610,14 +2768,17 @@
       <c r="C26" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E26" s="1">
+      <c r="D26" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E26" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F26" s="1">
         <v>293130</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="16.5">
+    <row r="27" spans="1:6" ht="16.5">
       <c r="A27" s="8"/>
       <c r="B27" s="1" t="s">
         <v>64</v>
@@ -2625,14 +2786,17 @@
       <c r="C27" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E27" s="1">
+      <c r="D27" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E27" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F27" s="1">
         <v>292917</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="16.5">
+    <row r="28" spans="1:6" ht="16.5">
       <c r="A28" s="8"/>
       <c r="B28" s="1" t="s">
         <v>65</v>
@@ -2640,14 +2804,17 @@
       <c r="C28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E28" s="1">
+      <c r="D28" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E28" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F28" s="1">
         <v>294351</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="16.5">
+    <row r="29" spans="1:6" ht="16.5">
       <c r="A29" s="8"/>
       <c r="B29" s="1" t="s">
         <v>66</v>
@@ -2655,14 +2822,17 @@
       <c r="C29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D29" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E29" s="1">
+      <c r="D29" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E29" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F29" s="1">
         <v>294306</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="16.5">
+    <row r="30" spans="1:6" ht="16.5">
       <c r="A30" s="8"/>
       <c r="B30" s="1" t="s">
         <v>61</v>
@@ -2670,14 +2840,17 @@
       <c r="C30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D30" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E30" s="1">
+      <c r="D30" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E30" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F30" s="1">
         <v>293131</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="16.5">
+    <row r="31" spans="1:6" ht="16.5">
       <c r="A31" s="8"/>
       <c r="B31" s="1" t="s">
         <v>67</v>
@@ -2685,14 +2858,17 @@
       <c r="C31" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D31" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E31" s="1">
+      <c r="D31" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E31" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F31" s="1">
         <v>292371</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="16.5">
+    <row r="32" spans="1:6" ht="16.5">
       <c r="A32" s="8"/>
       <c r="B32" s="1" t="s">
         <v>68</v>
@@ -2700,14 +2876,17 @@
       <c r="C32" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E32" s="1">
+      <c r="D32" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E32" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F32" s="1">
         <v>294307</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="16.5">
+    <row r="33" spans="1:6" ht="16.5">
       <c r="A33" s="8"/>
       <c r="B33" s="1" t="s">
         <v>69</v>
@@ -2715,14 +2894,17 @@
       <c r="C33" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D33" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E33" s="1">
+      <c r="D33" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E33" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F33" s="1">
         <v>293134</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="16.5">
+    <row r="34" spans="1:6" ht="16.5">
       <c r="A34" s="8"/>
       <c r="B34" s="1" t="s">
         <v>70</v>
@@ -2730,14 +2912,17 @@
       <c r="C34" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D34" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E34" s="1">
+      <c r="D34" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E34" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F34" s="1">
         <v>293007</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="16.5">
+    <row r="35" spans="1:6" ht="16.5">
       <c r="A35" s="8"/>
       <c r="B35" s="1" t="s">
         <v>71</v>
@@ -2745,14 +2930,17 @@
       <c r="C35" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D35" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E35" s="1">
+      <c r="D35" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E35" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F35" s="1">
         <v>292202</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="16.5">
+    <row r="36" spans="1:6" ht="16.5">
       <c r="A36" s="8"/>
       <c r="B36" s="1" t="s">
         <v>72</v>
@@ -2760,14 +2948,17 @@
       <c r="C36" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E36" s="1">
+      <c r="D36" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E36" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F36" s="1">
         <v>292763</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="16.5">
+    <row r="37" spans="1:6" ht="16.5">
       <c r="A37" s="8"/>
       <c r="B37" s="1" t="s">
         <v>73</v>
@@ -2775,14 +2966,17 @@
       <c r="C37" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D37" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E37" s="1">
+      <c r="D37" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E37" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F37" s="1">
         <v>293262</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="16.5">
+    <row r="38" spans="1:6" ht="16.5">
       <c r="A38" s="8"/>
       <c r="B38" s="1" t="s">
         <v>74</v>
@@ -2790,14 +2984,17 @@
       <c r="C38" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D38" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E38" s="1">
+      <c r="D38" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E38" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F38" s="1">
         <v>293287</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="16.5">
+    <row r="39" spans="1:6" ht="16.5">
       <c r="A39" s="8"/>
       <c r="B39" s="1" t="s">
         <v>75</v>
@@ -2805,14 +3002,17 @@
       <c r="C39" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D39" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E39" s="1">
+      <c r="D39" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E39" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F39" s="1">
         <v>293463</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="16.5">
+    <row r="40" spans="1:6" ht="16.5">
       <c r="A40" s="8"/>
       <c r="B40" s="1" t="s">
         <v>76</v>
@@ -2820,14 +3020,17 @@
       <c r="C40" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D40" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E40" s="1">
+      <c r="D40" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E40" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F40" s="1">
         <v>289000</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="16.5">
+    <row r="41" spans="1:6" ht="16.5">
       <c r="A41" s="8"/>
       <c r="B41" s="1" t="s">
         <v>75</v>
@@ -2835,14 +3038,17 @@
       <c r="C41" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D41" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E41" s="1">
+      <c r="D41" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E41" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F41" s="1">
         <v>293464</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="16.5">
+    <row r="42" spans="1:6" ht="16.5">
       <c r="A42" s="8"/>
       <c r="B42" s="1" t="s">
         <v>77</v>
@@ -2850,14 +3056,17 @@
       <c r="C42" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D42" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E42" s="1">
+      <c r="D42" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E42" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F42" s="1">
         <v>292789</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="16.5">
+    <row r="43" spans="1:6" ht="16.5">
       <c r="A43" s="8"/>
       <c r="B43" s="1" t="s">
         <v>78</v>
@@ -2865,14 +3074,17 @@
       <c r="C43" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D43" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E43" s="1">
+      <c r="D43" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E43" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F43" s="1">
         <v>293434</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="16.5">
+    <row r="44" spans="1:6" ht="16.5">
       <c r="A44" s="8"/>
       <c r="B44" s="1" t="s">
         <v>79</v>
@@ -2880,14 +3092,17 @@
       <c r="C44" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D44" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E44" s="1">
+      <c r="D44" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E44" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F44" s="1">
         <v>292610</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="16.5">
+    <row r="45" spans="1:6" ht="16.5">
       <c r="A45" s="8"/>
       <c r="B45" s="1" t="s">
         <v>80</v>
@@ -2895,14 +3110,17 @@
       <c r="C45" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D45" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E45" s="1">
+      <c r="D45" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E45" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F45" s="1">
         <v>294322</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="16.5">
+    <row r="46" spans="1:6" ht="16.5">
       <c r="A46" s="8"/>
       <c r="B46" s="1" t="s">
         <v>81</v>
@@ -2910,14 +3128,17 @@
       <c r="C46" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D46" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E46" s="1">
+      <c r="D46" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E46" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F46" s="1">
         <v>293962</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="16.5">
+    <row r="47" spans="1:6" ht="16.5">
       <c r="A47" s="8"/>
       <c r="B47" s="1" t="s">
         <v>60</v>
@@ -2925,14 +3146,17 @@
       <c r="C47" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D47" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E47" s="1">
+      <c r="D47" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E47" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F47" s="1">
         <v>293442</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="16.5">
+    <row r="48" spans="1:6" ht="16.5">
       <c r="A48" s="8"/>
       <c r="B48" s="1" t="s">
         <v>82</v>
@@ -2940,14 +3164,17 @@
       <c r="C48" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D48" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E48" s="1">
+      <c r="D48" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E48" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F48" s="1">
         <v>292802</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="16.5">
+    <row r="49" spans="1:6" ht="16.5">
       <c r="A49" s="8"/>
       <c r="B49" s="3" t="s">
         <v>91</v>
@@ -2955,40 +3182,55 @@
       <c r="C49" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D49" s="9">
-        <v>45946</v>
-      </c>
-      <c r="E49" s="3">
+      <c r="D49" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E49" s="6">
+        <v>45946</v>
+      </c>
+      <c r="F49" s="3">
         <v>292091</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="16.5">
+    <row r="50" spans="1:6" ht="16.5">
       <c r="A50" s="8"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="1"/>
-    </row>
-    <row r="51" spans="1:5" ht="16.5">
+      <c r="D50" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E50" s="6"/>
+      <c r="F50" s="1"/>
+    </row>
+    <row r="51" spans="1:6" ht="16.5">
       <c r="A51" s="8"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="1"/>
-    </row>
-    <row r="52" spans="1:5" ht="16.5">
+      <c r="D51" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E51" s="6"/>
+      <c r="F51" s="1"/>
+    </row>
+    <row r="52" spans="1:6" ht="16.5">
       <c r="A52" s="8"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="1"/>
-    </row>
-    <row r="53" spans="1:5" ht="16.5">
+      <c r="D52" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E52" s="6"/>
+      <c r="F52" s="1"/>
+    </row>
+    <row r="53" spans="1:6" ht="16.5">
       <c r="A53" s="8"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="1"/>
+      <c r="D53" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E53" s="6"/>
+      <c r="F53" s="1"/>
     </row>
   </sheetData>
   <sortState ref="B8:C51">
@@ -2997,8 +3239,8 @@
   <mergeCells count="4">
     <mergeCell ref="A5:A8"/>
     <mergeCell ref="A9:A53"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B3:F3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\명찰\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\명찰\nametag-app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5BB23D5-BBD0-4040-9CEC-DA75388274AB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2246FFE7-0467-48B5-B9E5-8D1DCA2DA2EC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19290" windowHeight="9540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="281">
   <si>
     <t xml:space="preserve">러닝센터 명찰제작 양식 </t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -54,123 +54,18 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>강삼선</t>
-  </si>
-  <si>
-    <t>고철현</t>
-  </si>
-  <si>
-    <t>김선남</t>
-  </si>
-  <si>
-    <t>김세현</t>
-  </si>
-  <si>
-    <t>김영주</t>
-  </si>
-  <si>
-    <t>김유중</t>
-  </si>
-  <si>
-    <t>김재흥</t>
-  </si>
-  <si>
-    <t>김훈진</t>
-  </si>
-  <si>
-    <t>김휘재</t>
-  </si>
-  <si>
     <t>박민호</t>
   </si>
   <si>
-    <t>박석래</t>
-  </si>
-  <si>
-    <t>박성준</t>
-  </si>
-  <si>
-    <t>박세득</t>
-  </si>
-  <si>
-    <t>서동빈</t>
-  </si>
-  <si>
-    <t>서영익</t>
-  </si>
-  <si>
-    <t>소영호</t>
-  </si>
-  <si>
-    <t>안준현</t>
-  </si>
-  <si>
-    <t>양우식</t>
-  </si>
-  <si>
-    <t>오맹수</t>
-  </si>
-  <si>
-    <t>우순식</t>
-  </si>
-  <si>
-    <t>유민준</t>
-  </si>
-  <si>
-    <t>유현진</t>
-  </si>
-  <si>
-    <t>윤복수</t>
-  </si>
-  <si>
-    <t>이경호</t>
-  </si>
-  <si>
-    <t>이지부</t>
-  </si>
-  <si>
-    <t>정미라</t>
-  </si>
-  <si>
     <t>정성규</t>
   </si>
   <si>
-    <t>정지성</t>
-  </si>
-  <si>
-    <t>정진우</t>
-  </si>
-  <si>
     <t>정현철</t>
   </si>
   <si>
     <t>조봉희</t>
   </si>
   <si>
-    <t>조성준</t>
-  </si>
-  <si>
-    <t>최문진</t>
-  </si>
-  <si>
-    <t>최병환</t>
-  </si>
-  <si>
-    <t>최신용</t>
-  </si>
-  <si>
-    <t>최장환</t>
-  </si>
-  <si>
-    <t>한승배</t>
-  </si>
-  <si>
-    <t>허주영</t>
-  </si>
-  <si>
-    <t>허준행</t>
-  </si>
-  <si>
     <t>순천서비스센터</t>
   </si>
   <si>
@@ -201,21 +96,12 @@
     <t>강동서비스센터</t>
   </si>
   <si>
-    <t>밀양서비스센터</t>
-  </si>
-  <si>
     <t>관악서비스센터</t>
   </si>
   <si>
-    <t>문경서비스센터</t>
-  </si>
-  <si>
     <t>춘천서비스센터</t>
   </si>
   <si>
-    <t>청주서비스센터</t>
-  </si>
-  <si>
     <t>동탄서비스센터</t>
   </si>
   <si>
@@ -228,9 +114,6 @@
     <t>전주서비스센터</t>
   </si>
   <si>
-    <t>군산서비스센터</t>
-  </si>
-  <si>
     <t>원주서비스센터</t>
   </si>
   <si>
@@ -264,18 +147,12 @@
     <t>동대문서비스센터</t>
   </si>
   <si>
-    <t>영주서비스센터</t>
-  </si>
-  <si>
     <t>도봉서비스센터</t>
   </si>
   <si>
     <t>강남출장서비스센터</t>
   </si>
   <si>
-    <t>강북서비스센터</t>
-  </si>
-  <si>
     <t>북수원서비스센터</t>
   </si>
   <si>
@@ -289,30 +166,6 @@
   </si>
   <si>
     <t>고객가치혁신 인재육성</t>
-  </si>
-  <si>
-    <t>코멘토 포텐스닷</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김유호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>박경현</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>사외 강사</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>춘천서비스센터</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>박동현</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>X802901</t>
@@ -323,19 +176,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>25년 서비스센터 실장 
-데이터 역량 교육</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>선택 특강</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>3. 성과관리/ 피플 리더십</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>1. AI Tool을 활용한 서비스 문제해결 워크샵</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -344,82 +188,697 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>2. AI Tool을 활용한 서비스 문제해결 워크샵</t>
-  </si>
-  <si>
-    <t>3. 데이터 핸들링 기초 역량 업그레이드</t>
-  </si>
-  <si>
-    <t>4. 성과관리/ 피플 리더십</t>
-  </si>
-  <si>
-    <t>3. AI Tool을 활용한 서비스 문제해결 워크샵</t>
-  </si>
-  <si>
-    <t>4. 데이터 핸들링 기초 역량 업그레이드</t>
-  </si>
-  <si>
-    <t>5. 성과관리/ 피플 리더십</t>
-  </si>
-  <si>
-    <t>4. AI Tool을 활용한 서비스 문제해결 워크샵</t>
-  </si>
-  <si>
-    <t>5. 데이터 핸들링 기초 역량 업그레이드</t>
-  </si>
-  <si>
-    <t>6. 성과관리/ 피플 리더십</t>
-  </si>
-  <si>
-    <t>5. AI Tool을 활용한 서비스 문제해결 워크샵</t>
-  </si>
-  <si>
-    <t>6. 데이터 핸들링 기초 역량 업그레이드</t>
-  </si>
-  <si>
-    <t>7. 성과관리/ 피플 리더십</t>
-  </si>
-  <si>
-    <t>6. AI Tool을 활용한 서비스 문제해결 워크샵</t>
-  </si>
-  <si>
-    <t>7. 데이터 핸들링 기초 역량 업그레이드</t>
-  </si>
-  <si>
-    <t>8. 성과관리/ 피플 리더십</t>
-  </si>
-  <si>
-    <t>7. AI Tool을 활용한 서비스 문제해결 워크샵</t>
-  </si>
-  <si>
-    <t>8. 데이터 핸들링 기초 역량 업그레이드</t>
-  </si>
-  <si>
-    <t>9. 성과관리/ 피플 리더십</t>
-  </si>
-  <si>
-    <t>8. AI Tool을 활용한 서비스 문제해결 워크샵</t>
-  </si>
-  <si>
-    <t>9. 데이터 핸들링 기초 역량 업그레이드</t>
-  </si>
-  <si>
-    <t>10. 성과관리/ 피플 리더십</t>
-  </si>
-  <si>
-    <t>9. AI Tool을 활용한 서비스 문제해결 워크샵</t>
-  </si>
-  <si>
-    <t>10. 데이터 핸들링 기초 역량 업그레이드</t>
-  </si>
-  <si>
-    <t>11. 성과관리/ 피플 리더십</t>
-  </si>
-  <si>
-    <t>10. AI Tool을 활용한 서비스 문제해결 워크샵</t>
-  </si>
-  <si>
-    <t>11. 데이터 핸들링 기초 역량 업그레이드</t>
+    <t>송병천</t>
+  </si>
+  <si>
+    <t>문유환</t>
+  </si>
+  <si>
+    <t>이준희</t>
+  </si>
+  <si>
+    <t>박진수</t>
+  </si>
+  <si>
+    <t>손정남</t>
+  </si>
+  <si>
+    <t>김병준</t>
+  </si>
+  <si>
+    <t>윤영진</t>
+  </si>
+  <si>
+    <t>박찬문</t>
+  </si>
+  <si>
+    <t>황재영</t>
+  </si>
+  <si>
+    <t>권순양</t>
+  </si>
+  <si>
+    <t>박지수</t>
+  </si>
+  <si>
+    <t>이태한</t>
+  </si>
+  <si>
+    <t>이승현</t>
+  </si>
+  <si>
+    <t>박승우</t>
+  </si>
+  <si>
+    <t>박기영</t>
+  </si>
+  <si>
+    <t>정연일</t>
+  </si>
+  <si>
+    <t>정수곤</t>
+  </si>
+  <si>
+    <t>박정빈</t>
+  </si>
+  <si>
+    <t>서현규</t>
+  </si>
+  <si>
+    <t>김상우</t>
+  </si>
+  <si>
+    <t>이상기</t>
+  </si>
+  <si>
+    <t>전명수</t>
+  </si>
+  <si>
+    <t>최승연</t>
+  </si>
+  <si>
+    <t>조훈래</t>
+  </si>
+  <si>
+    <t>정관중</t>
+  </si>
+  <si>
+    <t>한관수</t>
+  </si>
+  <si>
+    <t>곽동명</t>
+  </si>
+  <si>
+    <t>신현호</t>
+  </si>
+  <si>
+    <t>오흥철</t>
+  </si>
+  <si>
+    <t>한승용</t>
+  </si>
+  <si>
+    <t>한대식</t>
+  </si>
+  <si>
+    <t>김민우</t>
+  </si>
+  <si>
+    <t>이기모</t>
+  </si>
+  <si>
+    <t>심용석</t>
+  </si>
+  <si>
+    <t>홍상연</t>
+  </si>
+  <si>
+    <t>정범철</t>
+  </si>
+  <si>
+    <t>한영호</t>
+  </si>
+  <si>
+    <t>송승헌</t>
+  </si>
+  <si>
+    <t>윤치운</t>
+  </si>
+  <si>
+    <t>정진호</t>
+  </si>
+  <si>
+    <t>김재원</t>
+  </si>
+  <si>
+    <t>김권영</t>
+  </si>
+  <si>
+    <t>김범룡</t>
+  </si>
+  <si>
+    <t>박우경</t>
+  </si>
+  <si>
+    <t>한의진</t>
+  </si>
+  <si>
+    <t>임호성</t>
+  </si>
+  <si>
+    <t>조경원</t>
+  </si>
+  <si>
+    <t>김수훈</t>
+  </si>
+  <si>
+    <t>김상신</t>
+  </si>
+  <si>
+    <t>강상봉</t>
+  </si>
+  <si>
+    <t>최건영</t>
+  </si>
+  <si>
+    <t>신길재</t>
+  </si>
+  <si>
+    <t>김영우</t>
+  </si>
+  <si>
+    <t>홍성민</t>
+  </si>
+  <si>
+    <t>김명호</t>
+  </si>
+  <si>
+    <t>김인성</t>
+  </si>
+  <si>
+    <t>김장수</t>
+  </si>
+  <si>
+    <t>강수호</t>
+  </si>
+  <si>
+    <t>박진영</t>
+  </si>
+  <si>
+    <t>백종엽</t>
+  </si>
+  <si>
+    <t>손상범</t>
+  </si>
+  <si>
+    <t>김솔이</t>
+  </si>
+  <si>
+    <t>이동우</t>
+  </si>
+  <si>
+    <t>박창호</t>
+  </si>
+  <si>
+    <t>이성민</t>
+  </si>
+  <si>
+    <t>박선민</t>
+  </si>
+  <si>
+    <t>권혁민</t>
+  </si>
+  <si>
+    <t>김한승</t>
+  </si>
+  <si>
+    <t>이창진</t>
+  </si>
+  <si>
+    <t>강준수</t>
+  </si>
+  <si>
+    <t>김태현</t>
+  </si>
+  <si>
+    <t>유보선</t>
+  </si>
+  <si>
+    <t>이태우</t>
+  </si>
+  <si>
+    <t>이동수</t>
+  </si>
+  <si>
+    <t>윤명하</t>
+  </si>
+  <si>
+    <t>이덕만</t>
+  </si>
+  <si>
+    <t>이은경</t>
+  </si>
+  <si>
+    <t>염수일</t>
+  </si>
+  <si>
+    <t>김호량</t>
+  </si>
+  <si>
+    <t>송종우</t>
+  </si>
+  <si>
+    <t>손준우</t>
+  </si>
+  <si>
+    <t>안혜성</t>
+  </si>
+  <si>
+    <t>정혜림</t>
+  </si>
+  <si>
+    <t>강동원</t>
+  </si>
+  <si>
+    <t>2026-05-21 ~ 22</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>경산서비스센터</t>
+  </si>
+  <si>
+    <t>광산서비스센터</t>
+  </si>
+  <si>
+    <t>광진서비스센터</t>
+  </si>
+  <si>
+    <t>구미서비스센터</t>
+  </si>
+  <si>
+    <t>김포서비스센터</t>
+  </si>
+  <si>
+    <t>남부역량지원계</t>
+  </si>
+  <si>
+    <t>남수원서비스센터</t>
+  </si>
+  <si>
+    <t>남울산서비스센터</t>
+  </si>
+  <si>
+    <t>남청주서비스센터</t>
+  </si>
+  <si>
+    <t>대치서비스센터</t>
+  </si>
+  <si>
+    <t>덕천서비스센터</t>
+  </si>
+  <si>
+    <t>동대구서비스센터</t>
+  </si>
+  <si>
+    <t>동래서비스센터</t>
+  </si>
+  <si>
+    <t>마산서비스센터</t>
+  </si>
+  <si>
+    <t>부천서비스센터</t>
+  </si>
+  <si>
+    <t>북울산서비스센터</t>
+  </si>
+  <si>
+    <t>북인천서비스센터</t>
+  </si>
+  <si>
+    <t>서광주서비스센터</t>
+  </si>
+  <si>
+    <t>서귀포서비스센터</t>
+  </si>
+  <si>
+    <t>서대구서비스센터</t>
+  </si>
+  <si>
+    <t>서대전서비스센터</t>
+  </si>
+  <si>
+    <t>서면서비스센터</t>
+  </si>
+  <si>
+    <t>서부역량강화팀</t>
+  </si>
+  <si>
+    <t>서안산서비스센터</t>
+  </si>
+  <si>
+    <t>서초서비스센터</t>
+  </si>
+  <si>
+    <t>세종서비스센터</t>
+  </si>
+  <si>
+    <t>속초서비스센터</t>
+  </si>
+  <si>
+    <t>수도권역량지원계</t>
+  </si>
+  <si>
+    <t>아산서비스센터</t>
+  </si>
+  <si>
+    <t>양산서비스센터</t>
+  </si>
+  <si>
+    <t>양천서비스센터</t>
+  </si>
+  <si>
+    <t>오산서비스센터</t>
+  </si>
+  <si>
+    <t>용인출장서비스센터</t>
+  </si>
+  <si>
+    <t>의왕서비스센터</t>
+  </si>
+  <si>
+    <t>의정부서비스센터</t>
+  </si>
+  <si>
+    <t>이천서비스센터</t>
+  </si>
+  <si>
+    <t>일산서비스센터</t>
+  </si>
+  <si>
+    <t>진주서비스센터</t>
+  </si>
+  <si>
+    <t>창원서비스센터</t>
+  </si>
+  <si>
+    <t>충무로역서비스센터</t>
+  </si>
+  <si>
+    <t>태백서비스센터</t>
+  </si>
+  <si>
+    <t>파주서비스센터</t>
+  </si>
+  <si>
+    <t>포항서비스센터</t>
+  </si>
+  <si>
+    <t>프리미엄케어서비스센터</t>
+  </si>
+  <si>
+    <t>해외CC&amp;S역량개발팀</t>
+  </si>
+  <si>
+    <t>홍대역서비스센터</t>
+  </si>
+  <si>
+    <t>홍성서비스센터</t>
+  </si>
+  <si>
+    <t>대연서비스센터</t>
+  </si>
+  <si>
+    <t>남동서비스센터</t>
+  </si>
+  <si>
+    <t>남양주서비스센터</t>
+  </si>
+  <si>
+    <t>용산서비스센터</t>
+  </si>
+  <si>
+    <t>하남서비스센터</t>
+  </si>
+  <si>
+    <t>동해서비스센터</t>
+  </si>
+  <si>
+    <t>홍성길</t>
+  </si>
+  <si>
+    <t>김은기</t>
+  </si>
+  <si>
+    <t>최종근</t>
+  </si>
+  <si>
+    <t>심경훈</t>
+  </si>
+  <si>
+    <t>서상혁</t>
+  </si>
+  <si>
+    <t>이춘훈</t>
+  </si>
+  <si>
+    <t>현두용</t>
+  </si>
+  <si>
+    <t>심세윤</t>
+  </si>
+  <si>
+    <t>이창혁</t>
+  </si>
+  <si>
+    <t>김민섭</t>
+  </si>
+  <si>
+    <t>이민호</t>
+  </si>
+  <si>
+    <t>박찬석</t>
+  </si>
+  <si>
+    <t>장영목</t>
+  </si>
+  <si>
+    <t>나영민</t>
+  </si>
+  <si>
+    <t>도성준</t>
+  </si>
+  <si>
+    <t>박치원</t>
+  </si>
+  <si>
+    <t>권혁</t>
+  </si>
+  <si>
+    <t>이철호</t>
+  </si>
+  <si>
+    <t>이경훈</t>
+  </si>
+  <si>
+    <t>장대원</t>
+  </si>
+  <si>
+    <t>김기현</t>
+  </si>
+  <si>
+    <t>김효림</t>
+  </si>
+  <si>
+    <t>서영식</t>
+  </si>
+  <si>
+    <t>오원규</t>
+  </si>
+  <si>
+    <t>오진석</t>
+  </si>
+  <si>
+    <t>방설빈</t>
+  </si>
+  <si>
+    <t>안홍기</t>
+  </si>
+  <si>
+    <t>정재욱</t>
+  </si>
+  <si>
+    <t>홍경주</t>
+  </si>
+  <si>
+    <t>윤경찬</t>
+  </si>
+  <si>
+    <t>박정민</t>
+  </si>
+  <si>
+    <t>박지호</t>
+  </si>
+  <si>
+    <t>최기성</t>
+  </si>
+  <si>
+    <t>문종민</t>
+  </si>
+  <si>
+    <t>박경배</t>
+  </si>
+  <si>
+    <t>김승환</t>
+  </si>
+  <si>
+    <t>조덕희</t>
+  </si>
+  <si>
+    <t>권기만</t>
+  </si>
+  <si>
+    <t>김호영</t>
+  </si>
+  <si>
+    <t>김대현</t>
+  </si>
+  <si>
+    <t>정필완</t>
+  </si>
+  <si>
+    <t>엄영섭</t>
+  </si>
+  <si>
+    <t>김성원</t>
+  </si>
+  <si>
+    <t>김남덕</t>
+  </si>
+  <si>
+    <t>박재홍</t>
+  </si>
+  <si>
+    <t>오종택</t>
+  </si>
+  <si>
+    <t>양광복</t>
+  </si>
+  <si>
+    <t>이기춘</t>
+  </si>
+  <si>
+    <t>고창진</t>
+  </si>
+  <si>
+    <t>안희진</t>
+  </si>
+  <si>
+    <t>홍희진</t>
+  </si>
+  <si>
+    <t>강호성</t>
+  </si>
+  <si>
+    <t>최영진</t>
+  </si>
+  <si>
+    <t>최왕경</t>
+  </si>
+  <si>
+    <t>김영길</t>
+  </si>
+  <si>
+    <t>이춘재</t>
+  </si>
+  <si>
+    <t>송민규</t>
+  </si>
+  <si>
+    <t>김보성</t>
+  </si>
+  <si>
+    <t>한광일</t>
+  </si>
+  <si>
+    <t>현기혁</t>
+  </si>
+  <si>
+    <t>전종학</t>
+  </si>
+  <si>
+    <t>장인석</t>
+  </si>
+  <si>
+    <t>김황일</t>
+  </si>
+  <si>
+    <t>양서원</t>
+  </si>
+  <si>
+    <t>장경신</t>
+  </si>
+  <si>
+    <t>박영민</t>
+  </si>
+  <si>
+    <t>이민규</t>
+  </si>
+  <si>
+    <t>배극봉</t>
+  </si>
+  <si>
+    <t>CC&amp;S기술솔루션팀</t>
+  </si>
+  <si>
+    <t>강릉서비스센터</t>
+  </si>
+  <si>
+    <t>거제서비스센터</t>
+  </si>
+  <si>
+    <t>경주서비스센터</t>
+  </si>
+  <si>
+    <t>고객가치혁신한국충청실</t>
+  </si>
+  <si>
+    <t>김천서비스센터</t>
+  </si>
+  <si>
+    <t>김해서비스센터</t>
+  </si>
+  <si>
+    <t>남대구서비스센터</t>
+  </si>
+  <si>
+    <t>동대전서비스센터</t>
+  </si>
+  <si>
+    <t>목포서비스센터</t>
+  </si>
+  <si>
+    <t>사하서비스센터</t>
+  </si>
+  <si>
+    <t>수리자문계</t>
+  </si>
+  <si>
+    <t>안동서비스센터</t>
+  </si>
+  <si>
+    <t>여수서비스센터</t>
+  </si>
+  <si>
+    <t>재무지원_3반</t>
+  </si>
+  <si>
+    <t>제주서비스센터</t>
+  </si>
+  <si>
+    <t>죽전서비스센터</t>
+  </si>
+  <si>
+    <t>해남서비스센터</t>
+  </si>
+  <si>
+    <t>해운대서비스센터</t>
+  </si>
+  <si>
+    <t>커뮤니케이션역량개발팀</t>
+  </si>
+  <si>
+    <t>1. AI Tool을 활용한 서비스 문제해결 워크샵</t>
+  </si>
+  <si>
+    <t>3. 성과관리/ 피플 리더십</t>
+  </si>
+  <si>
+    <t>2. 데이터 핸들링 기초 역량 업그레이드</t>
+  </si>
+  <si>
+    <t>26년 서비스 핵심인재(JLP/SLP) 
+Pool-Stay 구성원 대상 교육</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -716,7 +1175,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -914,12 +1373,6 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="13">
     <border>
@@ -1721,7 +2174,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1731,9 +2184,6 @@
     <xf numFmtId="41" fontId="6" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="36" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1753,10 +2203,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="238">
@@ -2333,912 +2783,3234 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:F53"/>
+  <dimension ref="A2:F210"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="15.77734375" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" customWidth="1"/>
+    <col min="4" max="4" width="50.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="15.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:6" ht="20.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
     </row>
     <row r="3" spans="1:6" ht="54" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+    </row>
+    <row r="4" spans="1:6" ht="16.5">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="16.5" customHeight="1">
+      <c r="A5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" ht="16.5" customHeight="1">
+      <c r="A6" s="7"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6"/>
+    </row>
+    <row r="7" spans="1:6" ht="16.5" customHeight="1">
+      <c r="A7" s="7"/>
+      <c r="B7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F7" s="6">
+        <v>318537</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="16.5">
+      <c r="A8" s="7"/>
+      <c r="B8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A9" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E9" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F9" s="1">
+        <v>288202</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="16.5">
+      <c r="A10" s="7"/>
+      <c r="B10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E10" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F10" s="1">
+        <v>292081</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="16.5">
+      <c r="A11" s="7"/>
+      <c r="B11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E11" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F11" s="1">
+        <v>294132</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="16.5">
+      <c r="A12" s="7"/>
+      <c r="B12" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E12" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F12" s="1">
+        <v>292887</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="16.5">
+      <c r="A13" s="7"/>
+      <c r="B13" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="E13" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F13" s="1">
+        <v>288903</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="16.5">
+      <c r="A14" s="7"/>
+      <c r="B14" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E14" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F14" s="1">
+        <v>292985</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="16.5">
+      <c r="A15" s="7"/>
+      <c r="B15" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E15" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F15" s="1">
+        <v>292154</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="16.5">
+      <c r="A16" s="7"/>
+      <c r="B16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F16" s="1">
+        <v>288884</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="16.5">
+      <c r="A17" s="7"/>
+      <c r="B17" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E17" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F17" s="1">
+        <v>289026</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="16.5">
+      <c r="A18" s="7"/>
+      <c r="B18" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="E18" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F18" s="1">
+        <v>289046</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="16.5">
+      <c r="A19" s="7"/>
+      <c r="B19" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="E19" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F19" s="1">
+        <v>291755</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="16.5">
+      <c r="A20" s="7"/>
+      <c r="B20" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E20" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F20" s="1">
+        <v>288252</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="16.5">
+      <c r="A21" s="7"/>
+      <c r="B21" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E21" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F21" s="1">
+        <v>288752</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="16.5">
+      <c r="A22" s="7"/>
+      <c r="B22" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E22" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F22" s="1">
+        <v>288383</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="16.5">
+      <c r="A23" s="7"/>
+      <c r="B23" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="E23" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F23" s="1">
+        <v>288685</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="16.5">
+      <c r="A24" s="7"/>
+      <c r="B24" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F24" s="1">
+        <v>288602</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="16.5">
+      <c r="A25" s="7"/>
+      <c r="B25" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E25" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F25" s="1">
+        <v>288771</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="16.5">
+      <c r="A26" s="7"/>
+      <c r="B26" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E26" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F26" s="1">
+        <v>288390</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="16.5">
+      <c r="A27" s="7"/>
+      <c r="B27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E27" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F27" s="1">
+        <v>288195</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="16.5">
+      <c r="A28" s="7"/>
+      <c r="B28" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="E28" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F28" s="1">
+        <v>288328</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="16.5">
+      <c r="A29" s="7"/>
+      <c r="B29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E29" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F29" s="1">
+        <v>288940</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="16.5">
+      <c r="A30" s="7"/>
+      <c r="B30" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E30" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F30" s="1">
+        <v>292197</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="16.5">
+      <c r="A31" s="7"/>
+      <c r="B31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" s="1"/>
+      <c r="E31" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F31" s="1">
+        <v>294169</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="16.5">
+      <c r="A32" s="7"/>
+      <c r="B32" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E32" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F32" s="1">
+        <v>291962</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="16.5">
+      <c r="A33" s="7"/>
+      <c r="B33" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="E33" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F33" s="1">
+        <v>288985</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="16.5">
+      <c r="A34" s="7"/>
+      <c r="B34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" s="1"/>
+      <c r="E34" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F34" s="1">
+        <v>293266</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="16.5">
+      <c r="A35" s="7"/>
+      <c r="B35" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E35" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F35" s="1">
+        <v>288810</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="16.5">
+      <c r="A36" s="7"/>
+      <c r="B36" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E36" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F36" s="1">
+        <v>291798</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="16.5">
+      <c r="A37" s="7"/>
+      <c r="B37" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E37" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F37" s="1">
+        <v>288562</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="16.5">
+      <c r="A38" s="7"/>
+      <c r="B38" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="E38" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F38" s="1">
+        <v>289019</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="16.5">
+      <c r="A39" s="7"/>
+      <c r="B39" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E39" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F39" s="1">
+        <v>291999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="16.5">
+      <c r="A40" s="7"/>
+      <c r="B40" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E40" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F40" s="1">
+        <v>292050</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="16.5">
+      <c r="A41" s="7"/>
+      <c r="B41" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E41" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F41" s="1">
+        <v>294122</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="16.5">
+      <c r="A42" s="7"/>
+      <c r="B42" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E42" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F42" s="1">
+        <v>291802</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="16.5">
+      <c r="A43" s="7"/>
+      <c r="B43" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D43" s="6"/>
+      <c r="E43" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F43" s="1">
+        <v>288478</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="16.5">
+      <c r="A44" s="7"/>
+      <c r="B44" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E44" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F44" s="1">
+        <v>291939</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="16.5">
+      <c r="A45" s="7"/>
+      <c r="B45" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E45" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F45" s="1">
+        <v>288622</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="16.5">
+      <c r="A46" s="7"/>
+      <c r="B46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D46" s="1"/>
+      <c r="E46" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F46" s="1">
+        <v>288712</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="16.5">
+      <c r="A47" s="7"/>
+      <c r="B47" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E47" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F47" s="1">
+        <v>288417</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="16.5">
+      <c r="A48" s="7"/>
+      <c r="B48" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D48" s="6"/>
+      <c r="E48" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F48" s="1">
+        <v>292211</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="16.5">
+      <c r="A49" s="7"/>
+      <c r="B49" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E49" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F49" s="1">
+        <v>289099</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="16.5">
+      <c r="A50" s="7"/>
+      <c r="B50" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E50" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F50" s="1">
+        <v>288493</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="16.5">
+      <c r="A51" s="7"/>
+      <c r="B51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E51" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F51" s="1">
+        <v>289069</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="16.5">
+      <c r="A52" s="7"/>
+      <c r="B52" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E52" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F52" s="1">
+        <v>293279</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="16.5">
+      <c r="A53" s="7"/>
+      <c r="B53" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-    </row>
-    <row r="4" spans="1:6" ht="16.5">
-      <c r="A4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="D53" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="E53" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F53" s="1">
+        <v>288472</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="16.5">
+      <c r="A54" s="7"/>
+      <c r="B54" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A5" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A6" s="8"/>
-      <c r="B6" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A7" s="8"/>
-      <c r="B7" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="D54" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E54" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F54" s="1">
+        <v>291911</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="16.5">
+      <c r="A55" s="7"/>
+      <c r="B55" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D55" s="1"/>
+      <c r="E55" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F55" s="1">
+        <v>288997</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="16.5">
+      <c r="A56" s="7"/>
+      <c r="B56" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E7" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F7" s="7">
-        <v>318537</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="16.5">
-      <c r="A8" s="8"/>
-      <c r="B8" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" s="7" t="s">
+      <c r="D56" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E56" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F56" s="1">
+        <v>288828</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="16.5">
+      <c r="A57" s="7"/>
+      <c r="B57" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E8" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1">
-      <c r="A9" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="D57" s="1"/>
+      <c r="E57" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F57" s="1">
+        <v>289074</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="16.5">
+      <c r="A58" s="7"/>
+      <c r="B58" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="E58" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F58" s="1">
+        <v>292018</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="16.5">
+      <c r="A59" s="7"/>
+      <c r="B59" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D59" s="1"/>
+      <c r="E59" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F59" s="1">
+        <v>288615</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="16.5">
+      <c r="A60" s="7"/>
+      <c r="B60" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D60" s="1"/>
+      <c r="E60" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F60" s="1">
+        <v>288716</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="16.5">
+      <c r="A61" s="7"/>
+      <c r="B61" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E61" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F61" s="1">
+        <v>288342</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="16.5">
+      <c r="A62" s="7"/>
+      <c r="B62" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D62" s="1"/>
+      <c r="E62" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F62" s="1">
+        <v>288799</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="16.5">
+      <c r="A63" s="7"/>
+      <c r="B63" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="E63" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F63" s="1">
+        <v>294053</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="16.5">
+      <c r="A64" s="7"/>
+      <c r="B64" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E64" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F64" s="1">
+        <v>288839</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="16.5">
+      <c r="A65" s="7"/>
+      <c r="B65" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E65" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F65" s="1">
+        <v>288841</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="16.5">
+      <c r="A66" s="7"/>
+      <c r="B66" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E66" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F66" s="1">
+        <v>288803</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="16.5">
+      <c r="A67" s="7"/>
+      <c r="B67" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E67" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F67" s="1">
+        <v>288883</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="16.5">
+      <c r="A68" s="7"/>
+      <c r="B68" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="E68" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F68" s="1">
+        <v>291769</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="16.5">
+      <c r="A69" s="7"/>
+      <c r="B69" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E69" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F69" s="1">
+        <v>310164</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="16.5">
+      <c r="A70" s="7"/>
+      <c r="B70" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E70" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F70" s="1">
+        <v>289079</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="16.5">
+      <c r="A71" s="7"/>
+      <c r="B71" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D71" s="1"/>
+      <c r="E71" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F71" s="1">
+        <v>288227</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="16.5">
+      <c r="A72" s="7"/>
+      <c r="B72" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D72" s="1"/>
+      <c r="E72" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F72" s="1">
+        <v>288885</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="16.5">
+      <c r="A73" s="7"/>
+      <c r="B73" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E73" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F73" s="1">
+        <v>288945</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="16.5">
+      <c r="A74" s="7"/>
+      <c r="B74" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E74" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F74" s="1">
+        <v>291739</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="16.5">
+      <c r="A75" s="7"/>
+      <c r="B75" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E75" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F75" s="1">
+        <v>289050</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="16.5">
+      <c r="A76" s="7"/>
+      <c r="B76" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="E76" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F76" s="1">
+        <v>288676</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="16.5">
+      <c r="A77" s="7"/>
+      <c r="B77" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E77" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F77" s="1">
+        <v>291894</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="16.5">
+      <c r="A78" s="7"/>
+      <c r="B78" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E78" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F78" s="1">
+        <v>292819</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="16.5">
+      <c r="A79" s="7"/>
+      <c r="B79" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D79" s="1"/>
+      <c r="E79" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F79" s="1">
+        <v>289000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="16.5">
+      <c r="A80" s="7"/>
+      <c r="B80" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E80" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F80" s="1">
+        <v>288673</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="16.5">
+      <c r="A81" s="7"/>
+      <c r="B81" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="E81" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F81" s="1">
+        <v>288409</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="16.5">
+      <c r="A82" s="7"/>
+      <c r="B82" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E82" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F82" s="1">
+        <v>292746</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="16.5">
+      <c r="A83" s="7"/>
+      <c r="B83" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D83" s="1"/>
+      <c r="E83" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F83" s="1">
+        <v>292381</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="16.5">
+      <c r="A84" s="7"/>
+      <c r="B84" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E84" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F84" s="1">
+        <v>292552</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="16.5">
+      <c r="A85" s="7"/>
+      <c r="B85" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E85" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F85" s="1">
+        <v>292937</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="16.5">
+      <c r="A86" s="7"/>
+      <c r="B86" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D86" s="6"/>
+      <c r="E86" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F86" s="1">
+        <v>292568</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="16.5">
+      <c r="A87" s="7"/>
+      <c r="B87" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D87" s="1"/>
+      <c r="E87" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F87" s="1">
+        <v>292135</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="16.5">
+      <c r="A88" s="7"/>
+      <c r="B88" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E88" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F88" s="1">
+        <v>292670</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="16.5">
+      <c r="A89" s="7"/>
+      <c r="B89" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E89" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F89" s="1">
+        <v>292124</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="16.5">
+      <c r="A90" s="7"/>
+      <c r="B90" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D90" s="1"/>
+      <c r="E90" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F90" s="1">
+        <v>291784</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="16.5">
+      <c r="A91" s="7"/>
+      <c r="B91" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="E91" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F91" s="1">
+        <v>292964</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="16.5">
+      <c r="A92" s="7"/>
+      <c r="B92" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E92" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F92" s="1">
+        <v>292597</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="16.5">
+      <c r="A93" s="7"/>
+      <c r="B93" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E93" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F93" s="1">
+        <v>289029</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="16.5">
+      <c r="A94" s="7"/>
+      <c r="B94" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E94" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F94" s="1">
+        <v>293118</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="16.5">
+      <c r="A95" s="7"/>
+      <c r="B95" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D95" s="1"/>
+      <c r="E95" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F95" s="1">
+        <v>292302</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="16.5">
+      <c r="A96" s="7"/>
+      <c r="B96" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D96" s="6"/>
+      <c r="E96" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F96" s="1">
+        <v>292612</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="16.5">
+      <c r="A97" s="7"/>
+      <c r="B97" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E97" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F97" s="1">
+        <v>291800</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="16.5">
+      <c r="A98" s="7"/>
+      <c r="B98" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D98" s="1"/>
+      <c r="E98" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F98" s="1">
+        <v>293793</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="16.5">
+      <c r="A99" s="7"/>
+      <c r="B99" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E99" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F99" s="1">
+        <v>292579</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="16.5">
+      <c r="A100" s="7"/>
+      <c r="B100" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E100" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F100" s="1">
+        <v>292246</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="16.5">
+      <c r="A101" s="7"/>
+      <c r="B101" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="E101" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F101" s="1">
+        <v>294098</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="16.5">
+      <c r="A102" s="7"/>
+      <c r="B102" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E102" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F102" s="1">
+        <v>292744</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="16.5">
+      <c r="A103" s="7"/>
+      <c r="B103" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E103" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F103" s="1">
+        <v>289068</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="16.5">
+      <c r="A104" s="7"/>
+      <c r="B104" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E104" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F104" s="1">
+        <v>292848</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="16.5">
+      <c r="A105" s="7"/>
+      <c r="B105" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E105" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F105" s="1">
+        <v>292104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="16.5">
+      <c r="A106" s="7"/>
+      <c r="B106" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E106" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F106" s="1">
+        <v>291920</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="16.5">
+      <c r="A107" s="7"/>
+      <c r="B107" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E107" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F107" s="1">
+        <v>289127</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="16.5">
+      <c r="A108" s="7"/>
+      <c r="B108" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E108" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F108" s="1">
+        <v>289137</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="16.5">
+      <c r="A109" s="7"/>
+      <c r="B109" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D109" s="6"/>
+      <c r="E109" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F109" s="1">
+        <v>275950</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="16.5">
+      <c r="A110" s="7"/>
+      <c r="B110" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E110" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F110" s="1">
+        <v>292464</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="16.5">
+      <c r="A111" s="7"/>
+      <c r="B111" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E111" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F111" s="1">
+        <v>292577</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="16.5">
+      <c r="A112" s="7"/>
+      <c r="B112" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E112" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F112" s="1">
+        <v>292556</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="16.5">
+      <c r="A113" s="7"/>
+      <c r="B113" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E113" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F113" s="1">
+        <v>291916</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="16.5">
+      <c r="A114" s="7"/>
+      <c r="B114" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="E114" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F114" s="1">
+        <v>292467</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="16.5">
+      <c r="A115" s="7"/>
+      <c r="B115" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E115" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F115" s="1">
+        <v>292671</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="16.5">
+      <c r="A116" s="7"/>
+      <c r="B116" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E116" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F116" s="1">
+        <v>293006</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="16.5">
+      <c r="A117" s="7"/>
+      <c r="B117" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E117" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F117" s="1">
+        <v>288561</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="16.5">
+      <c r="A118" s="7"/>
+      <c r="B118" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E118" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F118" s="1">
+        <v>288927</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="16.5">
+      <c r="A119" s="7"/>
+      <c r="B119" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="E119" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F119" s="1">
+        <v>288189</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="16.5">
+      <c r="A120" s="7"/>
+      <c r="B120" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E120" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F120" s="1">
+        <v>293067</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="16.5">
+      <c r="A121" s="7"/>
+      <c r="B121" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D121" s="1"/>
+      <c r="E121" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F121" s="1">
+        <v>292976</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="16.5">
+      <c r="A122" s="7"/>
+      <c r="B122" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E122" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F122" s="1">
+        <v>292622</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="16.5">
+      <c r="A123" s="7"/>
+      <c r="B123" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E123" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F123" s="1">
+        <v>292151</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="16.5">
+      <c r="A124" s="7"/>
+      <c r="B124" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C124" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E9" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F9" s="1">
-        <v>293575</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="16.5">
-      <c r="A10" s="8"/>
-      <c r="B10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="D124" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="E124" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F124" s="1">
+        <v>288076</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="16.5">
+      <c r="A125" s="7"/>
+      <c r="B125" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E125" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F125" s="1">
+        <v>292101</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="16.5">
+      <c r="A126" s="7"/>
+      <c r="B126" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E126" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F126" s="1">
+        <v>292337</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="16.5">
+      <c r="A127" s="7"/>
+      <c r="B127" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E127" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F127" s="1">
+        <v>288287</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="16.5">
+      <c r="A128" s="7"/>
+      <c r="B128" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E128" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F128" s="1">
+        <v>292957</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="16.5">
+      <c r="A129" s="7"/>
+      <c r="B129" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="E129" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F129" s="1">
+        <v>292321</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="16.5">
+      <c r="A130" s="7"/>
+      <c r="B130" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E130" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F130" s="1">
+        <v>288341</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="16.5">
+      <c r="A131" s="7"/>
+      <c r="B131" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D131" s="1"/>
+      <c r="E131" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F131" s="1">
+        <v>293572</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="16.5">
+      <c r="A132" s="7"/>
+      <c r="B132" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E132" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F132" s="1">
+        <v>292258</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="16.5">
+      <c r="A133" s="7"/>
+      <c r="B133" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C133" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E10" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F10" s="1">
-        <v>294004</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="16.5">
-      <c r="A11" s="8"/>
-      <c r="B11" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="D133" s="1"/>
+      <c r="E133" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F133" s="1">
+        <v>292763</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="16.5">
+      <c r="A134" s="7"/>
+      <c r="B134" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="E134" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F134" s="1">
+        <v>293450</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" ht="16.5">
+      <c r="A135" s="7"/>
+      <c r="B135" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E135" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F135" s="1">
+        <v>288496</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="16.5">
+      <c r="A136" s="7"/>
+      <c r="B136" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E136" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F136" s="1">
+        <v>293071</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="16.5">
+      <c r="A137" s="7"/>
+      <c r="B137" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E137" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F137" s="1">
+        <v>292711</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="16.5">
+      <c r="A138" s="7"/>
+      <c r="B138" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E138" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F138" s="1">
+        <v>292946</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" ht="16.5">
+      <c r="A139" s="7"/>
+      <c r="B139" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E139" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F139" s="1">
+        <v>292037</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" ht="16.5">
+      <c r="A140" s="7"/>
+      <c r="B140" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E140" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F140" s="1">
+        <v>292513</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" ht="16.5">
+      <c r="A141" s="7"/>
+      <c r="B141" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E141" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F141" s="1">
+        <v>291821</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="16.5">
+      <c r="A142" s="7"/>
+      <c r="B142" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="E142" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F142" s="1">
+        <v>292843</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="16.5">
+      <c r="A143" s="7"/>
+      <c r="B143" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E143" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F143" s="1">
+        <v>292997</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" ht="16.5">
+      <c r="A144" s="7"/>
+      <c r="B144" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C144" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E11" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F11" s="1">
-        <v>292052</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="16.5">
-      <c r="A12" s="8"/>
-      <c r="B12" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E12" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F12" s="1">
-        <v>292052</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="16.5">
-      <c r="A13" s="8"/>
-      <c r="B13" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E13" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F13" s="1">
-        <v>293976</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="16.5">
-      <c r="A14" s="8"/>
-      <c r="B14" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E14" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F14" s="1">
-        <v>289090</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="16.5">
-      <c r="A15" s="8"/>
-      <c r="B15" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="D144" s="1"/>
+      <c r="E144" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F144" s="1">
+        <v>293463</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" ht="16.5">
+      <c r="A145" s="7"/>
+      <c r="B145" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E145" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F145" s="1">
+        <v>288644</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" ht="16.5">
+      <c r="A146" s="7"/>
+      <c r="B146" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E146" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F146" s="1">
+        <v>291806</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" ht="16.5">
+      <c r="A147" s="7"/>
+      <c r="B147" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="E147" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F147" s="1">
+        <v>293391</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" ht="16.5">
+      <c r="A148" s="7"/>
+      <c r="B148" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D148" s="1"/>
+      <c r="E148" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F148" s="1">
+        <v>291924</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" ht="16.5">
+      <c r="A149" s="7"/>
+      <c r="B149" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D149" s="1"/>
+      <c r="E149" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F149" s="1">
+        <v>292227</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" ht="16.5">
+      <c r="A150" s="7"/>
+      <c r="B150" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E150" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F150" s="1">
+        <v>291979</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" ht="16.5">
+      <c r="A151" s="7"/>
+      <c r="B151" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E151" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F151" s="1">
+        <v>292480</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" ht="16.5">
+      <c r="A152" s="7"/>
+      <c r="B152" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E15" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F15" s="1">
-        <v>293378</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="16.5">
-      <c r="A16" s="8"/>
-      <c r="B16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E16" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F16" s="1">
-        <v>292659</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="16.5">
-      <c r="A17" s="8"/>
-      <c r="B17" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E17" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F17" s="1">
-        <v>292672</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="16.5">
-      <c r="A18" s="8"/>
-      <c r="B18" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="E18" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F18" s="1">
-        <v>294269</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="16.5">
-      <c r="A19" s="8"/>
-      <c r="B19" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="E19" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F19" s="1">
-        <v>292325</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="16.5">
-      <c r="A20" s="8"/>
-      <c r="B20" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E20" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F20" s="1">
-        <v>293533</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="16.5">
-      <c r="A21" s="8"/>
-      <c r="B21" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E21" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F21" s="1">
-        <v>291742</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="16.5">
-      <c r="A22" s="8"/>
-      <c r="B22" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E22" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F22" s="1">
-        <v>293692</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="16.5">
-      <c r="A23" s="8"/>
-      <c r="B23" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="E23" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F23" s="1">
-        <v>293127</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="16.5">
-      <c r="A24" s="8"/>
-      <c r="B24" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E24" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F24" s="1">
-        <v>293979</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="16.5">
-      <c r="A25" s="8"/>
-      <c r="B25" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E25" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F25" s="1">
-        <v>292961</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="16.5">
-      <c r="A26" s="8"/>
-      <c r="B26" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E26" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F26" s="1">
-        <v>293130</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="16.5">
-      <c r="A27" s="8"/>
-      <c r="B27" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E27" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F27" s="1">
-        <v>292917</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="16.5">
-      <c r="A28" s="8"/>
-      <c r="B28" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="E28" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F28" s="1">
-        <v>294351</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="16.5">
-      <c r="A29" s="8"/>
-      <c r="B29" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E29" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F29" s="1">
-        <v>294306</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="16.5">
-      <c r="A30" s="8"/>
-      <c r="B30" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E30" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F30" s="1">
-        <v>293131</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="16.5">
-      <c r="A31" s="8"/>
-      <c r="B31" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E31" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F31" s="1">
-        <v>292371</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="16.5">
-      <c r="A32" s="8"/>
-      <c r="B32" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E32" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F32" s="1">
-        <v>294307</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="16.5">
-      <c r="A33" s="8"/>
-      <c r="B33" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C33" s="1" t="s">
+      <c r="C152" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D152" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="E152" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F152" s="1">
+        <v>288251</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" ht="16.5">
+      <c r="A153" s="7"/>
+      <c r="B153" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E153" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F153" s="1">
+        <v>293613</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" ht="16.5">
+      <c r="A154" s="7"/>
+      <c r="B154" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E154" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F154" s="1">
+        <v>289071</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" ht="16.5">
+      <c r="A155" s="7"/>
+      <c r="B155" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E155" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F155" s="1">
+        <v>291998</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" ht="16.5">
+      <c r="A156" s="7"/>
+      <c r="B156" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E156" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F156" s="1">
+        <v>293116</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" ht="16.5">
+      <c r="A157" s="7"/>
+      <c r="B157" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D157" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="E157" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F157" s="1">
+        <v>292199</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" ht="16.5">
+      <c r="A158" s="7"/>
+      <c r="B158" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D158" s="1"/>
+      <c r="E158" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F158" s="1">
+        <v>288766</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" ht="16.5">
+      <c r="A159" s="7"/>
+      <c r="B159" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E159" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F159" s="1">
+        <v>288858</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" ht="16.5">
+      <c r="A160" s="7"/>
+      <c r="B160" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D33" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E33" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F33" s="1">
-        <v>293134</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="16.5">
-      <c r="A34" s="8"/>
-      <c r="B34" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E34" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F34" s="1">
-        <v>293007</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="16.5">
-      <c r="A35" s="8"/>
-      <c r="B35" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E35" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F35" s="1">
-        <v>292202</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="16.5">
-      <c r="A36" s="8"/>
-      <c r="B36" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E36" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F36" s="1">
-        <v>292763</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="16.5">
-      <c r="A37" s="8"/>
-      <c r="B37" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E37" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F37" s="1">
-        <v>293262</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="16.5">
-      <c r="A38" s="8"/>
-      <c r="B38" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="E38" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F38" s="1">
-        <v>293287</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="16.5">
-      <c r="A39" s="8"/>
-      <c r="B39" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E39" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F39" s="1">
-        <v>293463</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="16.5">
-      <c r="A40" s="8"/>
-      <c r="B40" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E40" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F40" s="1">
-        <v>289000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="16.5">
-      <c r="A41" s="8"/>
-      <c r="B41" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E41" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F41" s="1">
-        <v>293464</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="16.5">
-      <c r="A42" s="8"/>
-      <c r="B42" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E42" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F42" s="1">
-        <v>292789</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="16.5">
-      <c r="A43" s="8"/>
-      <c r="B43" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E43" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F43" s="1">
-        <v>293434</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="16.5">
-      <c r="A44" s="8"/>
-      <c r="B44" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E44" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F44" s="1">
-        <v>292610</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="16.5">
-      <c r="A45" s="8"/>
-      <c r="B45" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E45" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F45" s="1">
-        <v>294322</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="16.5">
-      <c r="A46" s="8"/>
-      <c r="B46" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E46" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F46" s="1">
-        <v>293962</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="16.5">
-      <c r="A47" s="8"/>
-      <c r="B47" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E47" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F47" s="1">
-        <v>293442</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="16.5">
-      <c r="A48" s="8"/>
-      <c r="B48" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E48" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F48" s="1">
-        <v>292802</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="16.5">
-      <c r="A49" s="8"/>
-      <c r="B49" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E49" s="6">
-        <v>45946</v>
-      </c>
-      <c r="F49" s="3">
-        <v>292091</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="16.5">
-      <c r="A50" s="8"/>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E50" s="6"/>
-      <c r="F50" s="1"/>
-    </row>
-    <row r="51" spans="1:6" ht="16.5">
-      <c r="A51" s="8"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E51" s="6"/>
-      <c r="F51" s="1"/>
-    </row>
-    <row r="52" spans="1:6" ht="16.5">
-      <c r="A52" s="8"/>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E52" s="6"/>
-      <c r="F52" s="1"/>
-    </row>
-    <row r="53" spans="1:6" ht="16.5">
-      <c r="A53" s="8"/>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="D53" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="E53" s="6"/>
-      <c r="F53" s="1"/>
+      <c r="C160" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E160" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F160" s="1">
+        <v>294104</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" ht="16.5">
+      <c r="A161" s="7"/>
+      <c r="B161" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E161" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F161" s="1">
+        <v>288974</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" ht="16.5">
+      <c r="A162" s="7"/>
+      <c r="B162" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="E162" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F162" s="1">
+        <v>288385</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" ht="16.5">
+      <c r="A163" s="7"/>
+      <c r="B163" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E163" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F163" s="1">
+        <v>291858</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" ht="16.5">
+      <c r="A164" s="7"/>
+      <c r="B164" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E164" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F164" s="1">
+        <v>288395</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" ht="16.5">
+      <c r="A165" s="7"/>
+      <c r="B165" s="1"/>
+      <c r="C165" s="1"/>
+      <c r="D165" s="1"/>
+      <c r="E165" s="5"/>
+      <c r="F165" s="1"/>
+    </row>
+    <row r="166" spans="1:6" ht="16.5">
+      <c r="A166" s="7"/>
+      <c r="B166" s="1"/>
+      <c r="C166" s="1"/>
+      <c r="D166" s="1"/>
+      <c r="E166" s="5"/>
+      <c r="F166" s="1"/>
+    </row>
+    <row r="167" spans="1:6" ht="16.5">
+      <c r="A167" s="7"/>
+      <c r="B167" s="1"/>
+      <c r="C167" s="1"/>
+      <c r="D167" s="6"/>
+      <c r="E167" s="5"/>
+      <c r="F167" s="1"/>
+    </row>
+    <row r="168" spans="1:6" ht="16.5">
+      <c r="A168" s="7"/>
+      <c r="B168" s="1"/>
+      <c r="C168" s="1"/>
+      <c r="D168" s="1"/>
+      <c r="E168" s="5"/>
+      <c r="F168" s="1"/>
+    </row>
+    <row r="169" spans="1:6" ht="16.5">
+      <c r="A169" s="7"/>
+      <c r="B169" s="1"/>
+      <c r="C169" s="1"/>
+      <c r="D169" s="1"/>
+      <c r="E169" s="5"/>
+      <c r="F169" s="1"/>
+    </row>
+    <row r="170" spans="1:6" ht="16.5">
+      <c r="A170" s="7"/>
+      <c r="B170" s="1"/>
+      <c r="C170" s="1"/>
+      <c r="D170" s="1"/>
+      <c r="E170" s="5"/>
+      <c r="F170" s="1"/>
+    </row>
+    <row r="171" spans="1:6" ht="16.5">
+      <c r="A171" s="7"/>
+      <c r="B171" s="1"/>
+      <c r="C171" s="1"/>
+      <c r="D171" s="1"/>
+      <c r="E171" s="5"/>
+      <c r="F171" s="1"/>
+    </row>
+    <row r="172" spans="1:6" ht="16.5">
+      <c r="A172" s="7"/>
+      <c r="B172" s="1"/>
+      <c r="C172" s="1"/>
+      <c r="D172" s="1"/>
+      <c r="E172" s="5"/>
+      <c r="F172" s="1"/>
+    </row>
+    <row r="173" spans="1:6" ht="16.5">
+      <c r="A173" s="7"/>
+      <c r="B173" s="1"/>
+      <c r="C173" s="1"/>
+      <c r="D173" s="1"/>
+      <c r="E173" s="5"/>
+      <c r="F173" s="1"/>
+    </row>
+    <row r="174" spans="1:6" ht="16.5">
+      <c r="A174" s="7"/>
+      <c r="B174" s="1"/>
+      <c r="C174" s="1"/>
+      <c r="D174" s="1"/>
+      <c r="E174" s="5"/>
+      <c r="F174" s="1"/>
+    </row>
+    <row r="175" spans="1:6" ht="16.5">
+      <c r="A175" s="7"/>
+      <c r="B175" s="1"/>
+      <c r="C175" s="1"/>
+      <c r="D175" s="6"/>
+      <c r="E175" s="5"/>
+      <c r="F175" s="1"/>
+    </row>
+    <row r="176" spans="1:6" ht="16.5">
+      <c r="A176" s="7"/>
+      <c r="B176" s="1"/>
+      <c r="C176" s="1"/>
+      <c r="D176" s="1"/>
+      <c r="E176" s="5"/>
+      <c r="F176" s="1"/>
+    </row>
+    <row r="177" spans="1:6" ht="16.5">
+      <c r="A177" s="7"/>
+      <c r="B177" s="1"/>
+      <c r="C177" s="1"/>
+      <c r="D177" s="1"/>
+      <c r="E177" s="5"/>
+      <c r="F177" s="1"/>
+    </row>
+    <row r="178" spans="1:6" ht="16.5">
+      <c r="A178" s="7"/>
+      <c r="B178" s="1"/>
+      <c r="C178" s="1"/>
+      <c r="D178" s="1"/>
+      <c r="E178" s="5"/>
+      <c r="F178" s="1"/>
+    </row>
+    <row r="179" spans="1:6" ht="16.5">
+      <c r="A179" s="7"/>
+      <c r="B179" s="1"/>
+      <c r="C179" s="1"/>
+      <c r="D179" s="1"/>
+      <c r="E179" s="5"/>
+      <c r="F179" s="1"/>
+    </row>
+    <row r="180" spans="1:6" ht="16.5">
+      <c r="A180" s="7"/>
+      <c r="B180" s="1"/>
+      <c r="C180" s="1"/>
+      <c r="D180" s="6"/>
+      <c r="E180" s="5"/>
+      <c r="F180" s="1"/>
+    </row>
+    <row r="181" spans="1:6" ht="16.5">
+      <c r="A181" s="7"/>
+      <c r="B181" s="1"/>
+      <c r="C181" s="1"/>
+      <c r="D181" s="1"/>
+      <c r="E181" s="5"/>
+      <c r="F181" s="1"/>
+    </row>
+    <row r="182" spans="1:6" ht="16.5">
+      <c r="A182" s="7"/>
+      <c r="B182" s="1"/>
+      <c r="C182" s="1"/>
+      <c r="D182" s="1"/>
+      <c r="E182" s="5"/>
+      <c r="F182" s="1"/>
+    </row>
+    <row r="183" spans="1:6" ht="16.5">
+      <c r="A183" s="7"/>
+      <c r="B183" s="1"/>
+      <c r="C183" s="1"/>
+      <c r="D183" s="1"/>
+      <c r="E183" s="5"/>
+      <c r="F183" s="1"/>
+    </row>
+    <row r="184" spans="1:6" ht="16.5">
+      <c r="A184" s="7"/>
+      <c r="B184" s="1"/>
+      <c r="C184" s="1"/>
+      <c r="D184" s="1"/>
+      <c r="E184" s="5"/>
+      <c r="F184" s="1"/>
+    </row>
+    <row r="185" spans="1:6" ht="16.5">
+      <c r="A185" s="7"/>
+      <c r="B185" s="1"/>
+      <c r="C185" s="1"/>
+      <c r="D185" s="6"/>
+      <c r="E185" s="5"/>
+      <c r="F185" s="1"/>
+    </row>
+    <row r="186" spans="1:6" ht="16.5">
+      <c r="A186" s="7"/>
+      <c r="B186" s="1"/>
+      <c r="C186" s="1"/>
+      <c r="D186" s="1"/>
+      <c r="E186" s="5"/>
+      <c r="F186" s="1"/>
+    </row>
+    <row r="187" spans="1:6" ht="16.5">
+      <c r="A187" s="7"/>
+      <c r="B187" s="1"/>
+      <c r="C187" s="1"/>
+      <c r="D187" s="1"/>
+      <c r="E187" s="5"/>
+      <c r="F187" s="1"/>
+    </row>
+    <row r="188" spans="1:6" ht="16.5">
+      <c r="A188" s="7"/>
+      <c r="B188" s="1"/>
+      <c r="C188" s="1"/>
+      <c r="D188" s="1"/>
+      <c r="E188" s="5"/>
+      <c r="F188" s="1"/>
+    </row>
+    <row r="189" spans="1:6" ht="16.5">
+      <c r="A189" s="7"/>
+      <c r="B189" s="1"/>
+      <c r="C189" s="1"/>
+      <c r="D189" s="1"/>
+      <c r="E189" s="5"/>
+      <c r="F189" s="1"/>
+    </row>
+    <row r="190" spans="1:6" ht="16.5">
+      <c r="A190" s="7"/>
+      <c r="B190" s="1"/>
+      <c r="C190" s="1"/>
+      <c r="D190" s="6"/>
+      <c r="E190" s="5"/>
+      <c r="F190" s="1"/>
+    </row>
+    <row r="191" spans="1:6" ht="16.5">
+      <c r="A191" s="7"/>
+      <c r="B191" s="1"/>
+      <c r="C191" s="1"/>
+      <c r="D191" s="1"/>
+      <c r="E191" s="5"/>
+      <c r="F191" s="1"/>
+    </row>
+    <row r="192" spans="1:6" ht="16.5">
+      <c r="A192" s="7"/>
+      <c r="B192" s="1"/>
+      <c r="C192" s="1"/>
+      <c r="D192" s="1"/>
+      <c r="E192" s="5"/>
+      <c r="F192" s="1"/>
+    </row>
+    <row r="193" spans="1:6" ht="16.5">
+      <c r="A193" s="7"/>
+      <c r="B193" s="1"/>
+      <c r="C193" s="1"/>
+      <c r="D193" s="1"/>
+      <c r="E193" s="5"/>
+      <c r="F193" s="1"/>
+    </row>
+    <row r="194" spans="1:6" ht="16.5">
+      <c r="A194" s="7"/>
+      <c r="B194" s="1"/>
+      <c r="C194" s="1"/>
+      <c r="D194" s="1"/>
+      <c r="E194" s="5"/>
+      <c r="F194" s="1"/>
+    </row>
+    <row r="195" spans="1:6" ht="16.5">
+      <c r="A195" s="7"/>
+      <c r="B195" s="1"/>
+      <c r="C195" s="1"/>
+      <c r="D195" s="6"/>
+      <c r="E195" s="5"/>
+      <c r="F195" s="1"/>
+    </row>
+    <row r="196" spans="1:6" ht="16.5">
+      <c r="A196" s="7"/>
+      <c r="B196" s="1"/>
+      <c r="C196" s="1"/>
+      <c r="D196" s="1"/>
+      <c r="E196" s="5"/>
+      <c r="F196" s="1"/>
+    </row>
+    <row r="197" spans="1:6" ht="16.5">
+      <c r="A197" s="7"/>
+      <c r="B197" s="1"/>
+      <c r="C197" s="1"/>
+      <c r="D197" s="1"/>
+      <c r="E197" s="5"/>
+      <c r="F197" s="1"/>
+    </row>
+    <row r="198" spans="1:6" ht="16.5">
+      <c r="A198" s="7"/>
+      <c r="B198" s="1"/>
+      <c r="C198" s="1"/>
+      <c r="D198" s="1"/>
+      <c r="E198" s="5"/>
+      <c r="F198" s="1"/>
+    </row>
+    <row r="199" spans="1:6" ht="16.5">
+      <c r="A199" s="7"/>
+      <c r="B199" s="1"/>
+      <c r="C199" s="1"/>
+      <c r="D199" s="1"/>
+      <c r="E199" s="5"/>
+      <c r="F199" s="1"/>
+    </row>
+    <row r="200" spans="1:6" ht="16.5">
+      <c r="A200" s="7"/>
+      <c r="B200" s="1"/>
+      <c r="C200" s="1"/>
+      <c r="D200" s="6"/>
+      <c r="E200" s="5"/>
+      <c r="F200" s="1"/>
+    </row>
+    <row r="201" spans="1:6" ht="16.5">
+      <c r="A201" s="7"/>
+      <c r="B201" s="1"/>
+      <c r="C201" s="1"/>
+      <c r="D201" s="1"/>
+      <c r="E201" s="5"/>
+      <c r="F201" s="1"/>
+    </row>
+    <row r="202" spans="1:6" ht="16.5">
+      <c r="A202" s="7"/>
+      <c r="B202" s="1"/>
+      <c r="C202" s="1"/>
+      <c r="D202" s="1"/>
+      <c r="E202" s="5"/>
+      <c r="F202" s="1"/>
+    </row>
+    <row r="203" spans="1:6" ht="16.5">
+      <c r="A203" s="7"/>
+      <c r="B203" s="1"/>
+      <c r="C203" s="1"/>
+      <c r="D203" s="1"/>
+      <c r="E203" s="5"/>
+      <c r="F203" s="1"/>
+    </row>
+    <row r="204" spans="1:6" ht="16.5">
+      <c r="A204" s="7"/>
+      <c r="B204" s="1"/>
+      <c r="C204" s="1"/>
+      <c r="D204" s="1"/>
+      <c r="E204" s="5"/>
+      <c r="F204" s="1"/>
+    </row>
+    <row r="205" spans="1:6" ht="16.5">
+      <c r="A205" s="7"/>
+      <c r="B205" s="1"/>
+      <c r="C205" s="1"/>
+      <c r="D205" s="1"/>
+      <c r="E205" s="5"/>
+      <c r="F205" s="1"/>
+    </row>
+    <row r="206" spans="1:6" ht="16.5">
+      <c r="A206" s="7"/>
+      <c r="B206" s="1"/>
+      <c r="C206" s="1"/>
+      <c r="D206" s="1"/>
+      <c r="E206" s="5"/>
+      <c r="F206" s="1"/>
+    </row>
+    <row r="207" spans="1:6" ht="16.5">
+      <c r="A207" s="7"/>
+      <c r="B207" s="1"/>
+      <c r="C207" s="1"/>
+      <c r="D207" s="1"/>
+      <c r="E207" s="5"/>
+      <c r="F207" s="1"/>
+    </row>
+    <row r="208" spans="1:6" ht="16.5">
+      <c r="A208" s="7"/>
+      <c r="B208" s="1"/>
+      <c r="C208" s="1"/>
+      <c r="D208" s="1"/>
+      <c r="E208" s="5"/>
+      <c r="F208" s="1"/>
+    </row>
+    <row r="209" spans="1:6" ht="16.5">
+      <c r="A209" s="7"/>
+      <c r="B209" s="1"/>
+      <c r="C209" s="1"/>
+      <c r="D209" s="1"/>
+      <c r="E209" s="5"/>
+      <c r="F209" s="1"/>
+    </row>
+    <row r="210" spans="1:6" ht="16.5">
+      <c r="A210" s="7"/>
+      <c r="B210" s="1"/>
+      <c r="C210" s="1"/>
+      <c r="D210" s="1"/>
+      <c r="E210" s="5"/>
+      <c r="F210" s="1"/>
     </row>
   </sheetData>
-  <sortState ref="B8:C51">
-    <sortCondition ref="C8:C51"/>
+  <sortState ref="B8:C208">
+    <sortCondition ref="C8:C208"/>
   </sortState>
   <mergeCells count="4">
     <mergeCell ref="A5:A8"/>
-    <mergeCell ref="A9:A53"/>
+    <mergeCell ref="A9:A210"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B3:F3"/>
   </mergeCells>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\명찰\nametag-app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2246FFE7-0467-48B5-B9E5-8D1DCA2DA2EC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE0D03A-04AC-4D9B-9BA0-F85EF967FA9C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19290" windowHeight="9540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="280">
   <si>
     <t xml:space="preserve">러닝센터 명찰제작 양식 </t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -332,9 +332,6 @@
     <t>김수훈</t>
   </si>
   <si>
-    <t>김상신</t>
-  </si>
-  <si>
     <t>강상봉</t>
   </si>
   <si>
@@ -877,7 +874,7 @@
   </si>
   <si>
     <t>26년 서비스 핵심인재(JLP/SLP) 
-Pool-Stay 구성원 대상 교육</t>
+구성원 대상 교육</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2202,11 +2199,11 @@
     <xf numFmtId="0" fontId="3" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="35" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="238">
@@ -2806,13 +2803,13 @@
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
+      <c r="B3" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
     </row>
     <row r="4" spans="1:6" ht="16.5">
       <c r="A4" s="3" t="s">
@@ -2864,7 +2861,7 @@
         <v>49</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F7" s="6">
         <v>318537</v>
@@ -2882,7 +2879,7 @@
         <v>50</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>46</v>
@@ -2899,7 +2896,7 @@
         <v>51</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E9" s="5">
         <v>46163</v>
@@ -2917,7 +2914,7 @@
         <v>52</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E10" s="5">
         <v>46163</v>
@@ -2935,7 +2932,7 @@
         <v>53</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E11" s="5">
         <v>46163</v>
@@ -2947,13 +2944,13 @@
     <row r="12" spans="1:6" ht="16.5">
       <c r="A12" s="7"/>
       <c r="B12" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E12" s="5">
         <v>46163</v>
@@ -2965,13 +2962,13 @@
     <row r="13" spans="1:6" ht="16.5">
       <c r="A13" s="7"/>
       <c r="B13" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E13" s="5">
         <v>46163</v>
@@ -2983,13 +2980,13 @@
     <row r="14" spans="1:6" ht="16.5">
       <c r="A14" s="7"/>
       <c r="B14" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>56</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E14" s="5">
         <v>46163</v>
@@ -3001,13 +2998,13 @@
     <row r="15" spans="1:6" ht="16.5">
       <c r="A15" s="7"/>
       <c r="B15" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E15" s="5">
         <v>46163</v>
@@ -3024,7 +3021,9 @@
       <c r="C16" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="1"/>
+      <c r="D16" s="1" t="s">
+        <v>278</v>
+      </c>
       <c r="E16" s="5">
         <v>46163</v>
       </c>
@@ -3035,13 +3034,13 @@
     <row r="17" spans="1:6" ht="16.5">
       <c r="A17" s="7"/>
       <c r="B17" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>59</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E17" s="5">
         <v>46163</v>
@@ -3053,13 +3052,13 @@
     <row r="18" spans="1:6" ht="16.5">
       <c r="A18" s="7"/>
       <c r="B18" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>60</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E18" s="5">
         <v>46163</v>
@@ -3071,12 +3070,14 @@
     <row r="19" spans="1:6" ht="16.5">
       <c r="A19" s="7"/>
       <c r="B19" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="1"/>
+      <c r="D19" s="1" t="s">
+        <v>276</v>
+      </c>
       <c r="E19" s="5">
         <v>46163</v>
       </c>
@@ -3087,13 +3088,13 @@
     <row r="20" spans="1:6" ht="16.5">
       <c r="A20" s="7"/>
       <c r="B20" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E20" s="5">
         <v>46163</v>
@@ -3105,13 +3106,13 @@
     <row r="21" spans="1:6" ht="16.5">
       <c r="A21" s="7"/>
       <c r="B21" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E21" s="5">
         <v>46163</v>
@@ -3123,13 +3124,13 @@
     <row r="22" spans="1:6" ht="16.5">
       <c r="A22" s="7"/>
       <c r="B22" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E22" s="5">
         <v>46163</v>
@@ -3141,13 +3142,13 @@
     <row r="23" spans="1:6" ht="16.5">
       <c r="A23" s="7"/>
       <c r="B23" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>65</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E23" s="5">
         <v>46163</v>
@@ -3159,12 +3160,14 @@
     <row r="24" spans="1:6" ht="16.5">
       <c r="A24" s="7"/>
       <c r="B24" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D24" s="1"/>
+      <c r="D24" s="1" t="s">
+        <v>276</v>
+      </c>
       <c r="E24" s="5">
         <v>46163</v>
       </c>
@@ -3175,13 +3178,13 @@
     <row r="25" spans="1:6" ht="16.5">
       <c r="A25" s="7"/>
       <c r="B25" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E25" s="5">
         <v>46163</v>
@@ -3199,7 +3202,7 @@
         <v>68</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E26" s="5">
         <v>46163</v>
@@ -3217,7 +3220,7 @@
         <v>69</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E27" s="5">
         <v>46163</v>
@@ -3229,13 +3232,13 @@
     <row r="28" spans="1:6" ht="16.5">
       <c r="A28" s="7"/>
       <c r="B28" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>70</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E28" s="5">
         <v>46163</v>
@@ -3253,7 +3256,7 @@
         <v>71</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E29" s="5">
         <v>46163</v>
@@ -3265,13 +3268,13 @@
     <row r="30" spans="1:6" ht="16.5">
       <c r="A30" s="7"/>
       <c r="B30" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E30" s="5">
         <v>46163</v>
@@ -3288,7 +3291,9 @@
       <c r="C31" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D31" s="1"/>
+      <c r="D31" s="1" t="s">
+        <v>276</v>
+      </c>
       <c r="E31" s="5">
         <v>46163</v>
       </c>
@@ -3299,13 +3304,13 @@
     <row r="32" spans="1:6" ht="16.5">
       <c r="A32" s="7"/>
       <c r="B32" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>74</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E32" s="5">
         <v>46163</v>
@@ -3317,13 +3322,13 @@
     <row r="33" spans="1:6" ht="16.5">
       <c r="A33" s="7"/>
       <c r="B33" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E33" s="5">
         <v>46163</v>
@@ -3340,7 +3345,9 @@
       <c r="C34" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D34" s="1"/>
+      <c r="D34" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="E34" s="5">
         <v>46163</v>
       </c>
@@ -3351,13 +3358,13 @@
     <row r="35" spans="1:6" ht="16.5">
       <c r="A35" s="7"/>
       <c r="B35" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E35" s="5">
         <v>46163</v>
@@ -3369,13 +3376,13 @@
     <row r="36" spans="1:6" ht="16.5">
       <c r="A36" s="7"/>
       <c r="B36" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E36" s="5">
         <v>46163</v>
@@ -3387,13 +3394,13 @@
     <row r="37" spans="1:6" ht="16.5">
       <c r="A37" s="7"/>
       <c r="B37" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E37" s="5">
         <v>46163</v>
@@ -3405,13 +3412,13 @@
     <row r="38" spans="1:6" ht="16.5">
       <c r="A38" s="7"/>
       <c r="B38" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E38" s="5">
         <v>46163</v>
@@ -3423,13 +3430,13 @@
     <row r="39" spans="1:6" ht="16.5">
       <c r="A39" s="7"/>
       <c r="B39" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>81</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E39" s="5">
         <v>46163</v>
@@ -3441,13 +3448,13 @@
     <row r="40" spans="1:6" ht="16.5">
       <c r="A40" s="7"/>
       <c r="B40" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E40" s="5">
         <v>46163</v>
@@ -3459,13 +3466,13 @@
     <row r="41" spans="1:6" ht="16.5">
       <c r="A41" s="7"/>
       <c r="B41" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E41" s="5">
         <v>46163</v>
@@ -3477,13 +3484,13 @@
     <row r="42" spans="1:6" ht="16.5">
       <c r="A42" s="7"/>
       <c r="B42" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E42" s="5">
         <v>46163</v>
@@ -3500,7 +3507,9 @@
       <c r="C43" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D43" s="6"/>
+      <c r="D43" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="E43" s="5">
         <v>46163</v>
       </c>
@@ -3511,7 +3520,7 @@
     <row r="44" spans="1:6" ht="16.5">
       <c r="A44" s="7"/>
       <c r="B44" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>86</v>
@@ -3535,7 +3544,7 @@
         <v>87</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E45" s="5">
         <v>46163</v>
@@ -3552,7 +3561,9 @@
       <c r="C46" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D46" s="1"/>
+      <c r="D46" s="1" t="s">
+        <v>276</v>
+      </c>
       <c r="E46" s="5">
         <v>46163</v>
       </c>
@@ -3563,13 +3574,13 @@
     <row r="47" spans="1:6" ht="16.5">
       <c r="A47" s="7"/>
       <c r="B47" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E47" s="5">
         <v>46163</v>
@@ -3586,7 +3597,9 @@
       <c r="C48" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D48" s="6"/>
+      <c r="D48" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="E48" s="5">
         <v>46163</v>
       </c>
@@ -3597,13 +3610,13 @@
     <row r="49" spans="1:6" ht="16.5">
       <c r="A49" s="7"/>
       <c r="B49" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E49" s="5">
         <v>46163</v>
@@ -3615,13 +3628,13 @@
     <row r="50" spans="1:6" ht="16.5">
       <c r="A50" s="7"/>
       <c r="B50" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>92</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E50" s="5">
         <v>46163</v>
@@ -3639,7 +3652,7 @@
         <v>93</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E51" s="5">
         <v>46163</v>
@@ -3651,13 +3664,13 @@
     <row r="52" spans="1:6" ht="16.5">
       <c r="A52" s="7"/>
       <c r="B52" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>94</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E52" s="5">
         <v>46163</v>
@@ -3675,7 +3688,7 @@
         <v>95</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E53" s="5">
         <v>46163</v>
@@ -3687,13 +3700,13 @@
     <row r="54" spans="1:6" ht="16.5">
       <c r="A54" s="7"/>
       <c r="B54" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E54" s="5">
         <v>46163</v>
@@ -3710,7 +3723,9 @@
       <c r="C55" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D55" s="1"/>
+      <c r="D55" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="E55" s="5">
         <v>46163</v>
       </c>
@@ -3721,13 +3736,13 @@
     <row r="56" spans="1:6" ht="16.5">
       <c r="A56" s="7"/>
       <c r="B56" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>98</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E56" s="5">
         <v>46163</v>
@@ -3739,35 +3754,37 @@
     <row r="57" spans="1:6" ht="16.5">
       <c r="A57" s="7"/>
       <c r="B57" s="1" t="s">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D57" s="1"/>
+      <c r="D57" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="E57" s="5">
         <v>46163</v>
       </c>
       <c r="F57" s="1">
-        <v>289074</v>
+        <v>292018</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="16.5">
       <c r="A58" s="7"/>
       <c r="B58" s="1" t="s">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>100</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E58" s="5">
         <v>46163</v>
       </c>
       <c r="F58" s="1">
-        <v>292018</v>
+        <v>288615</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="16.5">
@@ -3778,12 +3795,14 @@
       <c r="C59" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D59" s="1"/>
+      <c r="D59" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="E59" s="5">
         <v>46163</v>
       </c>
       <c r="F59" s="1">
-        <v>288615</v>
+        <v>288716</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="16.5">
@@ -3794,12 +3813,14 @@
       <c r="C60" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D60" s="1"/>
+      <c r="D60" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="E60" s="5">
         <v>46163</v>
       </c>
       <c r="F60" s="1">
-        <v>288716</v>
+        <v>288342</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="16.5">
@@ -3811,13 +3832,13 @@
         <v>103</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E61" s="5">
         <v>46163</v>
       </c>
       <c r="F61" s="1">
-        <v>288342</v>
+        <v>288799</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="16.5">
@@ -3828,12 +3849,14 @@
       <c r="C62" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D62" s="1"/>
+      <c r="D62" s="1" t="s">
+        <v>278</v>
+      </c>
       <c r="E62" s="5">
         <v>46163</v>
       </c>
       <c r="F62" s="1">
-        <v>288799</v>
+        <v>294053</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="16.5">
@@ -3845,19 +3868,19 @@
         <v>105</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E63" s="5">
         <v>46163</v>
       </c>
       <c r="F63" s="1">
-        <v>294053</v>
+        <v>288839</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="16.5">
       <c r="A64" s="7"/>
       <c r="B64" s="1" t="s">
-        <v>172</v>
+        <v>32</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>106</v>
@@ -3869,25 +3892,25 @@
         <v>46163</v>
       </c>
       <c r="F64" s="1">
-        <v>288839</v>
+        <v>288841</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="16.5">
       <c r="A65" s="7"/>
       <c r="B65" s="1" t="s">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>107</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E65" s="5">
         <v>46163</v>
       </c>
       <c r="F65" s="1">
-        <v>288841</v>
+        <v>288803</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="16.5">
@@ -3899,19 +3922,19 @@
         <v>108</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E66" s="5">
         <v>46163</v>
       </c>
       <c r="F66" s="1">
-        <v>288803</v>
+        <v>288883</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="16.5">
       <c r="A67" s="7"/>
       <c r="B67" s="1" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>109</v>
@@ -3923,31 +3946,31 @@
         <v>46163</v>
       </c>
       <c r="F67" s="1">
-        <v>288883</v>
+        <v>291769</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="16.5">
       <c r="A68" s="7"/>
       <c r="B68" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>110</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E68" s="5">
         <v>46163</v>
       </c>
       <c r="F68" s="1">
-        <v>291769</v>
+        <v>310164</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="16.5">
       <c r="A69" s="7"/>
       <c r="B69" s="1" t="s">
-        <v>23</v>
+        <v>174</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>111</v>
@@ -3959,7 +3982,7 @@
         <v>46163</v>
       </c>
       <c r="F69" s="1">
-        <v>310164</v>
+        <v>289079</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="16.5">
@@ -3971,13 +3994,13 @@
         <v>112</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E70" s="5">
         <v>46163</v>
       </c>
       <c r="F70" s="1">
-        <v>289079</v>
+        <v>288227</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="16.5">
@@ -3988,34 +4011,38 @@
       <c r="C71" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D71" s="1"/>
+      <c r="D71" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="E71" s="5">
         <v>46163</v>
       </c>
       <c r="F71" s="1">
-        <v>288227</v>
+        <v>288885</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="16.5">
       <c r="A72" s="7"/>
       <c r="B72" s="1" t="s">
-        <v>177</v>
+        <v>13</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D72" s="1"/>
+      <c r="D72" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="E72" s="5">
         <v>46163</v>
       </c>
       <c r="F72" s="1">
-        <v>288885</v>
+        <v>288945</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="16.5">
       <c r="A73" s="7"/>
       <c r="B73" s="1" t="s">
-        <v>13</v>
+        <v>177</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>115</v>
@@ -4027,7 +4054,7 @@
         <v>46163</v>
       </c>
       <c r="F73" s="1">
-        <v>288945</v>
+        <v>291739</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="16.5">
@@ -4039,13 +4066,13 @@
         <v>116</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E74" s="5">
         <v>46163</v>
       </c>
       <c r="F74" s="1">
-        <v>291739</v>
+        <v>289050</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="16.5">
@@ -4057,13 +4084,13 @@
         <v>117</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E75" s="5">
         <v>46163</v>
       </c>
       <c r="F75" s="1">
-        <v>289050</v>
+        <v>288676</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="16.5">
@@ -4075,13 +4102,13 @@
         <v>118</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E76" s="5">
         <v>46163</v>
       </c>
       <c r="F76" s="1">
-        <v>288676</v>
+        <v>291894</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="16.5">
@@ -4093,71 +4120,73 @@
         <v>119</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E77" s="5">
         <v>46163</v>
       </c>
       <c r="F77" s="1">
-        <v>291894</v>
+        <v>292819</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="16.5">
       <c r="A78" s="7"/>
       <c r="B78" s="1" t="s">
-        <v>182</v>
+        <v>37</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>120</v>
+        <v>11</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E78" s="5">
         <v>46163</v>
       </c>
       <c r="F78" s="1">
-        <v>292819</v>
+        <v>289000</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="16.5">
       <c r="A79" s="7"/>
       <c r="B79" s="1" t="s">
-        <v>37</v>
+        <v>182</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D79" s="1"/>
+        <v>120</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>278</v>
+      </c>
       <c r="E79" s="5">
         <v>46163</v>
       </c>
       <c r="F79" s="1">
-        <v>289000</v>
+        <v>288673</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="16.5">
       <c r="A80" s="7"/>
       <c r="B80" s="1" t="s">
-        <v>183</v>
+        <v>31</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>121</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E80" s="5">
         <v>46163</v>
       </c>
       <c r="F80" s="1">
-        <v>288673</v>
+        <v>288409</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="16.5">
       <c r="A81" s="7"/>
       <c r="B81" s="1" t="s">
-        <v>31</v>
+        <v>183</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>122</v>
@@ -4169,7 +4198,7 @@
         <v>46163</v>
       </c>
       <c r="F81" s="1">
-        <v>288409</v>
+        <v>292746</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="16.5">
@@ -4181,53 +4210,55 @@
         <v>123</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E82" s="5">
         <v>46163</v>
       </c>
       <c r="F82" s="1">
-        <v>292746</v>
+        <v>292381</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="16.5">
       <c r="A83" s="7"/>
       <c r="B83" s="1" t="s">
-        <v>185</v>
+        <v>39</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D83" s="1"/>
+      <c r="D83" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="E83" s="5">
         <v>46163</v>
       </c>
       <c r="F83" s="1">
-        <v>292381</v>
+        <v>292552</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="16.5">
       <c r="A84" s="7"/>
       <c r="B84" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>125</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E84" s="5">
         <v>46163</v>
       </c>
       <c r="F84" s="1">
-        <v>292552</v>
+        <v>292937</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="16.5">
       <c r="A85" s="7"/>
       <c r="B85" s="1" t="s">
-        <v>38</v>
+        <v>151</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>126</v>
@@ -4239,91 +4270,97 @@
         <v>46163</v>
       </c>
       <c r="F85" s="1">
-        <v>292937</v>
+        <v>292568</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="16.5">
       <c r="A86" s="7"/>
       <c r="B86" s="1" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D86" s="6"/>
+      <c r="D86" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="E86" s="5">
         <v>46163</v>
       </c>
       <c r="F86" s="1">
-        <v>292568</v>
+        <v>292135</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="16.5">
       <c r="A87" s="7"/>
       <c r="B87" s="1" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D87" s="1"/>
+      <c r="D87" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="E87" s="5">
         <v>46163</v>
       </c>
       <c r="F87" s="1">
-        <v>292135</v>
+        <v>292670</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="16.5">
       <c r="A88" s="7"/>
       <c r="B88" s="1" t="s">
-        <v>186</v>
+        <v>28</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>129</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E88" s="5">
         <v>46163</v>
       </c>
       <c r="F88" s="1">
-        <v>292670</v>
+        <v>292124</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="16.5">
       <c r="A89" s="7"/>
       <c r="B89" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>130</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E89" s="5">
         <v>46163</v>
       </c>
       <c r="F89" s="1">
-        <v>292124</v>
+        <v>291784</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="16.5">
       <c r="A90" s="7"/>
       <c r="B90" s="1" t="s">
-        <v>23</v>
+        <v>186</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D90" s="1"/>
+      <c r="D90" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="E90" s="5">
         <v>46163</v>
       </c>
       <c r="F90" s="1">
-        <v>291784</v>
+        <v>292964</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="16.5">
@@ -4335,19 +4372,19 @@
         <v>132</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E91" s="5">
         <v>46163</v>
       </c>
       <c r="F91" s="1">
-        <v>292964</v>
+        <v>292597</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="16.5">
       <c r="A92" s="7"/>
       <c r="B92" s="1" t="s">
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>133</v>
@@ -4359,31 +4396,31 @@
         <v>46163</v>
       </c>
       <c r="F92" s="1">
-        <v>292597</v>
+        <v>289029</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="16.5">
       <c r="A93" s="7"/>
       <c r="B93" s="1" t="s">
-        <v>149</v>
+        <v>256</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>134</v>
+        <v>188</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E93" s="5">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F93" s="1">
-        <v>289029</v>
+        <v>293118</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="16.5">
       <c r="A94" s="7"/>
       <c r="B94" s="1" t="s">
-        <v>257</v>
+        <v>40</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>189</v>
@@ -4395,23 +4432,25 @@
         <v>46164</v>
       </c>
       <c r="F94" s="1">
-        <v>293118</v>
+        <v>292302</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="16.5">
       <c r="A95" s="7"/>
       <c r="B95" s="1" t="s">
-        <v>40</v>
+        <v>257</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D95" s="1"/>
+      <c r="D95" s="1" t="s">
+        <v>276</v>
+      </c>
       <c r="E95" s="5">
         <v>46164</v>
       </c>
       <c r="F95" s="1">
-        <v>292302</v>
+        <v>292612</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="16.5">
@@ -4422,64 +4461,68 @@
       <c r="C96" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="D96" s="6"/>
+      <c r="D96" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="E96" s="5">
         <v>46164</v>
       </c>
       <c r="F96" s="1">
-        <v>292612</v>
+        <v>291800</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="16.5">
       <c r="A97" s="7"/>
       <c r="B97" s="1" t="s">
-        <v>259</v>
+        <v>135</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>192</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E97" s="5">
         <v>46164</v>
       </c>
       <c r="F97" s="1">
-        <v>291800</v>
+        <v>293793</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="16.5">
       <c r="A98" s="7"/>
       <c r="B98" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D98" s="1"/>
+      <c r="D98" s="1" t="s">
+        <v>278</v>
+      </c>
       <c r="E98" s="5">
         <v>46164</v>
       </c>
       <c r="F98" s="1">
-        <v>293793</v>
+        <v>292579</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="16.5">
       <c r="A99" s="7"/>
       <c r="B99" s="1" t="s">
-        <v>136</v>
+        <v>259</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>194</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E99" s="5">
         <v>46164</v>
       </c>
       <c r="F99" s="1">
-        <v>292579</v>
+        <v>292246</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="16.5">
@@ -4497,173 +4540,175 @@
         <v>46164</v>
       </c>
       <c r="F100" s="1">
-        <v>292246</v>
+        <v>294098</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="16.5">
       <c r="A101" s="7"/>
       <c r="B101" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>196</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E101" s="5">
         <v>46164</v>
       </c>
       <c r="F101" s="1">
-        <v>294098</v>
+        <v>292744</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="16.5">
       <c r="A102" s="7"/>
       <c r="B102" s="1" t="s">
-        <v>261</v>
+        <v>22</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>197</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E102" s="5">
         <v>46164</v>
       </c>
       <c r="F102" s="1">
-        <v>292744</v>
+        <v>289068</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="16.5">
       <c r="A103" s="7"/>
       <c r="B103" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>198</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E103" s="5">
         <v>46164</v>
       </c>
       <c r="F103" s="1">
-        <v>289068</v>
+        <v>292848</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="16.5">
       <c r="A104" s="7"/>
       <c r="B104" s="1" t="s">
-        <v>14</v>
+        <v>136</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>199</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E104" s="5">
         <v>46164</v>
       </c>
       <c r="F104" s="1">
-        <v>292848</v>
+        <v>292104</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="16.5">
       <c r="A105" s="7"/>
       <c r="B105" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>200</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E105" s="5">
         <v>46164</v>
       </c>
       <c r="F105" s="1">
-        <v>292104</v>
+        <v>291920</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="16.5">
       <c r="A106" s="7"/>
       <c r="B106" s="1" t="s">
-        <v>139</v>
+        <v>30</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>201</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E106" s="5">
         <v>46164</v>
       </c>
       <c r="F106" s="1">
-        <v>291920</v>
+        <v>289127</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="16.5">
       <c r="A107" s="7"/>
       <c r="B107" s="1" t="s">
-        <v>30</v>
+        <v>261</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>202</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E107" s="5">
         <v>46164</v>
       </c>
       <c r="F107" s="1">
-        <v>289127</v>
+        <v>289137</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="16.5">
       <c r="A108" s="7"/>
       <c r="B108" s="1" t="s">
-        <v>262</v>
+        <v>139</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>203</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E108" s="5">
         <v>46164</v>
       </c>
       <c r="F108" s="1">
-        <v>289137</v>
+        <v>275950</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="16.5">
       <c r="A109" s="7"/>
       <c r="B109" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="D109" s="6"/>
+      <c r="D109" s="6" t="s">
+        <v>276</v>
+      </c>
       <c r="E109" s="5">
         <v>46164</v>
       </c>
       <c r="F109" s="1">
-        <v>275950</v>
+        <v>292464</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="16.5">
       <c r="A110" s="7"/>
       <c r="B110" s="1" t="s">
-        <v>140</v>
+        <v>262</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>205</v>
@@ -4675,7 +4720,7 @@
         <v>46164</v>
       </c>
       <c r="F110" s="1">
-        <v>292464</v>
+        <v>292577</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="16.5">
@@ -4693,43 +4738,43 @@
         <v>46164</v>
       </c>
       <c r="F111" s="1">
-        <v>292577</v>
+        <v>292556</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="16.5">
       <c r="A112" s="7"/>
       <c r="B112" s="1" t="s">
-        <v>264</v>
+        <v>140</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>207</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E112" s="5">
         <v>46164</v>
       </c>
       <c r="F112" s="1">
-        <v>292556</v>
+        <v>291916</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="16.5">
       <c r="A113" s="7"/>
       <c r="B113" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>208</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E113" s="5">
         <v>46164</v>
       </c>
       <c r="F113" s="1">
-        <v>291916</v>
+        <v>292467</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="16.5">
@@ -4741,67 +4786,67 @@
         <v>209</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E114" s="5">
         <v>46164</v>
       </c>
       <c r="F114" s="1">
-        <v>292467</v>
+        <v>292671</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="16.5">
       <c r="A115" s="7"/>
       <c r="B115" s="1" t="s">
-        <v>142</v>
+        <v>16</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>210</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E115" s="5">
         <v>46164</v>
       </c>
       <c r="F115" s="1">
-        <v>292671</v>
+        <v>293006</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="16.5">
       <c r="A116" s="7"/>
       <c r="B116" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>211</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E116" s="5">
         <v>46164</v>
       </c>
       <c r="F116" s="1">
-        <v>293006</v>
+        <v>288561</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="16.5">
       <c r="A117" s="7"/>
       <c r="B117" s="1" t="s">
-        <v>21</v>
+        <v>145</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>212</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E117" s="5">
         <v>46164</v>
       </c>
       <c r="F117" s="1">
-        <v>288561</v>
+        <v>288927</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="16.5">
@@ -4813,71 +4858,73 @@
         <v>213</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E118" s="5">
         <v>46164</v>
       </c>
       <c r="F118" s="1">
-        <v>288927</v>
+        <v>288189</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="16.5">
       <c r="A119" s="7"/>
       <c r="B119" s="1" t="s">
-        <v>147</v>
+        <v>264</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>214</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E119" s="5">
         <v>46164</v>
       </c>
       <c r="F119" s="1">
-        <v>288189</v>
+        <v>293067</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="16.5">
       <c r="A120" s="7"/>
       <c r="B120" s="1" t="s">
-        <v>265</v>
+        <v>147</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>215</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E120" s="5">
         <v>46164</v>
       </c>
       <c r="F120" s="1">
-        <v>293067</v>
+        <v>292976</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="16.5">
       <c r="A121" s="7"/>
       <c r="B121" s="1" t="s">
-        <v>148</v>
+        <v>24</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="D121" s="1"/>
+      <c r="D121" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="E121" s="5">
         <v>46164</v>
       </c>
       <c r="F121" s="1">
-        <v>292976</v>
+        <v>292622</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="16.5">
       <c r="A122" s="7"/>
       <c r="B122" s="1" t="s">
-        <v>24</v>
+        <v>265</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>217</v>
@@ -4889,49 +4936,49 @@
         <v>46164</v>
       </c>
       <c r="F122" s="1">
-        <v>292622</v>
+        <v>292151</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="16.5">
       <c r="A123" s="7"/>
       <c r="B123" s="1" t="s">
-        <v>266</v>
+        <v>149</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>218</v>
+        <v>8</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E123" s="5">
         <v>46164</v>
       </c>
       <c r="F123" s="1">
-        <v>292151</v>
+        <v>288076</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="16.5">
       <c r="A124" s="7"/>
       <c r="B124" s="1" t="s">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E124" s="5">
         <v>46164</v>
       </c>
       <c r="F124" s="1">
-        <v>288076</v>
+        <v>292101</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="16.5">
       <c r="A125" s="7"/>
       <c r="B125" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>219</v>
@@ -4943,31 +4990,31 @@
         <v>46164</v>
       </c>
       <c r="F125" s="1">
-        <v>292101</v>
+        <v>292337</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="16.5">
       <c r="A126" s="7"/>
       <c r="B126" s="1" t="s">
-        <v>41</v>
+        <v>266</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>220</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E126" s="5">
         <v>46164</v>
       </c>
       <c r="F126" s="1">
-        <v>292337</v>
+        <v>288287</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="16.5">
       <c r="A127" s="7"/>
       <c r="B127" s="1" t="s">
-        <v>267</v>
+        <v>152</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>221</v>
@@ -4979,7 +5026,7 @@
         <v>46164</v>
       </c>
       <c r="F127" s="1">
-        <v>288287</v>
+        <v>292957</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="16.5">
@@ -4991,31 +5038,31 @@
         <v>222</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E128" s="5">
         <v>46164</v>
       </c>
       <c r="F128" s="1">
-        <v>292957</v>
+        <v>292321</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="16.5">
       <c r="A129" s="7"/>
       <c r="B129" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>223</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E129" s="5">
         <v>46164</v>
       </c>
       <c r="F129" s="1">
-        <v>292321</v>
+        <v>288341</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="16.5">
@@ -5027,13 +5074,13 @@
         <v>224</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E130" s="5">
         <v>46164</v>
       </c>
       <c r="F130" s="1">
-        <v>288341</v>
+        <v>293572</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="16.5">
@@ -5044,88 +5091,92 @@
       <c r="C131" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="D131" s="1"/>
+      <c r="D131" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="E131" s="5">
         <v>46164</v>
       </c>
       <c r="F131" s="1">
-        <v>293572</v>
+        <v>292258</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="16.5">
       <c r="A132" s="7"/>
       <c r="B132" s="1" t="s">
-        <v>159</v>
+        <v>33</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>226</v>
+        <v>9</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E132" s="5">
         <v>46164</v>
       </c>
       <c r="F132" s="1">
-        <v>292258</v>
+        <v>292763</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="16.5">
       <c r="A133" s="7"/>
       <c r="B133" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D133" s="1"/>
+        <v>226</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>278</v>
+      </c>
       <c r="E133" s="5">
         <v>46164</v>
       </c>
       <c r="F133" s="1">
-        <v>292763</v>
+        <v>293450</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="16.5">
       <c r="A134" s="7"/>
       <c r="B134" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>227</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E134" s="5">
         <v>46164</v>
       </c>
       <c r="F134" s="1">
-        <v>293450</v>
+        <v>288496</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="16.5">
       <c r="A135" s="7"/>
       <c r="B135" s="1" t="s">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>228</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E135" s="5">
         <v>46164</v>
       </c>
       <c r="F135" s="1">
-        <v>288496</v>
+        <v>293071</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="16.5">
       <c r="A136" s="7"/>
       <c r="B136" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>229</v>
@@ -5137,25 +5188,25 @@
         <v>46164</v>
       </c>
       <c r="F136" s="1">
-        <v>293071</v>
+        <v>292711</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="16.5">
       <c r="A137" s="7"/>
       <c r="B137" s="1" t="s">
-        <v>163</v>
+        <v>267</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>230</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E137" s="5">
         <v>46164</v>
       </c>
       <c r="F137" s="1">
-        <v>292711</v>
+        <v>292946</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="16.5">
@@ -5167,13 +5218,13 @@
         <v>231</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E138" s="5">
         <v>46164</v>
       </c>
       <c r="F138" s="1">
-        <v>292946</v>
+        <v>292037</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="16.5">
@@ -5185,49 +5236,49 @@
         <v>232</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E139" s="5">
         <v>46164</v>
       </c>
       <c r="F139" s="1">
-        <v>292037</v>
+        <v>292513</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="16.5">
       <c r="A140" s="7"/>
       <c r="B140" s="1" t="s">
-        <v>270</v>
+        <v>20</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>233</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E140" s="5">
         <v>46164</v>
       </c>
       <c r="F140" s="1">
-        <v>292513</v>
+        <v>291821</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="16.5">
       <c r="A141" s="7"/>
       <c r="B141" s="1" t="s">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>234</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E141" s="5">
         <v>46164</v>
       </c>
       <c r="F141" s="1">
-        <v>291821</v>
+        <v>292843</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="16.5">
@@ -5239,101 +5290,103 @@
         <v>235</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E142" s="5">
         <v>46164</v>
       </c>
       <c r="F142" s="1">
-        <v>292843</v>
+        <v>292997</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="16.5">
       <c r="A143" s="7"/>
       <c r="B143" s="1" t="s">
-        <v>168</v>
+        <v>36</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>236</v>
+        <v>10</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E143" s="5">
         <v>46164</v>
       </c>
       <c r="F143" s="1">
-        <v>292997</v>
+        <v>293463</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="16.5">
       <c r="A144" s="7"/>
       <c r="B144" s="1" t="s">
-        <v>36</v>
+        <v>171</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D144" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="E144" s="5">
         <v>46164</v>
       </c>
       <c r="F144" s="1">
-        <v>293463</v>
+        <v>288644</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="16.5">
       <c r="A145" s="7"/>
       <c r="B145" s="1" t="s">
-        <v>172</v>
+        <v>270</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E145" s="5">
         <v>46164</v>
       </c>
       <c r="F145" s="1">
-        <v>288644</v>
+        <v>291806</v>
       </c>
     </row>
     <row r="146" spans="1:6" ht="16.5">
       <c r="A146" s="7"/>
       <c r="B146" s="1" t="s">
-        <v>271</v>
+        <v>27</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>238</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E146" s="5">
         <v>46164</v>
       </c>
       <c r="F146" s="1">
-        <v>291806</v>
+        <v>293391</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="16.5">
       <c r="A147" s="7"/>
       <c r="B147" s="1" t="s">
-        <v>27</v>
+        <v>271</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>239</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E147" s="5">
         <v>46164</v>
       </c>
       <c r="F147" s="1">
-        <v>293391</v>
+        <v>291924</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="16.5">
@@ -5344,28 +5397,32 @@
       <c r="C148" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="D148" s="1"/>
+      <c r="D148" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="E148" s="5">
         <v>46164</v>
       </c>
       <c r="F148" s="1">
-        <v>291924</v>
+        <v>292227</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="16.5">
       <c r="A149" s="7"/>
       <c r="B149" s="1" t="s">
-        <v>273</v>
+        <v>172</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="D149" s="1"/>
+      <c r="D149" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="E149" s="5">
         <v>46164</v>
       </c>
       <c r="F149" s="1">
-        <v>292227</v>
+        <v>291979</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="16.5">
@@ -5377,31 +5434,31 @@
         <v>242</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E150" s="5">
         <v>46164</v>
       </c>
       <c r="F150" s="1">
-        <v>291979</v>
+        <v>292480</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="16.5">
       <c r="A151" s="7"/>
       <c r="B151" s="1" t="s">
-        <v>174</v>
+        <v>13</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>243</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E151" s="5">
         <v>46164</v>
       </c>
       <c r="F151" s="1">
-        <v>292480</v>
+        <v>288251</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="16.5">
@@ -5413,19 +5470,19 @@
         <v>244</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E152" s="5">
         <v>46164</v>
       </c>
       <c r="F152" s="1">
-        <v>288251</v>
+        <v>293613</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="16.5">
       <c r="A153" s="7"/>
       <c r="B153" s="1" t="s">
-        <v>13</v>
+        <v>177</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>245</v>
@@ -5437,67 +5494,67 @@
         <v>46164</v>
       </c>
       <c r="F153" s="1">
-        <v>293613</v>
+        <v>289071</v>
       </c>
     </row>
     <row r="154" spans="1:6" ht="16.5">
       <c r="A154" s="7"/>
       <c r="B154" s="1" t="s">
-        <v>178</v>
+        <v>273</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>246</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E154" s="5">
         <v>46164</v>
       </c>
       <c r="F154" s="1">
-        <v>289071</v>
+        <v>291998</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="16.5">
       <c r="A155" s="7"/>
       <c r="B155" s="1" t="s">
-        <v>274</v>
+        <v>179</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>247</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E155" s="5">
         <v>46164</v>
       </c>
       <c r="F155" s="1">
-        <v>291998</v>
+        <v>293116</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="16.5">
       <c r="A156" s="7"/>
       <c r="B156" s="1" t="s">
-        <v>180</v>
+        <v>274</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>248</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E156" s="5">
         <v>46164</v>
       </c>
       <c r="F156" s="1">
-        <v>293116</v>
+        <v>292199</v>
       </c>
     </row>
     <row r="157" spans="1:6" ht="16.5">
       <c r="A157" s="7"/>
       <c r="B157" s="1" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>249</v>
@@ -5509,29 +5566,31 @@
         <v>46164</v>
       </c>
       <c r="F157" s="1">
-        <v>292199</v>
+        <v>288766</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="16.5">
       <c r="A158" s="7"/>
       <c r="B158" s="1" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D158" s="1"/>
+      <c r="D158" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="E158" s="5">
         <v>46164</v>
       </c>
       <c r="F158" s="1">
-        <v>288766</v>
+        <v>288858</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="16.5">
       <c r="A159" s="7"/>
       <c r="B159" s="1" t="s">
-        <v>276</v>
+        <v>31</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>251</v>
@@ -5543,31 +5602,31 @@
         <v>46164</v>
       </c>
       <c r="F159" s="1">
-        <v>288858</v>
+        <v>294104</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="16.5">
       <c r="A160" s="7"/>
       <c r="B160" s="1" t="s">
-        <v>31</v>
+        <v>260</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E160" s="5">
         <v>46164</v>
       </c>
       <c r="F160" s="1">
-        <v>294104</v>
+        <v>288974</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="16.5">
       <c r="A161" s="7"/>
       <c r="B161" s="1" t="s">
-        <v>261</v>
+        <v>183</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>253</v>
@@ -5579,62 +5638,52 @@
         <v>46164</v>
       </c>
       <c r="F161" s="1">
-        <v>288974</v>
+        <v>288385</v>
       </c>
     </row>
     <row r="162" spans="1:6" ht="16.5">
       <c r="A162" s="7"/>
       <c r="B162" s="1" t="s">
-        <v>184</v>
+        <v>271</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>254</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E162" s="5">
         <v>46164</v>
       </c>
       <c r="F162" s="1">
-        <v>288385</v>
+        <v>291858</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="16.5">
       <c r="A163" s="7"/>
       <c r="B163" s="1" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>255</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E163" s="5">
         <v>46164</v>
       </c>
       <c r="F163" s="1">
-        <v>291858</v>
+        <v>288395</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="16.5">
       <c r="A164" s="7"/>
-      <c r="B164" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E164" s="5">
-        <v>46164</v>
-      </c>
-      <c r="F164" s="1">
-        <v>288395</v>
-      </c>
+      <c r="B164" s="1"/>
+      <c r="C164" s="1"/>
+      <c r="D164" s="1"/>
+      <c r="E164" s="5"/>
+      <c r="F164" s="1"/>
     </row>
     <row r="165" spans="1:6" ht="16.5">
       <c r="A165" s="7"/>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\명찰\nametag-app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE0D03A-04AC-4D9B-9BA0-F85EF967FA9C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0AD346-338C-45C7-94B0-E90218F6B4A5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19290" windowHeight="9540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="293">
   <si>
     <t xml:space="preserve">러닝센터 명찰제작 양식 </t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -165,9 +165,6 @@
     <t>이유빈</t>
   </si>
   <si>
-    <t>고객가치혁신 인재육성</t>
-  </si>
-  <si>
     <t>X802901</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -184,697 +181,748 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>송병천</t>
+  </si>
+  <si>
+    <t>문유환</t>
+  </si>
+  <si>
+    <t>이준희</t>
+  </si>
+  <si>
+    <t>박진수</t>
+  </si>
+  <si>
+    <t>손정남</t>
+  </si>
+  <si>
+    <t>김병준</t>
+  </si>
+  <si>
+    <t>윤영진</t>
+  </si>
+  <si>
+    <t>박찬문</t>
+  </si>
+  <si>
+    <t>황재영</t>
+  </si>
+  <si>
+    <t>권순양</t>
+  </si>
+  <si>
+    <t>박지수</t>
+  </si>
+  <si>
+    <t>이태한</t>
+  </si>
+  <si>
+    <t>이승현</t>
+  </si>
+  <si>
+    <t>박승우</t>
+  </si>
+  <si>
+    <t>박기영</t>
+  </si>
+  <si>
+    <t>정연일</t>
+  </si>
+  <si>
+    <t>정수곤</t>
+  </si>
+  <si>
+    <t>박정빈</t>
+  </si>
+  <si>
+    <t>서현규</t>
+  </si>
+  <si>
+    <t>김상우</t>
+  </si>
+  <si>
+    <t>이상기</t>
+  </si>
+  <si>
+    <t>전명수</t>
+  </si>
+  <si>
+    <t>최승연</t>
+  </si>
+  <si>
+    <t>조훈래</t>
+  </si>
+  <si>
+    <t>정관중</t>
+  </si>
+  <si>
+    <t>한관수</t>
+  </si>
+  <si>
+    <t>곽동명</t>
+  </si>
+  <si>
+    <t>신현호</t>
+  </si>
+  <si>
+    <t>오흥철</t>
+  </si>
+  <si>
+    <t>한승용</t>
+  </si>
+  <si>
+    <t>한대식</t>
+  </si>
+  <si>
+    <t>김민우</t>
+  </si>
+  <si>
+    <t>이기모</t>
+  </si>
+  <si>
+    <t>심용석</t>
+  </si>
+  <si>
+    <t>홍상연</t>
+  </si>
+  <si>
+    <t>정범철</t>
+  </si>
+  <si>
+    <t>한영호</t>
+  </si>
+  <si>
+    <t>송승헌</t>
+  </si>
+  <si>
+    <t>윤치운</t>
+  </si>
+  <si>
+    <t>정진호</t>
+  </si>
+  <si>
+    <t>김재원</t>
+  </si>
+  <si>
+    <t>김권영</t>
+  </si>
+  <si>
+    <t>김범룡</t>
+  </si>
+  <si>
+    <t>박우경</t>
+  </si>
+  <si>
+    <t>한의진</t>
+  </si>
+  <si>
+    <t>임호성</t>
+  </si>
+  <si>
+    <t>조경원</t>
+  </si>
+  <si>
+    <t>김수훈</t>
+  </si>
+  <si>
+    <t>강상봉</t>
+  </si>
+  <si>
+    <t>최건영</t>
+  </si>
+  <si>
+    <t>신길재</t>
+  </si>
+  <si>
+    <t>김영우</t>
+  </si>
+  <si>
+    <t>홍성민</t>
+  </si>
+  <si>
+    <t>김명호</t>
+  </si>
+  <si>
+    <t>김인성</t>
+  </si>
+  <si>
+    <t>김장수</t>
+  </si>
+  <si>
+    <t>강수호</t>
+  </si>
+  <si>
+    <t>박진영</t>
+  </si>
+  <si>
+    <t>백종엽</t>
+  </si>
+  <si>
+    <t>손상범</t>
+  </si>
+  <si>
+    <t>김솔이</t>
+  </si>
+  <si>
+    <t>이동우</t>
+  </si>
+  <si>
+    <t>박창호</t>
+  </si>
+  <si>
+    <t>이성민</t>
+  </si>
+  <si>
+    <t>박선민</t>
+  </si>
+  <si>
+    <t>권혁민</t>
+  </si>
+  <si>
+    <t>김한승</t>
+  </si>
+  <si>
+    <t>이창진</t>
+  </si>
+  <si>
+    <t>강준수</t>
+  </si>
+  <si>
+    <t>김태현</t>
+  </si>
+  <si>
+    <t>유보선</t>
+  </si>
+  <si>
+    <t>이태우</t>
+  </si>
+  <si>
+    <t>이동수</t>
+  </si>
+  <si>
+    <t>윤명하</t>
+  </si>
+  <si>
+    <t>이덕만</t>
+  </si>
+  <si>
+    <t>이은경</t>
+  </si>
+  <si>
+    <t>염수일</t>
+  </si>
+  <si>
+    <t>김호량</t>
+  </si>
+  <si>
+    <t>송종우</t>
+  </si>
+  <si>
+    <t>손준우</t>
+  </si>
+  <si>
+    <t>안혜성</t>
+  </si>
+  <si>
+    <t>정혜림</t>
+  </si>
+  <si>
+    <t>강동원</t>
+  </si>
+  <si>
+    <t>2026-05-21 ~ 22</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>경산서비스센터</t>
+  </si>
+  <si>
+    <t>광산서비스센터</t>
+  </si>
+  <si>
+    <t>광진서비스센터</t>
+  </si>
+  <si>
+    <t>구미서비스센터</t>
+  </si>
+  <si>
+    <t>김포서비스센터</t>
+  </si>
+  <si>
+    <t>남부역량지원계</t>
+  </si>
+  <si>
+    <t>남수원서비스센터</t>
+  </si>
+  <si>
+    <t>남울산서비스센터</t>
+  </si>
+  <si>
+    <t>남청주서비스센터</t>
+  </si>
+  <si>
+    <t>대치서비스센터</t>
+  </si>
+  <si>
+    <t>덕천서비스센터</t>
+  </si>
+  <si>
+    <t>동대구서비스센터</t>
+  </si>
+  <si>
+    <t>동래서비스센터</t>
+  </si>
+  <si>
+    <t>마산서비스센터</t>
+  </si>
+  <si>
+    <t>부천서비스센터</t>
+  </si>
+  <si>
+    <t>북울산서비스센터</t>
+  </si>
+  <si>
+    <t>북인천서비스센터</t>
+  </si>
+  <si>
+    <t>서광주서비스센터</t>
+  </si>
+  <si>
+    <t>서귀포서비스센터</t>
+  </si>
+  <si>
+    <t>서대구서비스센터</t>
+  </si>
+  <si>
+    <t>서대전서비스센터</t>
+  </si>
+  <si>
+    <t>서면서비스센터</t>
+  </si>
+  <si>
+    <t>서부역량강화팀</t>
+  </si>
+  <si>
+    <t>서안산서비스센터</t>
+  </si>
+  <si>
+    <t>서초서비스센터</t>
+  </si>
+  <si>
+    <t>세종서비스센터</t>
+  </si>
+  <si>
+    <t>속초서비스센터</t>
+  </si>
+  <si>
+    <t>수도권역량지원계</t>
+  </si>
+  <si>
+    <t>아산서비스센터</t>
+  </si>
+  <si>
+    <t>양산서비스센터</t>
+  </si>
+  <si>
+    <t>양천서비스센터</t>
+  </si>
+  <si>
+    <t>오산서비스센터</t>
+  </si>
+  <si>
+    <t>용인출장서비스센터</t>
+  </si>
+  <si>
+    <t>의왕서비스센터</t>
+  </si>
+  <si>
+    <t>의정부서비스센터</t>
+  </si>
+  <si>
+    <t>이천서비스센터</t>
+  </si>
+  <si>
+    <t>일산서비스센터</t>
+  </si>
+  <si>
+    <t>진주서비스센터</t>
+  </si>
+  <si>
+    <t>창원서비스센터</t>
+  </si>
+  <si>
+    <t>충무로역서비스센터</t>
+  </si>
+  <si>
+    <t>태백서비스센터</t>
+  </si>
+  <si>
+    <t>파주서비스센터</t>
+  </si>
+  <si>
+    <t>포항서비스센터</t>
+  </si>
+  <si>
+    <t>프리미엄케어서비스센터</t>
+  </si>
+  <si>
+    <t>해외CC&amp;S역량개발팀</t>
+  </si>
+  <si>
+    <t>홍대역서비스센터</t>
+  </si>
+  <si>
+    <t>홍성서비스센터</t>
+  </si>
+  <si>
+    <t>대연서비스센터</t>
+  </si>
+  <si>
+    <t>남동서비스센터</t>
+  </si>
+  <si>
+    <t>남양주서비스센터</t>
+  </si>
+  <si>
+    <t>용산서비스센터</t>
+  </si>
+  <si>
+    <t>하남서비스센터</t>
+  </si>
+  <si>
+    <t>동해서비스센터</t>
+  </si>
+  <si>
+    <t>홍성길</t>
+  </si>
+  <si>
+    <t>김은기</t>
+  </si>
+  <si>
+    <t>최종근</t>
+  </si>
+  <si>
+    <t>심경훈</t>
+  </si>
+  <si>
+    <t>서상혁</t>
+  </si>
+  <si>
+    <t>이춘훈</t>
+  </si>
+  <si>
+    <t>현두용</t>
+  </si>
+  <si>
+    <t>심세윤</t>
+  </si>
+  <si>
+    <t>이창혁</t>
+  </si>
+  <si>
+    <t>김민섭</t>
+  </si>
+  <si>
+    <t>이민호</t>
+  </si>
+  <si>
+    <t>박찬석</t>
+  </si>
+  <si>
+    <t>장영목</t>
+  </si>
+  <si>
+    <t>나영민</t>
+  </si>
+  <si>
+    <t>도성준</t>
+  </si>
+  <si>
+    <t>박치원</t>
+  </si>
+  <si>
+    <t>권혁</t>
+  </si>
+  <si>
+    <t>이철호</t>
+  </si>
+  <si>
+    <t>이경훈</t>
+  </si>
+  <si>
+    <t>장대원</t>
+  </si>
+  <si>
+    <t>김기현</t>
+  </si>
+  <si>
+    <t>김효림</t>
+  </si>
+  <si>
+    <t>서영식</t>
+  </si>
+  <si>
+    <t>오원규</t>
+  </si>
+  <si>
+    <t>오진석</t>
+  </si>
+  <si>
+    <t>방설빈</t>
+  </si>
+  <si>
+    <t>안홍기</t>
+  </si>
+  <si>
+    <t>정재욱</t>
+  </si>
+  <si>
+    <t>홍경주</t>
+  </si>
+  <si>
+    <t>윤경찬</t>
+  </si>
+  <si>
+    <t>박정민</t>
+  </si>
+  <si>
+    <t>박지호</t>
+  </si>
+  <si>
+    <t>최기성</t>
+  </si>
+  <si>
+    <t>문종민</t>
+  </si>
+  <si>
+    <t>박경배</t>
+  </si>
+  <si>
+    <t>김승환</t>
+  </si>
+  <si>
+    <t>조덕희</t>
+  </si>
+  <si>
+    <t>권기만</t>
+  </si>
+  <si>
+    <t>김호영</t>
+  </si>
+  <si>
+    <t>김대현</t>
+  </si>
+  <si>
+    <t>정필완</t>
+  </si>
+  <si>
+    <t>엄영섭</t>
+  </si>
+  <si>
+    <t>김성원</t>
+  </si>
+  <si>
+    <t>김남덕</t>
+  </si>
+  <si>
+    <t>박재홍</t>
+  </si>
+  <si>
+    <t>오종택</t>
+  </si>
+  <si>
+    <t>양광복</t>
+  </si>
+  <si>
+    <t>이기춘</t>
+  </si>
+  <si>
+    <t>고창진</t>
+  </si>
+  <si>
+    <t>안희진</t>
+  </si>
+  <si>
+    <t>홍희진</t>
+  </si>
+  <si>
+    <t>강호성</t>
+  </si>
+  <si>
+    <t>최영진</t>
+  </si>
+  <si>
+    <t>최왕경</t>
+  </si>
+  <si>
+    <t>김영길</t>
+  </si>
+  <si>
+    <t>이춘재</t>
+  </si>
+  <si>
+    <t>송민규</t>
+  </si>
+  <si>
+    <t>김보성</t>
+  </si>
+  <si>
+    <t>한광일</t>
+  </si>
+  <si>
+    <t>현기혁</t>
+  </si>
+  <si>
+    <t>전종학</t>
+  </si>
+  <si>
+    <t>장인석</t>
+  </si>
+  <si>
+    <t>김황일</t>
+  </si>
+  <si>
+    <t>양서원</t>
+  </si>
+  <si>
+    <t>장경신</t>
+  </si>
+  <si>
+    <t>박영민</t>
+  </si>
+  <si>
+    <t>이민규</t>
+  </si>
+  <si>
+    <t>배극봉</t>
+  </si>
+  <si>
+    <t>CC&amp;S기술솔루션팀</t>
+  </si>
+  <si>
+    <t>강릉서비스센터</t>
+  </si>
+  <si>
+    <t>거제서비스센터</t>
+  </si>
+  <si>
+    <t>경주서비스센터</t>
+  </si>
+  <si>
+    <t>고객가치혁신한국충청실</t>
+  </si>
+  <si>
+    <t>김천서비스센터</t>
+  </si>
+  <si>
+    <t>김해서비스센터</t>
+  </si>
+  <si>
+    <t>남대구서비스센터</t>
+  </si>
+  <si>
+    <t>동대전서비스센터</t>
+  </si>
+  <si>
+    <t>목포서비스센터</t>
+  </si>
+  <si>
+    <t>사하서비스센터</t>
+  </si>
+  <si>
+    <t>수리자문계</t>
+  </si>
+  <si>
+    <t>안동서비스센터</t>
+  </si>
+  <si>
+    <t>여수서비스센터</t>
+  </si>
+  <si>
+    <t>재무지원_3반</t>
+  </si>
+  <si>
+    <t>제주서비스센터</t>
+  </si>
+  <si>
+    <t>죽전서비스센터</t>
+  </si>
+  <si>
+    <t>해남서비스센터</t>
+  </si>
+  <si>
+    <t>해운대서비스센터</t>
+  </si>
+  <si>
+    <t>커뮤니케이션역량개발팀</t>
+  </si>
+  <si>
+    <t>1. AI Tool을 활용한 서비스 문제해결 워크샵</t>
+  </si>
+  <si>
+    <t>3. 성과관리/ 피플 리더십</t>
+  </si>
+  <si>
+    <t>2. 데이터 핸들링 기초 역량 업그레이드</t>
+  </si>
+  <si>
+    <t>서비스 핵심인재 
+구성원 대상 교육</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>주보연</t>
+  </si>
+  <si>
+    <t>주보연</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>2. 데이터 핸들링 기초 역량 업그레이드</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>송병천</t>
-  </si>
-  <si>
-    <t>문유환</t>
-  </si>
-  <si>
-    <t>이준희</t>
-  </si>
-  <si>
-    <t>박진수</t>
-  </si>
-  <si>
-    <t>손정남</t>
-  </si>
-  <si>
-    <t>김병준</t>
-  </si>
-  <si>
-    <t>윤영진</t>
-  </si>
-  <si>
-    <t>박찬문</t>
-  </si>
-  <si>
-    <t>황재영</t>
-  </si>
-  <si>
-    <t>권순양</t>
-  </si>
-  <si>
-    <t>박지수</t>
-  </si>
-  <si>
-    <t>이태한</t>
-  </si>
-  <si>
-    <t>이승현</t>
-  </si>
-  <si>
-    <t>박승우</t>
-  </si>
-  <si>
-    <t>박기영</t>
-  </si>
-  <si>
-    <t>정연일</t>
-  </si>
-  <si>
-    <t>정수곤</t>
-  </si>
-  <si>
-    <t>박정빈</t>
-  </si>
-  <si>
-    <t>서현규</t>
-  </si>
-  <si>
-    <t>김상우</t>
-  </si>
-  <si>
-    <t>이상기</t>
-  </si>
-  <si>
-    <t>전명수</t>
-  </si>
-  <si>
-    <t>최승연</t>
-  </si>
-  <si>
-    <t>조훈래</t>
-  </si>
-  <si>
-    <t>정관중</t>
-  </si>
-  <si>
-    <t>한관수</t>
-  </si>
-  <si>
-    <t>곽동명</t>
-  </si>
-  <si>
-    <t>신현호</t>
-  </si>
-  <si>
-    <t>오흥철</t>
-  </si>
-  <si>
-    <t>한승용</t>
-  </si>
-  <si>
-    <t>한대식</t>
-  </si>
-  <si>
-    <t>김민우</t>
-  </si>
-  <si>
-    <t>이기모</t>
-  </si>
-  <si>
-    <t>심용석</t>
-  </si>
-  <si>
-    <t>홍상연</t>
-  </si>
-  <si>
-    <t>정범철</t>
-  </si>
-  <si>
-    <t>한영호</t>
-  </si>
-  <si>
-    <t>송승헌</t>
-  </si>
-  <si>
-    <t>윤치운</t>
-  </si>
-  <si>
-    <t>정진호</t>
-  </si>
-  <si>
-    <t>김재원</t>
-  </si>
-  <si>
-    <t>김권영</t>
-  </si>
-  <si>
-    <t>김범룡</t>
-  </si>
-  <si>
-    <t>박우경</t>
-  </si>
-  <si>
-    <t>한의진</t>
-  </si>
-  <si>
-    <t>임호성</t>
-  </si>
-  <si>
-    <t>조경원</t>
-  </si>
-  <si>
-    <t>김수훈</t>
-  </si>
-  <si>
-    <t>강상봉</t>
-  </si>
-  <si>
-    <t>최건영</t>
-  </si>
-  <si>
-    <t>신길재</t>
-  </si>
-  <si>
-    <t>김영우</t>
-  </si>
-  <si>
-    <t>홍성민</t>
-  </si>
-  <si>
-    <t>김명호</t>
-  </si>
-  <si>
-    <t>김인성</t>
-  </si>
-  <si>
-    <t>김장수</t>
-  </si>
-  <si>
-    <t>강수호</t>
-  </si>
-  <si>
-    <t>박진영</t>
-  </si>
-  <si>
-    <t>백종엽</t>
-  </si>
-  <si>
-    <t>손상범</t>
-  </si>
-  <si>
-    <t>김솔이</t>
-  </si>
-  <si>
-    <t>이동우</t>
-  </si>
-  <si>
-    <t>박창호</t>
-  </si>
-  <si>
-    <t>이성민</t>
-  </si>
-  <si>
-    <t>박선민</t>
-  </si>
-  <si>
-    <t>권혁민</t>
-  </si>
-  <si>
-    <t>김한승</t>
-  </si>
-  <si>
-    <t>이창진</t>
-  </si>
-  <si>
-    <t>강준수</t>
-  </si>
-  <si>
-    <t>김태현</t>
-  </si>
-  <si>
-    <t>유보선</t>
-  </si>
-  <si>
-    <t>이태우</t>
-  </si>
-  <si>
-    <t>이동수</t>
-  </si>
-  <si>
-    <t>윤명하</t>
-  </si>
-  <si>
-    <t>이덕만</t>
-  </si>
-  <si>
-    <t>이은경</t>
-  </si>
-  <si>
-    <t>염수일</t>
-  </si>
-  <si>
-    <t>김호량</t>
-  </si>
-  <si>
-    <t>송종우</t>
-  </si>
-  <si>
-    <t>손준우</t>
-  </si>
-  <si>
-    <t>안혜성</t>
-  </si>
-  <si>
-    <t>정혜림</t>
-  </si>
-  <si>
-    <t>강동원</t>
-  </si>
-  <si>
-    <t>2026-05-21 ~ 22</t>
+    <t>오수경</t>
+  </si>
+  <si>
+    <t>오수경</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>경산서비스센터</t>
-  </si>
-  <si>
-    <t>광산서비스센터</t>
-  </si>
-  <si>
-    <t>광진서비스센터</t>
-  </si>
-  <si>
-    <t>구미서비스센터</t>
-  </si>
-  <si>
-    <t>김포서비스센터</t>
-  </si>
-  <si>
-    <t>남부역량지원계</t>
-  </si>
-  <si>
-    <t>남수원서비스센터</t>
-  </si>
-  <si>
-    <t>남울산서비스센터</t>
-  </si>
-  <si>
-    <t>남청주서비스센터</t>
-  </si>
-  <si>
-    <t>대치서비스센터</t>
-  </si>
-  <si>
-    <t>덕천서비스센터</t>
-  </si>
-  <si>
-    <t>동대구서비스센터</t>
-  </si>
-  <si>
-    <t>동래서비스센터</t>
-  </si>
-  <si>
-    <t>마산서비스센터</t>
-  </si>
-  <si>
-    <t>부천서비스센터</t>
-  </si>
-  <si>
-    <t>북울산서비스센터</t>
-  </si>
-  <si>
-    <t>북인천서비스센터</t>
-  </si>
-  <si>
-    <t>서광주서비스센터</t>
-  </si>
-  <si>
-    <t>서귀포서비스센터</t>
-  </si>
-  <si>
-    <t>서대구서비스센터</t>
-  </si>
-  <si>
-    <t>서대전서비스센터</t>
-  </si>
-  <si>
-    <t>서면서비스센터</t>
-  </si>
-  <si>
-    <t>서부역량강화팀</t>
-  </si>
-  <si>
-    <t>서안산서비스센터</t>
-  </si>
-  <si>
-    <t>서초서비스센터</t>
-  </si>
-  <si>
-    <t>세종서비스센터</t>
-  </si>
-  <si>
-    <t>속초서비스센터</t>
-  </si>
-  <si>
-    <t>수도권역량지원계</t>
-  </si>
-  <si>
-    <t>아산서비스센터</t>
-  </si>
-  <si>
-    <t>양산서비스센터</t>
-  </si>
-  <si>
-    <t>양천서비스센터</t>
-  </si>
-  <si>
-    <t>오산서비스센터</t>
-  </si>
-  <si>
-    <t>용인출장서비스센터</t>
-  </si>
-  <si>
-    <t>의왕서비스센터</t>
-  </si>
-  <si>
-    <t>의정부서비스센터</t>
-  </si>
-  <si>
-    <t>이천서비스센터</t>
-  </si>
-  <si>
-    <t>일산서비스센터</t>
-  </si>
-  <si>
-    <t>진주서비스센터</t>
-  </si>
-  <si>
-    <t>창원서비스센터</t>
-  </si>
-  <si>
-    <t>충무로역서비스센터</t>
-  </si>
-  <si>
-    <t>태백서비스센터</t>
-  </si>
-  <si>
-    <t>파주서비스센터</t>
-  </si>
-  <si>
-    <t>포항서비스센터</t>
-  </si>
-  <si>
-    <t>프리미엄케어서비스센터</t>
-  </si>
-  <si>
-    <t>해외CC&amp;S역량개발팀</t>
-  </si>
-  <si>
-    <t>홍대역서비스센터</t>
-  </si>
-  <si>
-    <t>홍성서비스센터</t>
-  </si>
-  <si>
-    <t>대연서비스센터</t>
-  </si>
-  <si>
-    <t>남동서비스센터</t>
-  </si>
-  <si>
-    <t>남양주서비스센터</t>
-  </si>
-  <si>
-    <t>용산서비스센터</t>
-  </si>
-  <si>
-    <t>하남서비스센터</t>
-  </si>
-  <si>
-    <t>동해서비스센터</t>
-  </si>
-  <si>
-    <t>홍성길</t>
-  </si>
-  <si>
-    <t>김은기</t>
-  </si>
-  <si>
-    <t>최종근</t>
-  </si>
-  <si>
-    <t>심경훈</t>
-  </si>
-  <si>
-    <t>서상혁</t>
-  </si>
-  <si>
-    <t>이춘훈</t>
-  </si>
-  <si>
-    <t>현두용</t>
-  </si>
-  <si>
-    <t>심세윤</t>
-  </si>
-  <si>
-    <t>이창혁</t>
-  </si>
-  <si>
-    <t>김민섭</t>
-  </si>
-  <si>
-    <t>이민호</t>
-  </si>
-  <si>
-    <t>박찬석</t>
-  </si>
-  <si>
-    <t>장영목</t>
-  </si>
-  <si>
-    <t>나영민</t>
-  </si>
-  <si>
-    <t>도성준</t>
-  </si>
-  <si>
-    <t>박치원</t>
-  </si>
-  <si>
-    <t>권혁</t>
-  </si>
-  <si>
-    <t>이철호</t>
-  </si>
-  <si>
-    <t>이경훈</t>
-  </si>
-  <si>
-    <t>장대원</t>
-  </si>
-  <si>
-    <t>김기현</t>
-  </si>
-  <si>
-    <t>김효림</t>
-  </si>
-  <si>
-    <t>서영식</t>
-  </si>
-  <si>
-    <t>오원규</t>
-  </si>
-  <si>
-    <t>오진석</t>
-  </si>
-  <si>
-    <t>방설빈</t>
-  </si>
-  <si>
-    <t>안홍기</t>
-  </si>
-  <si>
-    <t>정재욱</t>
-  </si>
-  <si>
-    <t>홍경주</t>
-  </si>
-  <si>
-    <t>윤경찬</t>
-  </si>
-  <si>
-    <t>박정민</t>
-  </si>
-  <si>
-    <t>박지호</t>
-  </si>
-  <si>
-    <t>최기성</t>
-  </si>
-  <si>
-    <t>문종민</t>
-  </si>
-  <si>
-    <t>박경배</t>
-  </si>
-  <si>
-    <t>김승환</t>
-  </si>
-  <si>
-    <t>조덕희</t>
-  </si>
-  <si>
-    <t>권기만</t>
-  </si>
-  <si>
-    <t>김호영</t>
-  </si>
-  <si>
-    <t>김대현</t>
-  </si>
-  <si>
-    <t>정필완</t>
-  </si>
-  <si>
-    <t>엄영섭</t>
-  </si>
-  <si>
-    <t>김성원</t>
-  </si>
-  <si>
-    <t>김남덕</t>
-  </si>
-  <si>
-    <t>박재홍</t>
-  </si>
-  <si>
-    <t>오종택</t>
-  </si>
-  <si>
-    <t>양광복</t>
-  </si>
-  <si>
-    <t>이기춘</t>
-  </si>
-  <si>
-    <t>고창진</t>
-  </si>
-  <si>
-    <t>안희진</t>
-  </si>
-  <si>
-    <t>홍희진</t>
-  </si>
-  <si>
-    <t>강호성</t>
-  </si>
-  <si>
-    <t>최영진</t>
-  </si>
-  <si>
-    <t>최왕경</t>
-  </si>
-  <si>
-    <t>김영길</t>
-  </si>
-  <si>
-    <t>이춘재</t>
-  </si>
-  <si>
-    <t>송민규</t>
-  </si>
-  <si>
-    <t>김보성</t>
-  </si>
-  <si>
-    <t>한광일</t>
-  </si>
-  <si>
-    <t>현기혁</t>
-  </si>
-  <si>
-    <t>전종학</t>
-  </si>
-  <si>
-    <t>장인석</t>
-  </si>
-  <si>
-    <t>김황일</t>
-  </si>
-  <si>
-    <t>양서원</t>
-  </si>
-  <si>
-    <t>장경신</t>
-  </si>
-  <si>
-    <t>박영민</t>
-  </si>
-  <si>
-    <t>이민규</t>
-  </si>
-  <si>
-    <t>배극봉</t>
-  </si>
-  <si>
-    <t>CC&amp;S기술솔루션팀</t>
-  </si>
-  <si>
-    <t>강릉서비스센터</t>
-  </si>
-  <si>
-    <t>거제서비스센터</t>
-  </si>
-  <si>
-    <t>경주서비스센터</t>
-  </si>
-  <si>
-    <t>고객가치혁신한국충청실</t>
-  </si>
-  <si>
-    <t>김천서비스센터</t>
-  </si>
-  <si>
-    <t>김해서비스센터</t>
-  </si>
-  <si>
-    <t>남대구서비스센터</t>
-  </si>
-  <si>
-    <t>동대전서비스센터</t>
-  </si>
-  <si>
-    <t>목포서비스센터</t>
-  </si>
-  <si>
-    <t>사하서비스센터</t>
-  </si>
-  <si>
-    <t>수리자문계</t>
-  </si>
-  <si>
-    <t>안동서비스센터</t>
-  </si>
-  <si>
-    <t>여수서비스센터</t>
-  </si>
-  <si>
-    <t>재무지원_3반</t>
-  </si>
-  <si>
-    <t>제주서비스센터</t>
-  </si>
-  <si>
-    <t>죽전서비스센터</t>
-  </si>
-  <si>
-    <t>해남서비스센터</t>
-  </si>
-  <si>
-    <t>해운대서비스센터</t>
-  </si>
-  <si>
-    <t>커뮤니케이션역량개발팀</t>
-  </si>
-  <si>
-    <t>1. AI Tool을 활용한 서비스 문제해결 워크샵</t>
-  </si>
-  <si>
-    <t>3. 성과관리/ 피플 리더십</t>
-  </si>
-  <si>
-    <t>2. 데이터 핸들링 기초 역량 업그레이드</t>
-  </si>
-  <si>
-    <t>26년 서비스 핵심인재(JLP/SLP) 
-구성원 대상 교육</t>
+    <t>강예원</t>
+  </si>
+  <si>
+    <t>강예원</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전우진</t>
+  </si>
+  <si>
+    <t>전우진</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>나은숙</t>
+  </si>
+  <si>
+    <t>나은숙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김태경</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>남우섭</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>한철훈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>고객가치혁신EXG팀</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2780,10 +2828,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:F210"/>
+  <dimension ref="A2:F216"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.109375" customWidth="1"/>
     <col min="3" max="3" width="15.77734375" customWidth="1"/>
     <col min="4" max="4" width="50.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="15.77734375" customWidth="1"/>
@@ -2804,7 +2852,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
@@ -2822,10 +2870,10 @@
         <v>4</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>7</v>
@@ -2836,640 +2884,640 @@
         <v>6</v>
       </c>
       <c r="B5" s="1"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="2"/>
+      <c r="C5" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="6" spans="1:6" ht="16.5" customHeight="1">
       <c r="A6" s="7"/>
       <c r="B6" s="1"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="6"/>
+      <c r="C6" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="16.5" customHeight="1">
       <c r="A7" s="7"/>
-      <c r="B7" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="B7" s="1"/>
       <c r="C7" s="2" t="s">
-        <v>44</v>
+        <v>284</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="F7" s="6">
-        <v>318537</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="16.5">
+        <v>132</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="16.5" customHeight="1">
       <c r="A8" s="7"/>
-      <c r="B8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>50</v>
+      <c r="B8" s="1"/>
+      <c r="C8" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>275</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="13.5" customHeight="1">
-      <c r="A9" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>51</v>
+        <v>285</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="16.5" customHeight="1">
+      <c r="A9" s="7"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="2" t="s">
+        <v>288</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="E9" s="5">
-        <v>46163</v>
-      </c>
-      <c r="F9" s="1">
-        <v>288202</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="16.5">
+        <v>275</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="16.5" customHeight="1">
       <c r="A10" s="7"/>
       <c r="B10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E10" s="5">
-        <v>46163</v>
-      </c>
-      <c r="F10" s="1">
-        <v>292081</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="16.5">
+        <v>292</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F10" s="6">
+        <v>112700</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="16.5" customHeight="1">
       <c r="A11" s="7"/>
       <c r="B11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E11" s="5">
-        <v>46163</v>
-      </c>
-      <c r="F11" s="1">
-        <v>294132</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="16.5">
+        <v>292</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F11" s="6">
+        <v>307880</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="16.5" customHeight="1">
       <c r="A12" s="7"/>
       <c r="B12" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E12" s="5">
-        <v>46163</v>
-      </c>
-      <c r="F12" s="1">
-        <v>292887</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="16.5">
+        <v>292</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F12" s="6">
+        <v>42952</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="16.5" customHeight="1">
       <c r="A13" s="7"/>
       <c r="B13" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="E13" s="5">
-        <v>46163</v>
-      </c>
-      <c r="F13" s="1">
-        <v>288903</v>
+        <v>292</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F13" s="6">
+        <v>318537</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="16.5">
       <c r="A14" s="7"/>
       <c r="B14" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E14" s="5">
-        <v>46163</v>
-      </c>
-      <c r="F14" s="1">
-        <v>292985</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="16.5">
-      <c r="A15" s="7"/>
+        <v>43</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="6"/>
+      <c r="E14" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A15" s="7" t="s">
+        <v>5</v>
+      </c>
       <c r="B15" s="1" t="s">
-        <v>138</v>
+        <v>31</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E15" s="5">
         <v>46163</v>
       </c>
       <c r="F15" s="1">
-        <v>292154</v>
+        <v>288202</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="16.5">
       <c r="A16" s="7"/>
       <c r="B16" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E16" s="5">
         <v>46163</v>
       </c>
       <c r="F16" s="1">
-        <v>288884</v>
+        <v>292081</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="16.5">
       <c r="A17" s="7"/>
       <c r="B17" s="1" t="s">
-        <v>139</v>
+        <v>26</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E17" s="5">
         <v>46163</v>
       </c>
       <c r="F17" s="1">
-        <v>289026</v>
+        <v>294132</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="16.5">
       <c r="A18" s="7"/>
       <c r="B18" s="1" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>278</v>
+        <v>52</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>275</v>
       </c>
       <c r="E18" s="5">
         <v>46163</v>
       </c>
       <c r="F18" s="1">
-        <v>289046</v>
+        <v>292887</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="16.5">
       <c r="A19" s="7"/>
       <c r="B19" s="1" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>276</v>
+        <v>53</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="E19" s="5">
         <v>46163</v>
       </c>
       <c r="F19" s="1">
-        <v>291755</v>
+        <v>288903</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="16.5">
       <c r="A20" s="7"/>
       <c r="B20" s="1" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E20" s="5">
         <v>46163</v>
       </c>
       <c r="F20" s="1">
-        <v>288252</v>
+        <v>292985</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="16.5">
       <c r="A21" s="7"/>
       <c r="B21" s="1" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E21" s="5">
         <v>46163</v>
       </c>
       <c r="F21" s="1">
-        <v>288752</v>
+        <v>292154</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="16.5">
       <c r="A22" s="7"/>
       <c r="B22" s="1" t="s">
-        <v>143</v>
+        <v>30</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E22" s="5">
         <v>46163</v>
       </c>
       <c r="F22" s="1">
-        <v>288383</v>
+        <v>288884</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="16.5">
       <c r="A23" s="7"/>
       <c r="B23" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>277</v>
+        <v>57</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>275</v>
       </c>
       <c r="E23" s="5">
         <v>46163</v>
       </c>
       <c r="F23" s="1">
-        <v>288685</v>
+        <v>289026</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="16.5">
       <c r="A24" s="7"/>
       <c r="B24" s="1" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>276</v>
       </c>
       <c r="E24" s="5">
         <v>46163</v>
       </c>
       <c r="F24" s="1">
-        <v>288602</v>
+        <v>289046</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="16.5">
       <c r="A25" s="7"/>
       <c r="B25" s="1" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E25" s="5">
         <v>46163</v>
       </c>
       <c r="F25" s="1">
-        <v>288771</v>
+        <v>291755</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="16.5">
       <c r="A26" s="7"/>
       <c r="B26" s="1" t="s">
-        <v>39</v>
+        <v>139</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E26" s="5">
         <v>46163</v>
       </c>
       <c r="F26" s="1">
-        <v>288390</v>
+        <v>288252</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="16.5">
       <c r="A27" s="7"/>
       <c r="B27" s="1" t="s">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E27" s="5">
         <v>46163</v>
       </c>
       <c r="F27" s="1">
-        <v>288195</v>
+        <v>288752</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="16.5">
       <c r="A28" s="7"/>
       <c r="B28" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>277</v>
+        <v>62</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>275</v>
       </c>
       <c r="E28" s="5">
         <v>46163</v>
       </c>
       <c r="F28" s="1">
-        <v>288328</v>
+        <v>288383</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="16.5">
       <c r="A29" s="7"/>
       <c r="B29" s="1" t="s">
-        <v>38</v>
+        <v>142</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>277</v>
+        <v>63</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="E29" s="5">
         <v>46163</v>
       </c>
       <c r="F29" s="1">
-        <v>288940</v>
+        <v>288685</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="16.5">
       <c r="A30" s="7"/>
       <c r="B30" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E30" s="5">
         <v>46163</v>
       </c>
       <c r="F30" s="1">
-        <v>292197</v>
+        <v>288602</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="16.5">
       <c r="A31" s="7"/>
       <c r="B31" s="1" t="s">
-        <v>24</v>
+        <v>143</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E31" s="5">
         <v>46163</v>
       </c>
       <c r="F31" s="1">
-        <v>294169</v>
+        <v>288771</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="16.5">
       <c r="A32" s="7"/>
       <c r="B32" s="1" t="s">
-        <v>148</v>
+        <v>39</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E32" s="5">
         <v>46163</v>
       </c>
       <c r="F32" s="1">
-        <v>291962</v>
+        <v>288390</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="16.5">
       <c r="A33" s="7"/>
       <c r="B33" s="1" t="s">
-        <v>149</v>
+        <v>18</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>277</v>
+        <v>67</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>276</v>
       </c>
       <c r="E33" s="5">
         <v>46163</v>
       </c>
       <c r="F33" s="1">
-        <v>288985</v>
+        <v>288195</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="16.5">
       <c r="A34" s="7"/>
       <c r="B34" s="1" t="s">
-        <v>41</v>
+        <v>144</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>277</v>
+        <v>68</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="E34" s="5">
         <v>46163</v>
       </c>
       <c r="F34" s="1">
-        <v>293266</v>
+        <v>288328</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="16.5">
       <c r="A35" s="7"/>
       <c r="B35" s="1" t="s">
-        <v>150</v>
+        <v>38</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E35" s="5">
         <v>46163</v>
       </c>
       <c r="F35" s="1">
-        <v>288810</v>
+        <v>288940</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="16.5">
       <c r="A36" s="7"/>
       <c r="B36" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E36" s="5">
         <v>46163</v>
       </c>
       <c r="F36" s="1">
-        <v>291798</v>
+        <v>292197</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="16.5">
       <c r="A37" s="7"/>
       <c r="B37" s="1" t="s">
-        <v>152</v>
+        <v>24</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E37" s="5">
         <v>46163</v>
       </c>
       <c r="F37" s="1">
-        <v>288562</v>
+        <v>294169</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="16.5">
       <c r="A38" s="7"/>
       <c r="B38" s="1" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>276</v>
+        <v>72</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>275</v>
       </c>
       <c r="E38" s="5">
         <v>46163</v>
       </c>
       <c r="F38" s="1">
-        <v>289019</v>
+        <v>291962</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="16.5">
       <c r="A39" s="7"/>
       <c r="B39" s="1" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>277</v>
+        <v>73</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="E39" s="5">
         <v>46163</v>
       </c>
       <c r="F39" s="1">
-        <v>291999</v>
+        <v>288985</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="16.5">
       <c r="A40" s="7"/>
       <c r="B40" s="1" t="s">
-        <v>155</v>
+        <v>41</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E40" s="5">
         <v>46163</v>
       </c>
       <c r="F40" s="1">
-        <v>292050</v>
+        <v>293266</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="16.5">
       <c r="A41" s="7"/>
       <c r="B41" s="1" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>276</v>
@@ -3478,520 +3526,520 @@
         <v>46163</v>
       </c>
       <c r="F41" s="1">
-        <v>294122</v>
+        <v>288810</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="16.5">
       <c r="A42" s="7"/>
       <c r="B42" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E42" s="5">
         <v>46163</v>
       </c>
       <c r="F42" s="1">
-        <v>291802</v>
+        <v>291798</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="16.5">
       <c r="A43" s="7"/>
       <c r="B43" s="1" t="s">
-        <v>34</v>
+        <v>150</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>277</v>
+        <v>77</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>276</v>
       </c>
       <c r="E43" s="5">
         <v>46163</v>
       </c>
       <c r="F43" s="1">
-        <v>288478</v>
+        <v>288562</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="16.5">
       <c r="A44" s="7"/>
       <c r="B44" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>277</v>
+        <v>78</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>274</v>
       </c>
       <c r="E44" s="5">
         <v>46163</v>
       </c>
       <c r="F44" s="1">
-        <v>291939</v>
+        <v>289019</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="16.5">
       <c r="A45" s="7"/>
       <c r="B45" s="1" t="s">
-        <v>33</v>
+        <v>152</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E45" s="5">
         <v>46163</v>
       </c>
       <c r="F45" s="1">
-        <v>288622</v>
+        <v>291999</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="16.5">
       <c r="A46" s="7"/>
       <c r="B46" s="1" t="s">
-        <v>29</v>
+        <v>153</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E46" s="5">
         <v>46163</v>
       </c>
       <c r="F46" s="1">
-        <v>288712</v>
+        <v>292050</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="16.5">
       <c r="A47" s="7"/>
       <c r="B47" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E47" s="5">
         <v>46163</v>
       </c>
       <c r="F47" s="1">
-        <v>288417</v>
+        <v>294122</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="16.5">
       <c r="A48" s="7"/>
       <c r="B48" s="1" t="s">
-        <v>35</v>
+        <v>155</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>277</v>
+        <v>82</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>274</v>
       </c>
       <c r="E48" s="5">
         <v>46163</v>
       </c>
       <c r="F48" s="1">
-        <v>292211</v>
+        <v>291802</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="16.5">
       <c r="A49" s="7"/>
       <c r="B49" s="1" t="s">
-        <v>160</v>
+        <v>34</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>277</v>
+        <v>83</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="E49" s="5">
         <v>46163</v>
       </c>
       <c r="F49" s="1">
-        <v>289099</v>
+        <v>288478</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="16.5">
       <c r="A50" s="7"/>
       <c r="B50" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E50" s="5">
         <v>46163</v>
       </c>
       <c r="F50" s="1">
-        <v>288493</v>
+        <v>291939</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="16.5">
       <c r="A51" s="7"/>
       <c r="B51" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E51" s="5">
         <v>46163</v>
       </c>
       <c r="F51" s="1">
-        <v>289069</v>
+        <v>288622</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="16.5">
       <c r="A52" s="7"/>
       <c r="B52" s="1" t="s">
-        <v>162</v>
+        <v>29</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E52" s="5">
         <v>46163</v>
       </c>
       <c r="F52" s="1">
-        <v>293279</v>
+        <v>288712</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="16.5">
       <c r="A53" s="7"/>
       <c r="B53" s="1" t="s">
-        <v>12</v>
+        <v>157</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>278</v>
+        <v>87</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>276</v>
       </c>
       <c r="E53" s="5">
         <v>46163</v>
       </c>
       <c r="F53" s="1">
-        <v>288472</v>
+        <v>288417</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="16.5">
       <c r="A54" s="7"/>
       <c r="B54" s="1" t="s">
-        <v>163</v>
+        <v>35</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>278</v>
+        <v>88</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="E54" s="5">
         <v>46163</v>
       </c>
       <c r="F54" s="1">
-        <v>291911</v>
+        <v>292211</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="16.5">
       <c r="A55" s="7"/>
       <c r="B55" s="1" t="s">
-        <v>19</v>
+        <v>158</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E55" s="5">
         <v>46163</v>
       </c>
       <c r="F55" s="1">
-        <v>288997</v>
+        <v>289099</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="16.5">
       <c r="A56" s="7"/>
       <c r="B56" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E56" s="5">
         <v>46163</v>
       </c>
       <c r="F56" s="1">
-        <v>288828</v>
+        <v>288493</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="16.5">
       <c r="A57" s="7"/>
       <c r="B57" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E57" s="5">
         <v>46163</v>
       </c>
       <c r="F57" s="1">
-        <v>292018</v>
+        <v>289069</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="16.5">
       <c r="A58" s="7"/>
       <c r="B58" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>276</v>
+        <v>92</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>274</v>
       </c>
       <c r="E58" s="5">
         <v>46163</v>
       </c>
       <c r="F58" s="1">
-        <v>288615</v>
+        <v>293279</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="16.5">
       <c r="A59" s="7"/>
       <c r="B59" s="1" t="s">
-        <v>167</v>
+        <v>12</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>277</v>
+        <v>93</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>276</v>
       </c>
       <c r="E59" s="5">
         <v>46163</v>
       </c>
       <c r="F59" s="1">
-        <v>288716</v>
+        <v>288472</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="16.5">
       <c r="A60" s="7"/>
       <c r="B60" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E60" s="5">
         <v>46163</v>
       </c>
       <c r="F60" s="1">
-        <v>288342</v>
+        <v>291911</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="16.5">
       <c r="A61" s="7"/>
       <c r="B61" s="1" t="s">
-        <v>169</v>
+        <v>19</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E61" s="5">
         <v>46163</v>
       </c>
       <c r="F61" s="1">
-        <v>288799</v>
+        <v>288997</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="16.5">
       <c r="A62" s="7"/>
       <c r="B62" s="1" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E62" s="5">
         <v>46163</v>
       </c>
       <c r="F62" s="1">
-        <v>294053</v>
+        <v>288828</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="16.5">
       <c r="A63" s="7"/>
       <c r="B63" s="1" t="s">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>277</v>
+        <v>97</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>275</v>
       </c>
       <c r="E63" s="5">
         <v>46163</v>
       </c>
       <c r="F63" s="1">
-        <v>288839</v>
+        <v>292018</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="16.5">
       <c r="A64" s="7"/>
       <c r="B64" s="1" t="s">
-        <v>32</v>
+        <v>164</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>278</v>
+        <v>98</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>274</v>
       </c>
       <c r="E64" s="5">
         <v>46163</v>
       </c>
       <c r="F64" s="1">
-        <v>288841</v>
+        <v>288615</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="16.5">
       <c r="A65" s="7"/>
       <c r="B65" s="1" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E65" s="5">
         <v>46163</v>
       </c>
       <c r="F65" s="1">
-        <v>288803</v>
+        <v>288716</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="16.5">
       <c r="A66" s="7"/>
       <c r="B66" s="1" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E66" s="5">
         <v>46163</v>
       </c>
       <c r="F66" s="1">
-        <v>288883</v>
+        <v>288342</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="16.5">
       <c r="A67" s="7"/>
       <c r="B67" s="1" t="s">
-        <v>15</v>
+        <v>167</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E67" s="5">
         <v>46163</v>
       </c>
       <c r="F67" s="1">
-        <v>291769</v>
+        <v>288799</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="16.5">
       <c r="A68" s="7"/>
       <c r="B68" s="1" t="s">
-        <v>23</v>
+        <v>168</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D68" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>276</v>
       </c>
       <c r="E68" s="5">
         <v>46163</v>
       </c>
       <c r="F68" s="1">
-        <v>310164</v>
+        <v>294053</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="16.5">
       <c r="A69" s="7"/>
       <c r="B69" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>277</v>
+        <v>103</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="E69" s="5">
         <v>46163</v>
       </c>
       <c r="F69" s="1">
-        <v>289079</v>
+        <v>288839</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="16.5">
       <c r="A70" s="7"/>
       <c r="B70" s="1" t="s">
-        <v>175</v>
+        <v>32</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>276</v>
@@ -4000,1730 +4048,1790 @@
         <v>46163</v>
       </c>
       <c r="F70" s="1">
-        <v>288227</v>
+        <v>288841</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="16.5">
       <c r="A71" s="7"/>
       <c r="B71" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E71" s="5">
         <v>46163</v>
       </c>
       <c r="F71" s="1">
-        <v>288885</v>
+        <v>288803</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="16.5">
       <c r="A72" s="7"/>
       <c r="B72" s="1" t="s">
-        <v>13</v>
+        <v>171</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E72" s="5">
         <v>46163</v>
       </c>
       <c r="F72" s="1">
-        <v>288945</v>
+        <v>288883</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="16.5">
       <c r="A73" s="7"/>
       <c r="B73" s="1" t="s">
-        <v>177</v>
+        <v>15</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E73" s="5">
         <v>46163</v>
       </c>
       <c r="F73" s="1">
-        <v>291739</v>
+        <v>291769</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="16.5">
       <c r="A74" s="7"/>
       <c r="B74" s="1" t="s">
-        <v>178</v>
+        <v>23</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>276</v>
+        <v>108</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>274</v>
       </c>
       <c r="E74" s="5">
         <v>46163</v>
       </c>
       <c r="F74" s="1">
-        <v>289050</v>
+        <v>310164</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="16.5">
       <c r="A75" s="7"/>
       <c r="B75" s="1" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E75" s="5">
         <v>46163</v>
       </c>
       <c r="F75" s="1">
-        <v>288676</v>
+        <v>289079</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="16.5">
       <c r="A76" s="7"/>
       <c r="B76" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>277</v>
+        <v>110</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>274</v>
       </c>
       <c r="E76" s="5">
         <v>46163</v>
       </c>
       <c r="F76" s="1">
-        <v>291894</v>
+        <v>288227</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="16.5">
       <c r="A77" s="7"/>
       <c r="B77" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E77" s="5">
         <v>46163</v>
       </c>
       <c r="F77" s="1">
-        <v>292819</v>
+        <v>288885</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="16.5">
       <c r="A78" s="7"/>
       <c r="B78" s="1" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>11</v>
+        <v>112</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E78" s="5">
         <v>46163</v>
       </c>
       <c r="F78" s="1">
-        <v>289000</v>
+        <v>288945</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="16.5">
       <c r="A79" s="7"/>
       <c r="B79" s="1" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E79" s="5">
         <v>46163</v>
       </c>
       <c r="F79" s="1">
-        <v>288673</v>
+        <v>291739</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="16.5">
       <c r="A80" s="7"/>
       <c r="B80" s="1" t="s">
-        <v>31</v>
+        <v>176</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E80" s="5">
         <v>46163</v>
       </c>
       <c r="F80" s="1">
-        <v>288409</v>
+        <v>289050</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="16.5">
       <c r="A81" s="7"/>
       <c r="B81" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>277</v>
+        <v>115</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>276</v>
       </c>
       <c r="E81" s="5">
         <v>46163</v>
       </c>
       <c r="F81" s="1">
-        <v>292746</v>
+        <v>288676</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="16.5">
       <c r="A82" s="7"/>
       <c r="B82" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>277</v>
+        <v>116</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="E82" s="5">
         <v>46163</v>
       </c>
       <c r="F82" s="1">
-        <v>292381</v>
+        <v>291894</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="16.5">
       <c r="A83" s="7"/>
       <c r="B83" s="1" t="s">
-        <v>39</v>
+        <v>179</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E83" s="5">
         <v>46163</v>
       </c>
       <c r="F83" s="1">
-        <v>292552</v>
+        <v>292819</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="16.5">
       <c r="A84" s="7"/>
       <c r="B84" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>125</v>
+        <v>11</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E84" s="5">
         <v>46163</v>
       </c>
       <c r="F84" s="1">
-        <v>292937</v>
+        <v>289000</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="16.5">
       <c r="A85" s="7"/>
       <c r="B85" s="1" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E85" s="5">
         <v>46163</v>
       </c>
       <c r="F85" s="1">
-        <v>292568</v>
+        <v>288673</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="16.5">
       <c r="A86" s="7"/>
       <c r="B86" s="1" t="s">
-        <v>165</v>
+        <v>31</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>277</v>
+        <v>119</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>274</v>
       </c>
       <c r="E86" s="5">
         <v>46163</v>
       </c>
       <c r="F86" s="1">
-        <v>292135</v>
+        <v>288409</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="16.5">
       <c r="A87" s="7"/>
       <c r="B87" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>277</v>
+        <v>120</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="E87" s="5">
         <v>46163</v>
       </c>
       <c r="F87" s="1">
-        <v>292670</v>
+        <v>292746</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="16.5">
       <c r="A88" s="7"/>
       <c r="B88" s="1" t="s">
-        <v>28</v>
+        <v>182</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E88" s="5">
         <v>46163</v>
       </c>
       <c r="F88" s="1">
-        <v>292124</v>
+        <v>292381</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="16.5">
       <c r="A89" s="7"/>
       <c r="B89" s="1" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E89" s="5">
         <v>46163</v>
       </c>
       <c r="F89" s="1">
-        <v>291784</v>
+        <v>292552</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="16.5">
       <c r="A90" s="7"/>
       <c r="B90" s="1" t="s">
-        <v>186</v>
+        <v>38</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E90" s="5">
         <v>46163</v>
       </c>
       <c r="F90" s="1">
-        <v>292964</v>
+        <v>292937</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="16.5">
       <c r="A91" s="7"/>
       <c r="B91" s="1" t="s">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D91" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>276</v>
       </c>
       <c r="E91" s="5">
         <v>46163</v>
       </c>
       <c r="F91" s="1">
-        <v>292597</v>
+        <v>292568</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="16.5">
       <c r="A92" s="7"/>
       <c r="B92" s="1" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>277</v>
+        <v>125</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="E92" s="5">
         <v>46163</v>
       </c>
       <c r="F92" s="1">
-        <v>289029</v>
+        <v>292135</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="16.5">
       <c r="A93" s="7"/>
       <c r="B93" s="1" t="s">
-        <v>256</v>
+        <v>183</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E93" s="5">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="F93" s="1">
-        <v>293118</v>
+        <v>292670</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="16.5">
       <c r="A94" s="7"/>
       <c r="B94" s="1" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>189</v>
+        <v>127</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E94" s="5">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="F94" s="1">
-        <v>292302</v>
+        <v>292124</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="16.5">
       <c r="A95" s="7"/>
       <c r="B95" s="1" t="s">
-        <v>257</v>
+        <v>23</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>190</v>
+        <v>128</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E95" s="5">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="F95" s="1">
-        <v>292612</v>
+        <v>291784</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="16.5">
       <c r="A96" s="7"/>
       <c r="B96" s="1" t="s">
-        <v>258</v>
+        <v>184</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D96" s="6" t="s">
-        <v>277</v>
+        <v>129</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>275</v>
       </c>
       <c r="E96" s="5">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="F96" s="1">
-        <v>291800</v>
+        <v>292964</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="16.5">
       <c r="A97" s="7"/>
       <c r="B97" s="1" t="s">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>277</v>
+        <v>130</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>274</v>
       </c>
       <c r="E97" s="5">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="F97" s="1">
-        <v>293793</v>
+        <v>292597</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="16.5">
       <c r="A98" s="7"/>
       <c r="B98" s="1" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>193</v>
+        <v>131</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E98" s="5">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="F98" s="1">
-        <v>292579</v>
+        <v>289029</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="16.5">
       <c r="A99" s="7"/>
       <c r="B99" s="1" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E99" s="5">
         <v>46164</v>
       </c>
       <c r="F99" s="1">
-        <v>292246</v>
+        <v>293118</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="16.5">
       <c r="A100" s="7"/>
       <c r="B100" s="1" t="s">
-        <v>260</v>
+        <v>40</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E100" s="5">
         <v>46164</v>
       </c>
       <c r="F100" s="1">
-        <v>294098</v>
+        <v>292302</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="16.5">
       <c r="A101" s="7"/>
       <c r="B101" s="1" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D101" s="6" t="s">
-        <v>278</v>
+        <v>188</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>274</v>
       </c>
       <c r="E101" s="5">
         <v>46164</v>
       </c>
       <c r="F101" s="1">
-        <v>292744</v>
+        <v>292612</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="16.5">
       <c r="A102" s="7"/>
       <c r="B102" s="1" t="s">
-        <v>22</v>
+        <v>256</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>277</v>
+        <v>189</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="E102" s="5">
         <v>46164</v>
       </c>
       <c r="F102" s="1">
-        <v>289068</v>
+        <v>291800</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="16.5">
       <c r="A103" s="7"/>
       <c r="B103" s="1" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E103" s="5">
         <v>46164</v>
       </c>
       <c r="F103" s="1">
-        <v>292848</v>
+        <v>293793</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="16.5">
       <c r="A104" s="7"/>
       <c r="B104" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E104" s="5">
         <v>46164</v>
       </c>
       <c r="F104" s="1">
-        <v>292104</v>
+        <v>292579</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="16.5">
       <c r="A105" s="7"/>
       <c r="B105" s="1" t="s">
-        <v>138</v>
+        <v>257</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E105" s="5">
         <v>46164</v>
       </c>
       <c r="F105" s="1">
-        <v>291920</v>
+        <v>292246</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="16.5">
       <c r="A106" s="7"/>
       <c r="B106" s="1" t="s">
-        <v>30</v>
+        <v>258</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E106" s="5">
         <v>46164</v>
       </c>
       <c r="F106" s="1">
-        <v>289127</v>
+        <v>294098</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="16.5">
       <c r="A107" s="7"/>
       <c r="B107" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="D107" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D107" s="6" t="s">
         <v>276</v>
       </c>
       <c r="E107" s="5">
         <v>46164</v>
       </c>
       <c r="F107" s="1">
-        <v>289137</v>
+        <v>292744</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="16.5">
       <c r="A108" s="7"/>
       <c r="B108" s="1" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E108" s="5">
         <v>46164</v>
       </c>
       <c r="F108" s="1">
-        <v>275950</v>
+        <v>289068</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="16.5">
       <c r="A109" s="7"/>
       <c r="B109" s="1" t="s">
-        <v>139</v>
+        <v>14</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D109" s="6" t="s">
-        <v>276</v>
+        <v>196</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>275</v>
       </c>
       <c r="E109" s="5">
         <v>46164</v>
       </c>
       <c r="F109" s="1">
-        <v>292464</v>
+        <v>292848</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="16.5">
       <c r="A110" s="7"/>
       <c r="B110" s="1" t="s">
-        <v>262</v>
+        <v>134</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E110" s="5">
         <v>46164</v>
       </c>
       <c r="F110" s="1">
-        <v>292577</v>
+        <v>292104</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="16.5">
       <c r="A111" s="7"/>
       <c r="B111" s="1" t="s">
-        <v>263</v>
+        <v>136</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E111" s="5">
         <v>46164</v>
       </c>
       <c r="F111" s="1">
-        <v>292556</v>
+        <v>291920</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="16.5">
       <c r="A112" s="7"/>
       <c r="B112" s="1" t="s">
-        <v>140</v>
+        <v>30</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E112" s="5">
         <v>46164</v>
       </c>
       <c r="F112" s="1">
-        <v>291916</v>
+        <v>289127</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="16.5">
       <c r="A113" s="7"/>
       <c r="B113" s="1" t="s">
-        <v>140</v>
+        <v>259</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E113" s="5">
         <v>46164</v>
       </c>
       <c r="F113" s="1">
-        <v>292467</v>
+        <v>289137</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="16.5">
       <c r="A114" s="7"/>
       <c r="B114" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="D114" s="6" t="s">
-        <v>277</v>
+        <v>201</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>274</v>
       </c>
       <c r="E114" s="5">
         <v>46164</v>
       </c>
       <c r="F114" s="1">
-        <v>292671</v>
+        <v>275950</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="16.5">
       <c r="A115" s="7"/>
       <c r="B115" s="1" t="s">
-        <v>16</v>
+        <v>137</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>277</v>
+        <v>202</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>274</v>
       </c>
       <c r="E115" s="5">
         <v>46164</v>
       </c>
       <c r="F115" s="1">
-        <v>293006</v>
+        <v>292464</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="16.5">
       <c r="A116" s="7"/>
       <c r="B116" s="1" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E116" s="5">
         <v>46164</v>
       </c>
       <c r="F116" s="1">
-        <v>288561</v>
+        <v>292577</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="16.5">
       <c r="A117" s="7"/>
       <c r="B117" s="1" t="s">
-        <v>145</v>
+        <v>261</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E117" s="5">
         <v>46164</v>
       </c>
       <c r="F117" s="1">
-        <v>288927</v>
+        <v>292556</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="16.5">
       <c r="A118" s="7"/>
       <c r="B118" s="1" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E118" s="5">
         <v>46164</v>
       </c>
       <c r="F118" s="1">
-        <v>288189</v>
+        <v>291916</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="16.5">
       <c r="A119" s="7"/>
       <c r="B119" s="1" t="s">
-        <v>264</v>
+        <v>138</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="D119" s="6" t="s">
-        <v>277</v>
+        <v>206</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>276</v>
       </c>
       <c r="E119" s="5">
         <v>46164</v>
       </c>
       <c r="F119" s="1">
-        <v>293067</v>
+        <v>292467</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="16.5">
       <c r="A120" s="7"/>
       <c r="B120" s="1" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>277</v>
+        <v>207</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="E120" s="5">
         <v>46164</v>
       </c>
       <c r="F120" s="1">
-        <v>292976</v>
+        <v>292671</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="16.5">
       <c r="A121" s="7"/>
       <c r="B121" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E121" s="5">
         <v>46164</v>
       </c>
       <c r="F121" s="1">
-        <v>292622</v>
+        <v>293006</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="16.5">
       <c r="A122" s="7"/>
       <c r="B122" s="1" t="s">
-        <v>265</v>
+        <v>21</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E122" s="5">
         <v>46164</v>
       </c>
       <c r="F122" s="1">
-        <v>292151</v>
+        <v>288561</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="16.5">
       <c r="A123" s="7"/>
       <c r="B123" s="1" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E123" s="5">
         <v>46164</v>
       </c>
       <c r="F123" s="1">
-        <v>288076</v>
+        <v>288927</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="16.5">
       <c r="A124" s="7"/>
       <c r="B124" s="1" t="s">
-        <v>25</v>
+        <v>144</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="D124" s="6" t="s">
-        <v>277</v>
+        <v>211</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>276</v>
       </c>
       <c r="E124" s="5">
         <v>46164</v>
       </c>
       <c r="F124" s="1">
-        <v>292101</v>
+        <v>288189</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="16.5">
       <c r="A125" s="7"/>
       <c r="B125" s="1" t="s">
-        <v>41</v>
+        <v>262</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>278</v>
+        <v>212</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="E125" s="5">
         <v>46164</v>
       </c>
       <c r="F125" s="1">
-        <v>292337</v>
+        <v>293067</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="16.5">
       <c r="A126" s="7"/>
       <c r="B126" s="1" t="s">
-        <v>266</v>
+        <v>145</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E126" s="5">
         <v>46164</v>
       </c>
       <c r="F126" s="1">
-        <v>288287</v>
+        <v>292976</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="16.5">
       <c r="A127" s="7"/>
       <c r="B127" s="1" t="s">
-        <v>152</v>
+        <v>24</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E127" s="5">
         <v>46164</v>
       </c>
       <c r="F127" s="1">
-        <v>292957</v>
+        <v>292622</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="16.5">
       <c r="A128" s="7"/>
       <c r="B128" s="1" t="s">
-        <v>153</v>
+        <v>263</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E128" s="5">
         <v>46164</v>
       </c>
       <c r="F128" s="1">
-        <v>292321</v>
+        <v>292151</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="16.5">
       <c r="A129" s="7"/>
       <c r="B129" s="1" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="D129" s="6" t="s">
-        <v>276</v>
+        <v>8</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>275</v>
       </c>
       <c r="E129" s="5">
         <v>46164</v>
       </c>
       <c r="F129" s="1">
-        <v>288341</v>
+        <v>288076</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="16.5">
       <c r="A130" s="7"/>
       <c r="B130" s="1" t="s">
-        <v>157</v>
+        <v>25</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>276</v>
+        <v>216</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="E130" s="5">
         <v>46164</v>
       </c>
       <c r="F130" s="1">
-        <v>293572</v>
+        <v>292101</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="16.5">
       <c r="A131" s="7"/>
       <c r="B131" s="1" t="s">
-        <v>158</v>
+        <v>41</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E131" s="5">
         <v>46164</v>
       </c>
       <c r="F131" s="1">
-        <v>292258</v>
+        <v>292337</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="16.5">
       <c r="A132" s="7"/>
       <c r="B132" s="1" t="s">
-        <v>33</v>
+        <v>264</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>9</v>
+        <v>218</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E132" s="5">
         <v>46164</v>
       </c>
       <c r="F132" s="1">
-        <v>292763</v>
+        <v>288287</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="16.5">
       <c r="A133" s="7"/>
       <c r="B133" s="1" t="s">
-        <v>29</v>
+        <v>150</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E133" s="5">
         <v>46164</v>
       </c>
       <c r="F133" s="1">
-        <v>293450</v>
+        <v>292957</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="16.5">
       <c r="A134" s="7"/>
       <c r="B134" s="1" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D134" s="6" t="s">
-        <v>277</v>
+        <v>220</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>275</v>
       </c>
       <c r="E134" s="5">
         <v>46164</v>
       </c>
       <c r="F134" s="1">
-        <v>288496</v>
+        <v>292321</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="16.5">
       <c r="A135" s="7"/>
       <c r="B135" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>277</v>
+        <v>221</v>
+      </c>
+      <c r="D135" s="6" t="s">
+        <v>274</v>
       </c>
       <c r="E135" s="5">
         <v>46164</v>
       </c>
       <c r="F135" s="1">
-        <v>293071</v>
+        <v>288341</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="16.5">
       <c r="A136" s="7"/>
       <c r="B136" s="1" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E136" s="5">
         <v>46164</v>
       </c>
       <c r="F136" s="1">
-        <v>292711</v>
+        <v>293572</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="16.5">
       <c r="A137" s="7"/>
       <c r="B137" s="1" t="s">
-        <v>267</v>
+        <v>156</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E137" s="5">
         <v>46164</v>
       </c>
       <c r="F137" s="1">
-        <v>292946</v>
+        <v>292258</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="16.5">
       <c r="A138" s="7"/>
       <c r="B138" s="1" t="s">
-        <v>268</v>
+        <v>33</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>231</v>
+        <v>9</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E138" s="5">
         <v>46164</v>
       </c>
       <c r="F138" s="1">
-        <v>292037</v>
+        <v>292763</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="16.5">
       <c r="A139" s="7"/>
       <c r="B139" s="1" t="s">
-        <v>269</v>
+        <v>29</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E139" s="5">
         <v>46164</v>
       </c>
       <c r="F139" s="1">
-        <v>292513</v>
+        <v>293450</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="16.5">
       <c r="A140" s="7"/>
       <c r="B140" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>277</v>
+        <v>225</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="E140" s="5">
         <v>46164</v>
       </c>
       <c r="F140" s="1">
-        <v>291821</v>
+        <v>288496</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="16.5">
       <c r="A141" s="7"/>
       <c r="B141" s="1" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E141" s="5">
         <v>46164</v>
       </c>
       <c r="F141" s="1">
-        <v>292843</v>
+        <v>293071</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="16.5">
       <c r="A142" s="7"/>
       <c r="B142" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="D142" s="6" t="s">
-        <v>277</v>
+        <v>227</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>276</v>
       </c>
       <c r="E142" s="5">
         <v>46164</v>
       </c>
       <c r="F142" s="1">
-        <v>292997</v>
+        <v>292711</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="16.5">
       <c r="A143" s="7"/>
       <c r="B143" s="1" t="s">
-        <v>36</v>
+        <v>265</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>10</v>
+        <v>228</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E143" s="5">
         <v>46164</v>
       </c>
       <c r="F143" s="1">
-        <v>293463</v>
+        <v>292946</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="16.5">
       <c r="A144" s="7"/>
       <c r="B144" s="1" t="s">
-        <v>171</v>
+        <v>266</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E144" s="5">
         <v>46164</v>
       </c>
       <c r="F144" s="1">
-        <v>288644</v>
+        <v>292037</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="16.5">
       <c r="A145" s="7"/>
       <c r="B145" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E145" s="5">
         <v>46164</v>
       </c>
       <c r="F145" s="1">
-        <v>291806</v>
+        <v>292513</v>
       </c>
     </row>
     <row r="146" spans="1:6" ht="16.5">
       <c r="A146" s="7"/>
       <c r="B146" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E146" s="5">
         <v>46164</v>
       </c>
       <c r="F146" s="1">
-        <v>293391</v>
+        <v>291821</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="16.5">
       <c r="A147" s="7"/>
       <c r="B147" s="1" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="D147" s="6" t="s">
-        <v>276</v>
+        <v>232</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>275</v>
       </c>
       <c r="E147" s="5">
         <v>46164</v>
       </c>
       <c r="F147" s="1">
-        <v>291924</v>
+        <v>292843</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="16.5">
       <c r="A148" s="7"/>
       <c r="B148" s="1" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>277</v>
+        <v>233</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="E148" s="5">
         <v>46164</v>
       </c>
       <c r="F148" s="1">
-        <v>292227</v>
+        <v>292997</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="16.5">
       <c r="A149" s="7"/>
       <c r="B149" s="1" t="s">
-        <v>172</v>
+        <v>36</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>241</v>
+        <v>10</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E149" s="5">
         <v>46164</v>
       </c>
       <c r="F149" s="1">
-        <v>291979</v>
+        <v>293463</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="16.5">
       <c r="A150" s="7"/>
       <c r="B150" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E150" s="5">
         <v>46164</v>
       </c>
       <c r="F150" s="1">
-        <v>292480</v>
+        <v>288644</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="16.5">
       <c r="A151" s="7"/>
       <c r="B151" s="1" t="s">
-        <v>13</v>
+        <v>268</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E151" s="5">
         <v>46164</v>
       </c>
       <c r="F151" s="1">
-        <v>288251</v>
+        <v>291806</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="16.5">
       <c r="A152" s="7"/>
       <c r="B152" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="D152" s="6" t="s">
-        <v>277</v>
+        <v>236</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>275</v>
       </c>
       <c r="E152" s="5">
         <v>46164</v>
       </c>
       <c r="F152" s="1">
-        <v>293613</v>
+        <v>293391</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="16.5">
       <c r="A153" s="7"/>
       <c r="B153" s="1" t="s">
-        <v>177</v>
+        <v>269</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>278</v>
+        <v>237</v>
+      </c>
+      <c r="D153" s="6" t="s">
+        <v>274</v>
       </c>
       <c r="E153" s="5">
         <v>46164</v>
       </c>
       <c r="F153" s="1">
-        <v>289071</v>
+        <v>291924</v>
       </c>
     </row>
     <row r="154" spans="1:6" ht="16.5">
       <c r="A154" s="7"/>
       <c r="B154" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E154" s="5">
         <v>46164</v>
       </c>
       <c r="F154" s="1">
-        <v>291998</v>
+        <v>292227</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="16.5">
       <c r="A155" s="7"/>
       <c r="B155" s="1" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E155" s="5">
         <v>46164</v>
       </c>
       <c r="F155" s="1">
-        <v>293116</v>
+        <v>291979</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="16.5">
       <c r="A156" s="7"/>
       <c r="B156" s="1" t="s">
-        <v>274</v>
+        <v>171</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E156" s="5">
         <v>46164</v>
       </c>
       <c r="F156" s="1">
-        <v>292199</v>
+        <v>292480</v>
       </c>
     </row>
     <row r="157" spans="1:6" ht="16.5">
       <c r="A157" s="7"/>
       <c r="B157" s="1" t="s">
-        <v>266</v>
+        <v>13</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="D157" s="6" t="s">
-        <v>277</v>
+        <v>241</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>275</v>
       </c>
       <c r="E157" s="5">
         <v>46164</v>
       </c>
       <c r="F157" s="1">
-        <v>288766</v>
+        <v>288251</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="16.5">
       <c r="A158" s="7"/>
       <c r="B158" s="1" t="s">
-        <v>275</v>
+        <v>13</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>277</v>
+        <v>242</v>
+      </c>
+      <c r="D158" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="E158" s="5">
         <v>46164</v>
       </c>
       <c r="F158" s="1">
-        <v>288858</v>
+        <v>293613</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="16.5">
       <c r="A159" s="7"/>
       <c r="B159" s="1" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E159" s="5">
         <v>46164</v>
       </c>
       <c r="F159" s="1">
-        <v>294104</v>
+        <v>289071</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="16.5">
       <c r="A160" s="7"/>
       <c r="B160" s="1" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E160" s="5">
         <v>46164</v>
       </c>
       <c r="F160" s="1">
-        <v>288974</v>
+        <v>291998</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="16.5">
       <c r="A161" s="7"/>
       <c r="B161" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E161" s="5">
         <v>46164</v>
       </c>
       <c r="F161" s="1">
-        <v>288385</v>
+        <v>293116</v>
       </c>
     </row>
     <row r="162" spans="1:6" ht="16.5">
       <c r="A162" s="7"/>
       <c r="B162" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D162" s="6" t="s">
-        <v>277</v>
+        <v>246</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>274</v>
       </c>
       <c r="E162" s="5">
         <v>46164</v>
       </c>
       <c r="F162" s="1">
-        <v>291858</v>
+        <v>292199</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="16.5">
       <c r="A163" s="7"/>
       <c r="B163" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>276</v>
+        <v>247</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="E163" s="5">
         <v>46164</v>
       </c>
       <c r="F163" s="1">
-        <v>288395</v>
+        <v>288766</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="16.5">
       <c r="A164" s="7"/>
-      <c r="B164" s="1"/>
-      <c r="C164" s="1"/>
-      <c r="D164" s="1"/>
-      <c r="E164" s="5"/>
-      <c r="F164" s="1"/>
+      <c r="B164" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E164" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F164" s="1">
+        <v>288858</v>
+      </c>
     </row>
     <row r="165" spans="1:6" ht="16.5">
       <c r="A165" s="7"/>
-      <c r="B165" s="1"/>
-      <c r="C165" s="1"/>
-      <c r="D165" s="1"/>
-      <c r="E165" s="5"/>
-      <c r="F165" s="1"/>
+      <c r="B165" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="E165" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F165" s="1">
+        <v>294104</v>
+      </c>
     </row>
     <row r="166" spans="1:6" ht="16.5">
       <c r="A166" s="7"/>
-      <c r="B166" s="1"/>
-      <c r="C166" s="1"/>
-      <c r="D166" s="1"/>
-      <c r="E166" s="5"/>
-      <c r="F166" s="1"/>
+      <c r="B166" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E166" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F166" s="1">
+        <v>288974</v>
+      </c>
     </row>
     <row r="167" spans="1:6" ht="16.5">
       <c r="A167" s="7"/>
-      <c r="B167" s="1"/>
-      <c r="C167" s="1"/>
-      <c r="D167" s="6"/>
-      <c r="E167" s="5"/>
-      <c r="F167" s="1"/>
+      <c r="B167" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E167" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F167" s="1">
+        <v>288385</v>
+      </c>
     </row>
     <row r="168" spans="1:6" ht="16.5">
       <c r="A168" s="7"/>
-      <c r="B168" s="1"/>
-      <c r="C168" s="1"/>
-      <c r="D168" s="1"/>
-      <c r="E168" s="5"/>
-      <c r="F168" s="1"/>
+      <c r="B168" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D168" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="E168" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F168" s="1">
+        <v>291858</v>
+      </c>
     </row>
     <row r="169" spans="1:6" ht="16.5">
       <c r="A169" s="7"/>
-      <c r="B169" s="1"/>
-      <c r="C169" s="1"/>
-      <c r="D169" s="1"/>
-      <c r="E169" s="5"/>
-      <c r="F169" s="1"/>
+      <c r="B169" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E169" s="5">
+        <v>46164</v>
+      </c>
+      <c r="F169" s="1">
+        <v>288395</v>
+      </c>
     </row>
     <row r="170" spans="1:6" ht="16.5">
       <c r="A170" s="7"/>
@@ -5753,7 +5861,7 @@
       <c r="A173" s="7"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
-      <c r="D173" s="1"/>
+      <c r="D173" s="6"/>
       <c r="E173" s="5"/>
       <c r="F173" s="1"/>
     </row>
@@ -5769,7 +5877,7 @@
       <c r="A175" s="7"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
-      <c r="D175" s="6"/>
+      <c r="D175" s="1"/>
       <c r="E175" s="5"/>
       <c r="F175" s="1"/>
     </row>
@@ -5809,7 +5917,7 @@
       <c r="A180" s="7"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
-      <c r="D180" s="6"/>
+      <c r="D180" s="1"/>
       <c r="E180" s="5"/>
       <c r="F180" s="1"/>
     </row>
@@ -5817,7 +5925,7 @@
       <c r="A181" s="7"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
-      <c r="D181" s="1"/>
+      <c r="D181" s="6"/>
       <c r="E181" s="5"/>
       <c r="F181" s="1"/>
     </row>
@@ -5849,7 +5957,7 @@
       <c r="A185" s="7"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
-      <c r="D185" s="6"/>
+      <c r="D185" s="1"/>
       <c r="E185" s="5"/>
       <c r="F185" s="1"/>
     </row>
@@ -5857,7 +5965,7 @@
       <c r="A186" s="7"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
-      <c r="D186" s="1"/>
+      <c r="D186" s="6"/>
       <c r="E186" s="5"/>
       <c r="F186" s="1"/>
     </row>
@@ -5889,7 +5997,7 @@
       <c r="A190" s="7"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
-      <c r="D190" s="6"/>
+      <c r="D190" s="1"/>
       <c r="E190" s="5"/>
       <c r="F190" s="1"/>
     </row>
@@ -5897,7 +6005,7 @@
       <c r="A191" s="7"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
-      <c r="D191" s="1"/>
+      <c r="D191" s="6"/>
       <c r="E191" s="5"/>
       <c r="F191" s="1"/>
     </row>
@@ -5929,7 +6037,7 @@
       <c r="A195" s="7"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
-      <c r="D195" s="6"/>
+      <c r="D195" s="1"/>
       <c r="E195" s="5"/>
       <c r="F195" s="1"/>
     </row>
@@ -5937,7 +6045,7 @@
       <c r="A196" s="7"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
-      <c r="D196" s="1"/>
+      <c r="D196" s="6"/>
       <c r="E196" s="5"/>
       <c r="F196" s="1"/>
     </row>
@@ -5969,7 +6077,7 @@
       <c r="A200" s="7"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
-      <c r="D200" s="6"/>
+      <c r="D200" s="1"/>
       <c r="E200" s="5"/>
       <c r="F200" s="1"/>
     </row>
@@ -5977,7 +6085,7 @@
       <c r="A201" s="7"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
-      <c r="D201" s="1"/>
+      <c r="D201" s="6"/>
       <c r="E201" s="5"/>
       <c r="F201" s="1"/>
     </row>
@@ -6017,7 +6125,7 @@
       <c r="A206" s="7"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
-      <c r="D206" s="1"/>
+      <c r="D206" s="6"/>
       <c r="E206" s="5"/>
       <c r="F206" s="1"/>
     </row>
@@ -6053,13 +6161,61 @@
       <c r="E210" s="5"/>
       <c r="F210" s="1"/>
     </row>
+    <row r="211" spans="1:6" ht="16.5">
+      <c r="A211" s="7"/>
+      <c r="B211" s="1"/>
+      <c r="C211" s="1"/>
+      <c r="D211" s="1"/>
+      <c r="E211" s="5"/>
+      <c r="F211" s="1"/>
+    </row>
+    <row r="212" spans="1:6" ht="16.5">
+      <c r="A212" s="7"/>
+      <c r="B212" s="1"/>
+      <c r="C212" s="1"/>
+      <c r="D212" s="1"/>
+      <c r="E212" s="5"/>
+      <c r="F212" s="1"/>
+    </row>
+    <row r="213" spans="1:6" ht="16.5">
+      <c r="A213" s="7"/>
+      <c r="B213" s="1"/>
+      <c r="C213" s="1"/>
+      <c r="D213" s="1"/>
+      <c r="E213" s="5"/>
+      <c r="F213" s="1"/>
+    </row>
+    <row r="214" spans="1:6" ht="16.5">
+      <c r="A214" s="7"/>
+      <c r="B214" s="1"/>
+      <c r="C214" s="1"/>
+      <c r="D214" s="1"/>
+      <c r="E214" s="5"/>
+      <c r="F214" s="1"/>
+    </row>
+    <row r="215" spans="1:6" ht="16.5">
+      <c r="A215" s="7"/>
+      <c r="B215" s="1"/>
+      <c r="C215" s="1"/>
+      <c r="D215" s="1"/>
+      <c r="E215" s="5"/>
+      <c r="F215" s="1"/>
+    </row>
+    <row r="216" spans="1:6" ht="16.5">
+      <c r="A216" s="7"/>
+      <c r="B216" s="1"/>
+      <c r="C216" s="1"/>
+      <c r="D216" s="1"/>
+      <c r="E216" s="5"/>
+      <c r="F216" s="1"/>
+    </row>
   </sheetData>
-  <sortState ref="B8:C208">
-    <sortCondition ref="C8:C208"/>
+  <sortState ref="B14:C214">
+    <sortCondition ref="C14:C214"/>
   </sortState>
   <mergeCells count="4">
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="A9:A210"/>
+    <mergeCell ref="A5:A14"/>
+    <mergeCell ref="A15:A216"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B3:F3"/>
   </mergeCells>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\명찰\nametag-app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0AD346-338C-45C7-94B0-E90218F6B4A5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0C72C8-5FBD-4DCF-B4DF-CF23CC95239F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19290" windowHeight="9540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -872,31 +872,55 @@
   </si>
   <si>
     <t>주보연</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 데이터 핸들링 기초 역량 업그레이드</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>오수경</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>강예원</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전우진</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>나은숙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김태경</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>남우섭</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>한철훈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>고객가치혁신EXG팀</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>주보연</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>2. 데이터 핸들링 기초 역량 업그레이드</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>오수경</t>
-  </si>
-  <si>
     <t>오수경</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>강예원</t>
-  </si>
-  <si>
-    <t>강예원</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>전우진</t>
   </si>
   <si>
     <t>전우진</t>
@@ -904,25 +928,6 @@
   </si>
   <si>
     <t>나은숙</t>
-  </si>
-  <si>
-    <t>나은숙</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김태경</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>남우섭</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>한철훈</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>고객가치혁신EXG팀</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2885,23 +2890,23 @@
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>280</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>278</v>
+      <c r="F5" s="6" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="16.5" customHeight="1">
       <c r="A6" s="7"/>
       <c r="B6" s="1"/>
       <c r="C6" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>48</v>
@@ -2910,14 +2915,14 @@
         <v>132</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="16.5" customHeight="1">
       <c r="A7" s="7"/>
       <c r="B7" s="1"/>
       <c r="C7" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>48</v>
@@ -2925,15 +2930,15 @@
       <c r="E7" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>283</v>
+      <c r="F7" s="6" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="16.5" customHeight="1">
       <c r="A8" s="7"/>
       <c r="B8" s="1"/>
       <c r="C8" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>275</v>
@@ -2942,14 +2947,14 @@
         <v>132</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="16.5" customHeight="1">
       <c r="A9" s="7"/>
       <c r="B9" s="1"/>
       <c r="C9" s="2" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>275</v>
@@ -2957,17 +2962,17 @@
       <c r="E9" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>287</v>
+      <c r="F9" s="6" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="16.5" customHeight="1">
       <c r="A10" s="7"/>
       <c r="B10" s="1" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="5" t="s">
@@ -2980,10 +2985,10 @@
     <row r="11" spans="1:6" ht="16.5" customHeight="1">
       <c r="A11" s="7"/>
       <c r="B11" s="1" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="5" t="s">
@@ -2996,10 +3001,10 @@
     <row r="12" spans="1:6" ht="16.5" customHeight="1">
       <c r="A12" s="7"/>
       <c r="B12" s="1" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="5" t="s">
@@ -3012,7 +3017,7 @@
     <row r="13" spans="1:6" ht="16.5" customHeight="1">
       <c r="A13" s="7"/>
       <c r="B13" s="1" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>44</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\명찰\nametag-app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0C72C8-5FBD-4DCF-B4DF-CF23CC95239F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E947D75-ABC4-4442-8D84-8E23D71FD625}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19290" windowHeight="9540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="288">
   <si>
     <t xml:space="preserve">러닝센터 명찰제작 양식 </t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -908,26 +908,6 @@
   </si>
   <si>
     <t>고객가치혁신EXG팀</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>주보연</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>오수경</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>강예원</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>전우진</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>나은숙</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2898,8 +2878,8 @@
       <c r="E5" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>288</v>
+      <c r="F5" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="16.5" customHeight="1">
@@ -2914,8 +2894,8 @@
       <c r="E6" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>289</v>
+      <c r="F6" s="6">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="16.5" customHeight="1">
@@ -2930,8 +2910,8 @@
       <c r="E7" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>290</v>
+      <c r="F7" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="16.5" customHeight="1">
@@ -2946,8 +2926,8 @@
       <c r="E8" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>291</v>
+      <c r="F8" s="6">
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="16.5" customHeight="1">
@@ -2962,8 +2942,8 @@
       <c r="E9" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>292</v>
+      <c r="F9" s="6">
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="16.5" customHeight="1">
